--- a/docs/Datathon Project.xlsx
+++ b/docs/Datathon Project.xlsx
@@ -8,19 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Master of Data Science - UoA\Datathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E74E3BC-DDEF-426D-A999-357D3FC24234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713CCEEA-820A-4DBC-AF60-6729722BE10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Overview" sheetId="2" r:id="rId1"/>
-    <sheet name="Requirements" sheetId="1" r:id="rId2"/>
+    <sheet name="MVP Requirements + Design" sheetId="1" r:id="rId2"/>
     <sheet name="Data Model" sheetId="7" r:id="rId3"/>
     <sheet name="Project Plan" sheetId="3" r:id="rId4"/>
     <sheet name="Risk Matrix" sheetId="4" r:id="rId5"/>
     <sheet name="Team votes" sheetId="5" r:id="rId6"/>
     <sheet name="Tasks" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId9"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Sheet2!$A$1:$M$38</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="455">
   <si>
     <t>MoScoW</t>
   </si>
@@ -632,6 +640,12 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
     <t>Tracker</t>
   </si>
   <si>
@@ -749,13 +763,777 @@
   </si>
   <si>
     <t>(absent) was working on CI/CD pipeline</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>- made ingestion agent in snowflake
+- helped E Sam with access problems
+- was mostly blocked on other things</t>
+  </si>
+  <si>
+    <t>Test full process- WORKING DEMO</t>
+  </si>
+  <si>
+    <t>Presentation</t>
+  </si>
+  <si>
+    <t>24-Sep, 9 pm</t>
+  </si>
+  <si>
+    <t>building visualizations and insights</t>
+  </si>
+  <si>
+    <t>Extract from PDF document to structured data</t>
+  </si>
+  <si>
+    <t>dbt implementation</t>
+  </si>
+  <si>
+    <t>Build UI</t>
+  </si>
+  <si>
+    <t>complete GitHub configuration</t>
+  </si>
+  <si>
+    <t>24-Sep, 8 pm</t>
+  </si>
+  <si>
+    <t>24-sep, 10 am</t>
+  </si>
+  <si>
+    <t>24-sep, 3 pm</t>
+  </si>
+  <si>
+    <t>ingestion pipeline</t>
+  </si>
+  <si>
+    <t>greg</t>
+  </si>
+  <si>
+    <t>db schema</t>
+  </si>
+  <si>
+    <t>permissions</t>
+  </si>
+  <si>
+    <t>front-end implementation - insights</t>
+  </si>
+  <si>
+    <t>ETL and deployment pipeline</t>
+  </si>
+  <si>
+    <t>Snowflake and dbt implementation</t>
+  </si>
+  <si>
+    <t>In-progress</t>
+  </si>
+  <si>
+    <t>24-sep, 7:30 pm</t>
+  </si>
+  <si>
+    <t>To Be Started</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Milestones</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Consequence / impact</t>
+  </si>
+  <si>
+    <t>Likelihood (1–5)</t>
+  </si>
+  <si>
+    <t>Impact (1–5)</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Mitigation / action</t>
+  </si>
+  <si>
+    <t>Trigger</t>
+  </si>
+  <si>
+    <t>Contingency</t>
+  </si>
+  <si>
+    <t>Linked tasks</t>
+  </si>
+  <si>
+    <t>Raised</t>
+  </si>
+  <si>
+    <t>Review by</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>Bedrock model access not granted, or blocked in the trial</t>
+  </si>
+  <si>
+    <t>No LLM extraction; demo loses its AI component</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>Test in the first hour (T05)</t>
+  </si>
+  <si>
+    <t>No successful call by M1</t>
+  </si>
+  <si>
+    <t>Cortex AI_COMPLETE (T26); last resort rules only</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>LLM returns a submitted or comparator figure instead of the court's</t>
+  </si>
+  <si>
+    <t>Wrong figures in charts; credibility with judges</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>Court-determined-only prompt rule; required quote; arithmetic check</t>
+  </si>
+  <si>
+    <t>Money-field accuracy &lt; 80% on gold set</t>
+  </si>
+  <si>
+    <t>Route to REVIEW; narrow to 4 fields</t>
+  </si>
+  <si>
+    <t>R03</t>
+  </si>
+  <si>
+    <t>Scope creep: too many fields, pages or charts</t>
+  </si>
+  <si>
+    <t>Must features unfinished</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>MoSCoW priorities; feature freeze 09:30</t>
+  </si>
+  <si>
+    <t>New feature proposed after M4</t>
+  </si>
+  <si>
+    <t>Park it in the roadmap</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>11:00 code deadline missed</t>
+  </si>
+  <si>
+    <t>Code deliverable missed</t>
+  </si>
+  <si>
+    <t>Milestones and timeboxes; freeze 90 min early</t>
+  </si>
+  <si>
+    <t>M5 more than 1 h late</t>
+  </si>
+  <si>
+    <t>Cut Should/Could tasks; demo on gold set</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>Document variety breaks the rules (old layouts, pre-trial rulings, several defendants)</t>
+  </si>
+  <si>
+    <t>Missing or wrong fields for some documents</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>Classify type first; multi-defendant schema; test both layouts</t>
+  </si>
+  <si>
+    <t>Rule accuracy &lt; 95% on gold set</t>
+  </si>
+  <si>
+    <t>Send failing fields to LLM at REVIEW tier</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>Text noise (footnotes, headers) breaks paragraphs and quotes</t>
+  </si>
+  <si>
+    <t>More quotes fail verification; bigger review queue</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Tested cleaner; normalised quote matching</t>
+  </si>
+  <si>
+    <t>&gt; 5% of quotes fail verification</t>
+  </si>
+  <si>
+    <t>Fuzzy match; check neighbouring paragraphs</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>Team cannot explain AI-generated code</t>
+  </si>
+  <si>
+    <t>Judging penalty on code quality</t>
+  </si>
+  <si>
+    <t>Owner reviews and explains every PR</t>
+  </si>
+  <si>
+    <t>Reviewer cannot explain a PR</t>
+  </si>
+  <si>
+    <t>Rewrite simpler before merging</t>
+  </si>
+  <si>
+    <t>R08</t>
+  </si>
+  <si>
+    <t>Live demo fails</t>
+  </si>
+  <si>
+    <t>Weak demo and presentation score</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>Pre-loaded data; two rehearsals</t>
+  </si>
+  <si>
+    <t>Any failure in rehearsal</t>
+  </si>
+  <si>
+    <t>Recorded video and screenshots</t>
+  </si>
+  <si>
+    <t>R09</t>
+  </si>
+  <si>
+    <t>Privacy: suppressed names or victim details exposed</t>
+  </si>
+  <si>
+    <t>Privacy breach; responsible-AI score hit</t>
+  </si>
+  <si>
+    <t>Keep redactions; never extract victim/witness details; flag suppression orders</t>
+  </si>
+  <si>
+    <t>Non-defendant personal name in CORE</t>
+  </si>
+  <si>
+    <t>Delete row; fix prompt</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>Snowflake–S3 integration (IAM trust) takes too long</t>
+  </si>
+  <si>
+    <t>Ingestion delayed; critical path slips</t>
+  </si>
+  <si>
+    <t>Follow setup steps; 1 h timebox</t>
+  </si>
+  <si>
+    <t>Not working at M1 + 30 min</t>
+  </si>
+  <si>
+    <t>Internal stage via Snowsight upload</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>Trial credits or compute limits reached</t>
+  </si>
+  <si>
+    <t>Pipeline stops mid-run</t>
+  </si>
+  <si>
+    <t>XS warehouse; 60 s auto-suspend; one LLM call per doc</t>
+  </si>
+  <si>
+    <t>Credit use &gt; 50%</t>
+  </si>
+  <si>
+    <t>Limit to gold set + 20 docs</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>Small sample makes charts look like legal conclusions</t>
+  </si>
+  <si>
+    <t>Misleading insights</t>
+  </si>
+  <si>
+    <t>Show n on every chart; frame as method demo</t>
+  </si>
+  <si>
+    <t>Chart group with n &lt; 5</t>
+  </si>
+  <si>
+    <t>Show counts, hide averages</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>Source website slow, or reuse terms unclear</t>
+  </si>
+  <si>
+    <t>Fewer documents to analyse</t>
+  </si>
+  <si>
+    <t>Download early in one batch; log source; attribute</t>
+  </si>
+  <si>
+    <t>Downloads unfinished at M2</t>
+  </si>
+  <si>
+    <t>Continue with minimum 20</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>Merge conflicts break main</t>
+  </si>
+  <si>
+    <t>Blocked merges; lost time</t>
+  </si>
+  <si>
+    <t>Small PRs; CI on every PR; one owner per folder</t>
+  </si>
+  <si>
+    <t>CI red on main &gt; 30 min</t>
+  </si>
+  <si>
+    <t>Revert last merge</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>A team member is unavailable</t>
+  </si>
+  <si>
+    <t>Tasks stall</t>
+  </si>
+  <si>
+    <t>Named backup per role</t>
+  </si>
+  <si>
+    <t>Absent &gt; 1 h at a milestone</t>
+  </si>
+  <si>
+    <t>Backup takes over the task</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Code deadline is 25 Sep 11:00 NZST; presentation later that day</t>
+  </si>
+  <si>
+    <t>If wrong: Timeline must shift</t>
+  </si>
+  <si>
+    <t>Confirm: Ask organisers (T03)</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>Snowflake and AWS trial accounts come with admin rights</t>
+  </si>
+  <si>
+    <t>If wrong: Setup blocked until access fixed</t>
+  </si>
+  <si>
+    <t>Confirm: Confirmed at M1</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>A Claude model is available on Bedrock in ap-southeast-2 or via cross-region inference</t>
+  </si>
+  <si>
+    <t>If wrong: Switch to Cortex fallback</t>
+  </si>
+  <si>
+    <t>Confirm: Test call (T05)</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>Published judgments are public and anonymised; non-commercial PoC reuse with attribution is acceptable</t>
+  </si>
+  <si>
+    <t>If wrong: Must change data source or restrict use</t>
+  </si>
+  <si>
+    <t>Confirm: Check source site terms</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>30–40 documents counts as a manageable sample</t>
+  </si>
+  <si>
+    <t>If wrong: Scope of data must change</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>Downloaded PDFs have a text layer, as all 7 samples do</t>
+  </si>
+  <si>
+    <t>If wrong: OCR needed; out of scope</t>
+  </si>
+  <si>
+    <t>Confirm: Font check on ingest</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>GitHub is allowed for code; all compute stays in AWS and Snowflake</t>
+  </si>
+  <si>
+    <t>If wrong: Code hosting must move</t>
+  </si>
+  <si>
+    <t>Confirm: Organisers require GitHub</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>Outputs are descriptive research, not legal advice</t>
+  </si>
+  <si>
+    <t>If wrong: Legal framing must change</t>
+  </si>
+  <si>
+    <t>Confirm: Disclaimer in app and deck</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>The court states its final figures explicitly in the text</t>
+  </si>
+  <si>
+    <t>If wrong: More values land in REVIEW</t>
+  </si>
+  <si>
+    <t>Confirm: Gold-set labelling (T13)</t>
+  </si>
+  <si>
+    <t>I01</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>2 of 7 samples are pre-trial rulings, not sentencing decisions</t>
+  </si>
+  <si>
+    <t>No sentence fields for those documents</t>
+  </si>
+  <si>
+    <t>Add document_type; fill sentence fields only for sentencing</t>
+  </si>
+  <si>
+    <t>I02</t>
+  </si>
+  <si>
+    <t>File names do not match citation numbers</t>
+  </si>
+  <si>
+    <t>Wrong joins if file name is the key</t>
+  </si>
+  <si>
+    <t>Neutral citation is the case key</t>
+  </si>
+  <si>
+    <t>I03</t>
+  </si>
+  <si>
+    <t>[2023] NZDC 2078 is dated 2 February 2024</t>
+  </si>
+  <si>
+    <t>Year filters disagree</t>
+  </si>
+  <si>
+    <t>Store citation year and judgment date separately</t>
+  </si>
+  <si>
+    <t>I04</t>
+  </si>
+  <si>
+    <t>Metallic Sweeping's final fine awaits a capacity-to-pay hearing</t>
+  </si>
+  <si>
+    <t>End fine is not final</t>
+  </si>
+  <si>
+    <t>Outcome = pending; set capacity_to_pay_flag</t>
+  </si>
+  <si>
+    <t>I05</t>
+  </si>
+  <si>
+    <t>Two regimes: HSEA 1992 and HSWA 2015, with different penalty scales</t>
+  </si>
+  <si>
+    <t>Misleading comparisons</t>
+  </si>
+  <si>
+    <t>Compare within one Act only</t>
+  </si>
+  <si>
+    <t>I06</t>
+  </si>
+  <si>
+    <t>Footnotes run into body text after extraction</t>
+  </si>
+  <si>
+    <t>Broken paragraphs and quotes</t>
+  </si>
+  <si>
+    <t>Cleaner step (T15)</t>
+  </si>
+  <si>
+    <t>D01</t>
+  </si>
+  <si>
+    <t>Dependency</t>
+  </si>
+  <si>
+    <t>Bedrock model access approved</t>
+  </si>
+  <si>
+    <t>If late: blocks T23, T24</t>
+  </si>
+  <si>
+    <t>Chase owner at each stand-up</t>
+  </si>
+  <si>
+    <t>T23, T24</t>
+  </si>
+  <si>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>Snowflake storage integration trusted by the AWS IAM role</t>
+  </si>
+  <si>
+    <t>If late: blocks T11</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>D03</t>
+  </si>
+  <si>
+    <t>Ministry of Justice decisions site reachable</t>
+  </si>
+  <si>
+    <t>If late: blocks T10</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>Gold set labelled before evaluation</t>
+  </si>
+  <si>
+    <t>If late: blocks T24, T38</t>
+  </si>
+  <si>
+    <t>PM, DA</t>
+  </si>
+  <si>
+    <t>T24, T38</t>
+  </si>
+  <si>
+    <t>D05</t>
+  </si>
+  <si>
+    <t>Schema frozen (T12, T21) before prompt, validation and app work</t>
+  </si>
+  <si>
+    <t>If late: blocks T22, T27, T31</t>
+  </si>
+  <si>
+    <t>AE, DS</t>
+  </si>
+  <si>
+    <t>T22, T27, T31</t>
+  </si>
+  <si>
+    <t>D06</t>
+  </si>
+  <si>
+    <t>GitHub access for all 6 members</t>
+  </si>
+  <si>
+    <t>If late: blocks All tasks</t>
+  </si>
+  <si>
+    <t>All tasks</t>
+  </si>
+  <si>
+    <t>D07</t>
+  </si>
+  <si>
+    <t>Organisers confirm submission format and slot</t>
+  </si>
+  <si>
+    <t>If late: blocks T44–T46</t>
+  </si>
+  <si>
+    <t>T44–T46</t>
+  </si>
+  <si>
+    <t>Legend: filter column B by type. Likelihood, Impact and Status are yellow input cells; Score and Rating calculate for risks only. Add new rows below the table and copy the Score/Rating formulas down.</t>
+  </si>
+  <si>
+    <t>Likelihood ↓ / Impact →</t>
+  </si>
+  <si>
+    <t>1 Negligible</t>
+  </si>
+  <si>
+    <t>2 Minor</t>
+  </si>
+  <si>
+    <t>3 Moderate</t>
+  </si>
+  <si>
+    <t>4 Major</t>
+  </si>
+  <si>
+    <t>5 Severe</t>
+  </si>
+  <si>
+    <t>5 Almost certain</t>
+  </si>
+  <si>
+    <t>4 Likely</t>
+  </si>
+  <si>
+    <t>3 Possible</t>
+  </si>
+  <si>
+    <t>2 Unlikely</t>
+  </si>
+  <si>
+    <t>1 Rare</t>
+  </si>
+  <si>
+    <t>Rating: Red = 15–25 (act now, report every stand-up) · Amber = 8–14 (mitigation owned, checked at milestones) · Green = 1–7 (monitor)</t>
+  </si>
+  <si>
+    <t>Scoring scales</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Rare (&lt; 10%)</t>
+  </si>
+  <si>
+    <t>Negligible: &lt; 15 min delay</t>
+  </si>
+  <si>
+    <t>Unlikely (10–30%)</t>
+  </si>
+  <si>
+    <t>Minor: &lt; 1 h delay, no deliverable affected</t>
+  </si>
+  <si>
+    <t>Possible (30–50%)</t>
+  </si>
+  <si>
+    <t>Moderate: 1–3 h delay, or a Should feature lost</t>
+  </si>
+  <si>
+    <t>Likely (50–80%)</t>
+  </si>
+  <si>
+    <t>Major: a Must feature degraded, or a judging criterion weakened</t>
+  </si>
+  <si>
+    <t>Almost certain (&gt; 80%, or already seen)</t>
+  </si>
+  <si>
+    <t>Severe: no working demo, or deadline missed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="173" formatCode="dd\ mmm\ yyyy"/>
+  </numFmts>
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -822,8 +1600,52 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF2E2A6B"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -857,8 +1679,74 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E2A6B"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFE8CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFFFE8CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE8F5"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE8CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDCE8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E7C1"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0A3"/>
+        <bgColor rgb="FFFFE8CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B6B6"/>
+        <bgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -922,12 +1810,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1006,12 +1910,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{14932F8F-D927-485B-AB53-AFE965104563}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC9E7C1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE0A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1028,23 +2009,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>577849</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>565150</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>2172462</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>305330</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>63855</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C1C8E83-CF11-4A7F-A9EF-411C789E73D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBFAFEAC-1DB1-44E8-8879-A78285F43D67}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1060,8 +2041,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9925050" y="761999"/>
-          <a:ext cx="4724400" cy="4541013"/>
+          <a:off x="0" y="6051550"/>
+          <a:ext cx="10306580" cy="6902805"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1071,6 +2052,515 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>55060</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>13207</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6E89624-7E18-4023-95B9-AA0C25F67BB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10856410" y="1854200"/>
+          <a:ext cx="9762547" cy="4057650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>6432550</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>109171</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{446D0D7C-34C5-4F49-9FD2-0F20FB8DDA26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11049000" y="6134100"/>
+          <a:ext cx="6184900" cy="5944821"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Summary"/>
+      <sheetName val="Tasks"/>
+      <sheetName val="Milestones"/>
+      <sheetName val="RAID Log"/>
+      <sheetName val="Risk Matrix"/>
+      <sheetName val="Risk Metrics"/>
+      <sheetName val="RACI"/>
+      <sheetName val="Test Cases"/>
+      <sheetName val="Deliverables"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F2">
+            <v>4</v>
+          </cell>
+          <cell r="G2">
+            <v>5</v>
+          </cell>
+          <cell r="N2" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F3">
+            <v>4</v>
+          </cell>
+          <cell r="G3">
+            <v>4</v>
+          </cell>
+          <cell r="N3" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F4">
+            <v>4</v>
+          </cell>
+          <cell r="G4">
+            <v>4</v>
+          </cell>
+          <cell r="N4" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F5">
+            <v>3</v>
+          </cell>
+          <cell r="G5">
+            <v>5</v>
+          </cell>
+          <cell r="N5" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F6">
+            <v>5</v>
+          </cell>
+          <cell r="G6">
+            <v>3</v>
+          </cell>
+          <cell r="N6" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F7">
+            <v>4</v>
+          </cell>
+          <cell r="G7">
+            <v>3</v>
+          </cell>
+          <cell r="N7" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F8">
+            <v>3</v>
+          </cell>
+          <cell r="G8">
+            <v>4</v>
+          </cell>
+          <cell r="N8" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F9">
+            <v>3</v>
+          </cell>
+          <cell r="G9">
+            <v>4</v>
+          </cell>
+          <cell r="N9" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F10">
+            <v>2</v>
+          </cell>
+          <cell r="G10">
+            <v>5</v>
+          </cell>
+          <cell r="N10" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F11">
+            <v>3</v>
+          </cell>
+          <cell r="G11">
+            <v>3</v>
+          </cell>
+          <cell r="N11" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F12">
+            <v>2</v>
+          </cell>
+          <cell r="G12">
+            <v>4</v>
+          </cell>
+          <cell r="N12" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F13">
+            <v>4</v>
+          </cell>
+          <cell r="G13">
+            <v>2</v>
+          </cell>
+          <cell r="N13" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F14">
+            <v>2</v>
+          </cell>
+          <cell r="G14">
+            <v>3</v>
+          </cell>
+          <cell r="N14" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F15">
+            <v>3</v>
+          </cell>
+          <cell r="G15">
+            <v>2</v>
+          </cell>
+          <cell r="N15" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Risk</v>
+          </cell>
+          <cell r="F16">
+            <v>2</v>
+          </cell>
+          <cell r="G16">
+            <v>3</v>
+          </cell>
+          <cell r="N16" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N17" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N18" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N19" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N20" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N21" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N22" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N23" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N24" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>Assumption</v>
+          </cell>
+          <cell r="N25" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>Issue</v>
+          </cell>
+          <cell r="N26" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>Issue</v>
+          </cell>
+          <cell r="N27" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>Issue</v>
+          </cell>
+          <cell r="N28" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>Issue</v>
+          </cell>
+          <cell r="N29" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>Issue</v>
+          </cell>
+          <cell r="N30" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>Issue</v>
+          </cell>
+          <cell r="N31" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N32" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N33" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N34" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N35" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N36" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N37" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>Dependency</v>
+          </cell>
+          <cell r="N38" t="str">
+            <v>Open</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1375,11 +2865,12 @@
   <cols>
     <col min="2" max="2" width="71" customWidth="1"/>
     <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="5" max="5" width="49.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1387,40 +2878,40 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K2" s="16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="K3" t="s">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="K4" t="s">
-        <v>184</v>
+        <v>175</v>
+      </c>
+      <c r="K4" s="34" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="K5" t="s">
-        <v>185</v>
+        <v>174</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -1428,7 +2919,7 @@
         <v>161</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -1442,8 +2933,9 @@
         <v>21</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>195</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
@@ -1456,8 +2948,9 @@
         <v>24</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>197</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
@@ -1470,10 +2963,11 @@
         <v>22</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>12</v>
       </c>
@@ -1484,7 +2978,10 @@
         <v>25</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>198</v>
+        <v>200</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -1498,8 +2995,9 @@
         <v>26</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>198</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
@@ -1510,8 +3008,9 @@
         <v>23</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>194</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
@@ -1524,58 +3023,59 @@
         <v>28</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>199</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="E16" s="7"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C21" s="15"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C22" s="15"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C23" s="15"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C24" s="15"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="25" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C26" s="15"/>
     </row>
@@ -1612,34 +3112,34 @@
     <row r="35" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2993,15 +4493,159 @@
     <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA72A998-9D73-4F3B-A55F-A4F70ED3DBFB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="52.453125" customWidth="1"/>
+    <col min="2" max="2" width="39.08984375" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="36">
+        <v>46288</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3228,12 +4872,2043 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>193</v>
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}">
+  <dimension ref="A1:T40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.08984375" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" customWidth="1"/>
+    <col min="6" max="6" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" customWidth="1"/>
+    <col min="12" max="13" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.36328125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="21.54296875" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="26" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="J1" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="K1" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="L1" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="R1" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="S1" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="T1" s="40" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="42">
+        <v>4</v>
+      </c>
+      <c r="G2" s="42">
+        <v>5</v>
+      </c>
+      <c r="H2" s="37">
+        <f>IF(AND(B2="Risk",ISNUMBER(F2),ISNUMBER(G2)),F2*G2,"")</f>
+        <v>20</v>
+      </c>
+      <c r="I2" s="37" t="str">
+        <f t="shared" ref="I2:I38" si="0">IF(H2="","",IF(H2&gt;=15,"Red",IF(H2&gt;=8,"Amber","Green")))</f>
+        <v>Red</v>
+      </c>
+      <c r="J2" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="K2" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L2" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M2" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R2" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="S2" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="T2" s="41"/>
+    </row>
+    <row r="3" spans="1:20" ht="50" x14ac:dyDescent="0.35">
+      <c r="A3" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="42">
+        <v>4</v>
+      </c>
+      <c r="G3" s="42">
+        <v>4</v>
+      </c>
+      <c r="H3" s="37">
+        <f t="shared" ref="H3:H38" si="1">IF(AND(B3="Risk",ISNUMBER(F3),ISNUMBER(G3)),F3*G3,"")</f>
+        <v>16</v>
+      </c>
+      <c r="I3" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Red</v>
+      </c>
+      <c r="J3" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="K3" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L3" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M3" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R3" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="S3" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="T3" s="41"/>
+    </row>
+    <row r="4" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A4" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="42">
+        <v>4</v>
+      </c>
+      <c r="G4" s="42">
+        <v>4</v>
+      </c>
+      <c r="H4" s="37">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="I4" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Red</v>
+      </c>
+      <c r="J4" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="K4" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L4" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M4" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R4" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="S4" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="T4" s="41"/>
+    </row>
+    <row r="5" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" s="42">
+        <v>3</v>
+      </c>
+      <c r="G5" s="42">
+        <v>5</v>
+      </c>
+      <c r="H5" s="37">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I5" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Red</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="K5" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L5" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M5" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R5" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="S5" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="T5" s="41"/>
+    </row>
+    <row r="6" spans="1:20" ht="50" x14ac:dyDescent="0.35">
+      <c r="A6" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="F6" s="42">
+        <v>5</v>
+      </c>
+      <c r="G6" s="42">
+        <v>3</v>
+      </c>
+      <c r="H6" s="37">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="I6" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Red</v>
+      </c>
+      <c r="J6" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L6" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M6" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R6" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="S6" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F7" s="42">
+        <v>4</v>
+      </c>
+      <c r="G7" s="42">
+        <v>3</v>
+      </c>
+      <c r="H7" s="37">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="I7" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="K7" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L7" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M7" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R7" s="41" t="s">
+        <v>279</v>
+      </c>
+      <c r="S7" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="T7" s="41"/>
+    </row>
+    <row r="8" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A8" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>283</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F8" s="42">
+        <v>3</v>
+      </c>
+      <c r="G8" s="42">
+        <v>4</v>
+      </c>
+      <c r="H8" s="37">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="I8" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L8" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M8" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R8" s="41" t="s">
+        <v>285</v>
+      </c>
+      <c r="S8" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="T8" s="41"/>
+    </row>
+    <row r="9" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A9" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="F9" s="42">
+        <v>3</v>
+      </c>
+      <c r="G9" s="42">
+        <v>4</v>
+      </c>
+      <c r="H9" s="37">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="I9" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>291</v>
+      </c>
+      <c r="K9" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L9" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M9" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R9" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="S9" s="41" t="s">
+        <v>293</v>
+      </c>
+      <c r="T9" s="41"/>
+    </row>
+    <row r="10" spans="1:20" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="41" t="s">
+        <v>294</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F10" s="42">
+        <v>2</v>
+      </c>
+      <c r="G10" s="42">
+        <v>5</v>
+      </c>
+      <c r="H10" s="37">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I10" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J10" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M10" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R10" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="S10" s="41" t="s">
+        <v>299</v>
+      </c>
+      <c r="T10" s="41"/>
+    </row>
+    <row r="11" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A11" s="41" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F11" s="42">
+        <v>3</v>
+      </c>
+      <c r="G11" s="42">
+        <v>3</v>
+      </c>
+      <c r="H11" s="37">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="I11" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="K11" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L11" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M11" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R11" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="S11" s="41" t="s">
+        <v>305</v>
+      </c>
+      <c r="T11" s="41"/>
+    </row>
+    <row r="12" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="41" t="s">
+        <v>306</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F12" s="42">
+        <v>2</v>
+      </c>
+      <c r="G12" s="42">
+        <v>4</v>
+      </c>
+      <c r="H12" s="37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I12" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J12" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M12" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R12" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="S12" s="41" t="s">
+        <v>311</v>
+      </c>
+      <c r="T12" s="41"/>
+    </row>
+    <row r="13" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="41" t="s">
+        <v>312</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="F13" s="42">
+        <v>4</v>
+      </c>
+      <c r="G13" s="42">
+        <v>2</v>
+      </c>
+      <c r="H13" s="37">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I13" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Amber</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="K13" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L13" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M13" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R13" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="S13" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="T13" s="41"/>
+    </row>
+    <row r="14" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>319</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" s="42">
+        <v>2</v>
+      </c>
+      <c r="G14" s="42">
+        <v>3</v>
+      </c>
+      <c r="H14" s="37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I14" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Green</v>
+      </c>
+      <c r="J14" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="K14" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L14" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M14" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R14" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="S14" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="T14" s="41"/>
+    </row>
+    <row r="15" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="42">
+        <v>3</v>
+      </c>
+      <c r="G15" s="42">
+        <v>2</v>
+      </c>
+      <c r="H15" s="37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I15" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Green</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="K15" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M15" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R15" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="S15" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="T15" s="41"/>
+    </row>
+    <row r="16" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A16" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F16" s="42">
+        <v>2</v>
+      </c>
+      <c r="G16" s="42">
+        <v>3</v>
+      </c>
+      <c r="H16" s="37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I16" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Green</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>333</v>
+      </c>
+      <c r="K16" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L16" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M16" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R16" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="S16" s="41" t="s">
+        <v>335</v>
+      </c>
+      <c r="T16" s="41"/>
+    </row>
+    <row r="17" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A17" s="41" t="s">
+        <v>336</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I17" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="K17" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L17" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M17" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+    </row>
+    <row r="18" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A18" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I18" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L18" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M18" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+    </row>
+    <row r="19" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="41" t="s">
+        <v>345</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I19" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J19" s="41" t="s">
+        <v>348</v>
+      </c>
+      <c r="K19" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L19" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M19" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+    </row>
+    <row r="20" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="41" t="s">
+        <v>349</v>
+      </c>
+      <c r="B20" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>351</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I20" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="41" t="s">
+        <v>352</v>
+      </c>
+      <c r="K20" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M20" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+    </row>
+    <row r="21" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A21" s="41" t="s">
+        <v>353</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>355</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I21" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J21" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="K21" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L21" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M21" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
+    </row>
+    <row r="22" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A22" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="B22" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>357</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>358</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I22" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>359</v>
+      </c>
+      <c r="K22" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L22" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M22" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+    </row>
+    <row r="23" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>361</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>362</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I23" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J23" s="41" t="s">
+        <v>363</v>
+      </c>
+      <c r="K23" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L23" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M23" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="41"/>
+    </row>
+    <row r="24" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A24" s="41" t="s">
+        <v>364</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>365</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I24" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J24" s="41" t="s">
+        <v>367</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M24" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="41"/>
+    </row>
+    <row r="25" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A25" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="B25" s="45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>370</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I25" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J25" s="41" t="s">
+        <v>371</v>
+      </c>
+      <c r="K25" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L25" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M25" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R25" s="41"/>
+      <c r="S25" s="41"/>
+      <c r="T25" s="41"/>
+    </row>
+    <row r="26" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I26" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J26" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M26" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R26" s="41"/>
+      <c r="S26" s="41"/>
+      <c r="T26" s="41"/>
+    </row>
+    <row r="27" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A27" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>378</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I27" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J27" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L27" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M27" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+    </row>
+    <row r="28" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I28" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J28" s="41" t="s">
+        <v>384</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L28" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M28" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+    </row>
+    <row r="29" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>386</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>387</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>250</v>
+      </c>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I29" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J29" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L29" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M29" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+    </row>
+    <row r="30" spans="1:20" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="B30" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>390</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>391</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I30" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J30" s="41" t="s">
+        <v>392</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L30" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M30" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+    </row>
+    <row r="31" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A31" s="41" t="s">
+        <v>393</v>
+      </c>
+      <c r="B31" s="46" t="s">
+        <v>373</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" s="41" t="s">
+        <v>395</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I31" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J31" s="41" t="s">
+        <v>396</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L31" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M31" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R31" s="41"/>
+      <c r="S31" s="41"/>
+      <c r="T31" s="41"/>
+    </row>
+    <row r="32" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A32" s="41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>399</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I32" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J32" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L32" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M32" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R32" s="41"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A33" s="41" t="s">
+        <v>403</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>404</v>
+      </c>
+      <c r="D33" s="41" t="s">
+        <v>405</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I33" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J33" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K33" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L33" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M33" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R33" s="41"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="41" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A34" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>409</v>
+      </c>
+      <c r="E34" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I34" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J34" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K34" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L34" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M34" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R34" s="41"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A35" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>412</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>413</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I35" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J35" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L35" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M35" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R35" s="41"/>
+      <c r="S35" s="41"/>
+      <c r="T35" s="41" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A36" s="41" t="s">
+        <v>416</v>
+      </c>
+      <c r="B36" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>417</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>418</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>419</v>
+      </c>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I36" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J36" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K36" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L36" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M36" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R36" s="41"/>
+      <c r="S36" s="41"/>
+      <c r="T36" s="41" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A37" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="B37" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>422</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>423</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I37" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J37" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L37" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M37" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R37" s="41"/>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="25" x14ac:dyDescent="0.35">
+      <c r="A38" s="41" t="s">
+        <v>425</v>
+      </c>
+      <c r="B38" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>426</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>427</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I38" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J38" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K38" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="L38" s="43">
+        <v>46289</v>
+      </c>
+      <c r="M38" s="43">
+        <v>46290</v>
+      </c>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="41" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A40" s="39" t="s">
+        <v>429</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="38"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M38" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}"/>
+  <conditionalFormatting sqref="I2:I38">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Red"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Amber"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Green"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28DF5487-4AEC-472D-8D8B-F19F15732F89}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.26953125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="48" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>431</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="F1" s="49" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="50" t="s">
+        <v>436</v>
+      </c>
+      <c r="B2" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="53">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="E2" s="53">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="53">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="50" t="s">
+        <v>437</v>
+      </c>
+      <c r="B3" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="53">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="53">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="50" t="s">
+        <v>438</v>
+      </c>
+      <c r="B4" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="53">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="50" t="s">
+        <v>439</v>
+      </c>
+      <c r="B5" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>2</v>
+      </c>
+      <c r="E5" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="52">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="50" t="s">
+        <v>440</v>
+      </c>
+      <c r="B6" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="51">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="54" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="55" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>443</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="37">
+        <v>1</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>445</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="37">
+        <v>2</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="37">
+        <v>3</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>449</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="37">
+        <v>4</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>451</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="37">
+        <v>5</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>453</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Datathon Project.xlsx
+++ b/docs/Datathon Project.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Master of Data Science - UoA\Datathon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5081E1C3-6D80-4841-B8C7-9DD9D787138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F45C70-46F2-4ED9-BA24-C0D066ABD238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Overview" sheetId="2" r:id="rId1"/>
     <sheet name="MVP Requirements + Design" sheetId="1" r:id="rId2"/>
-    <sheet name="Project Plan , Sprint Meetings" sheetId="3" r:id="rId3"/>
-    <sheet name="Team Progress View- JIRA SCRUM" sheetId="11" r:id="rId4"/>
-    <sheet name="RAID Logs " sheetId="9" r:id="rId5"/>
-    <sheet name="Data Model" sheetId="7" r:id="rId6"/>
-    <sheet name="Tasks" sheetId="6" state="hidden" r:id="rId7"/>
-    <sheet name="Team votes &amp; Misc Info" sheetId="5" r:id="rId8"/>
+    <sheet name="Project Plan &amp; Sprint Meetings" sheetId="3" r:id="rId3"/>
+    <sheet name="RAID Logs " sheetId="9" r:id="rId4"/>
+    <sheet name="Team Progress View- JIRA SCRUM" sheetId="11" r:id="rId5"/>
+    <sheet name="JIRA Task Breakdown" sheetId="12" r:id="rId6"/>
+    <sheet name="Data Model" sheetId="7" r:id="rId7"/>
+    <sheet name="Tasks" sheetId="6" state="hidden" r:id="rId8"/>
+    <sheet name="Team votes &amp; Misc Info" sheetId="5" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RAID Logs '!$A$1:$M$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RAID Logs '!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="502">
   <si>
     <t>court</t>
   </si>
@@ -599,9 +600,6 @@
     <t>Test full process- WORKING DEMO</t>
   </si>
   <si>
-    <t>building visualizations and insights</t>
-  </si>
-  <si>
     <t>Build UI</t>
   </si>
   <si>
@@ -725,18 +723,9 @@
     <t>R05</t>
   </si>
   <si>
-    <t>Document variety breaks the rules (old layouts, pre-trial rulings, several defendants)</t>
-  </si>
-  <si>
     <t>Missing or wrong fields for some documents</t>
   </si>
   <si>
-    <t>AE</t>
-  </si>
-  <si>
-    <t>Classify type first; multi-defendant schema; test both layouts</t>
-  </si>
-  <si>
     <t>Rule accuracy &lt; 95% on gold set</t>
   </si>
   <si>
@@ -761,6 +750,9 @@
     <t>Rewrite simpler before merging</t>
   </si>
   <si>
+    <t>R08</t>
+  </si>
+  <si>
     <t>Any failure in rehearsal</t>
   </si>
   <si>
@@ -815,9 +807,6 @@
     <t>Tasks stall</t>
   </si>
   <si>
-    <t>Named backup per role</t>
-  </si>
-  <si>
     <t>Absent &gt; 1 h at a milestone</t>
   </si>
   <si>
@@ -836,9 +825,6 @@
     <t/>
   </si>
   <si>
-    <t>Confirm: Ask organisers (T03)</t>
-  </si>
-  <si>
     <t>A02</t>
   </si>
   <si>
@@ -908,9 +894,6 @@
     <t>T11</t>
   </si>
   <si>
-    <t>D03</t>
-  </si>
-  <si>
     <t>T10</t>
   </si>
   <si>
@@ -933,9 +916,6 @@
   </si>
   <si>
     <t>All tasks</t>
-  </si>
-  <si>
-    <t>Organisers confirm submission format and slot</t>
   </si>
   <si>
     <t>T44–T46</t>
@@ -1512,15 +1492,303 @@
 (Start and End Timelines)</t>
   </si>
   <si>
-    <t>TIMELINE View</t>
-  </si>
-  <si>
     <t>Sprint Completion - Agile Custom Reports</t>
+  </si>
+  <si>
+    <t>Epic Key</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Item Key</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>SCRUM-36</t>
+  </si>
+  <si>
+    <t>Plan and set up (kick-off, requirements, GitHub, cloud access)</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>SCRUM-1</t>
+  </si>
+  <si>
+    <t>Project Planning document (BRD)</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>SCRUM-15</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>PM: Project Plan Creation</t>
+  </si>
+  <si>
+    <t>SCRUM-26</t>
+  </si>
+  <si>
+    <t>Set up AWS Bedrock Account</t>
+  </si>
+  <si>
+    <t>Simon Lin</t>
+  </si>
+  <si>
+    <t>SCRUM-17</t>
+  </si>
+  <si>
+    <t>PM: Document requirements, RAID logs, track task and project progress</t>
+  </si>
+  <si>
+    <t>SCRUM-16</t>
+  </si>
+  <si>
+    <t>Fix issues of Devopt</t>
+  </si>
+  <si>
+    <t>Engleang Sam</t>
+  </si>
+  <si>
+    <t>SCRUM-30</t>
+  </si>
+  <si>
+    <t>Submit support ticket AWS</t>
+  </si>
+  <si>
+    <t>SCRUM-3</t>
+  </si>
+  <si>
+    <t>Dbt implementation/configuration</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Cancelled</t>
+  </si>
+  <si>
+    <t>SCRUM-14</t>
+  </si>
+  <si>
+    <t>Develop and deploy project</t>
+  </si>
+  <si>
+    <t>SCRUM-27</t>
+  </si>
+  <si>
+    <t>Code Streamlit UI</t>
+  </si>
+  <si>
+    <t>Highest</t>
+  </si>
+  <si>
+    <t>SCRUM-19</t>
+  </si>
+  <si>
+    <t>Database/App: ingestion pipeline</t>
+  </si>
+  <si>
+    <t>Gregory Hinds</t>
+  </si>
+  <si>
+    <t>SCRUM-6</t>
+  </si>
+  <si>
+    <t>Database: build ingestion code</t>
+  </si>
+  <si>
+    <t>SCRUM-11</t>
+  </si>
+  <si>
+    <t>Database: finalise data format</t>
+  </si>
+  <si>
+    <t>Radiya Binte Reza</t>
+  </si>
+  <si>
+    <t>SCRUM-12</t>
+  </si>
+  <si>
+    <t>Database: amend schema to align with finalised format</t>
+  </si>
+  <si>
+    <t>SCRUM-21</t>
+  </si>
+  <si>
+    <t>Snowflake permissions implementation</t>
+  </si>
+  <si>
+    <t>SCRUM-29</t>
+  </si>
+  <si>
+    <t>Push Streamlit UI on GitHub</t>
+  </si>
+  <si>
+    <t>SCRUM-8</t>
+  </si>
+  <si>
+    <t>Database: ingest test data</t>
+  </si>
+  <si>
+    <t>SCRUM-13</t>
+  </si>
+  <si>
+    <t>Database: create/build security roles</t>
+  </si>
+  <si>
+    <t>SCRUM-18</t>
+  </si>
+  <si>
+    <t>Database: make DBT project</t>
+  </si>
+  <si>
+    <t>SCRUM-20</t>
+  </si>
+  <si>
+    <t>Fix issues of Snowflake schema</t>
+  </si>
+  <si>
+    <t>SCRUM-23</t>
+  </si>
+  <si>
+    <t>Data collection: input</t>
+  </si>
+  <si>
+    <t>SCRUM-28</t>
+  </si>
+  <si>
+    <t>Run test cases on Streamlit app</t>
+  </si>
+  <si>
+    <t>SCRUM-33</t>
+  </si>
+  <si>
+    <t>Enable duplicate detection</t>
+  </si>
+  <si>
+    <t>SCRUM-35</t>
+  </si>
+  <si>
+    <t>Snowflake: create/update permissions for roles</t>
+  </si>
+  <si>
+    <t>SCRUM-38</t>
+  </si>
+  <si>
+    <t>Create roles: Snowflake database and schema</t>
+  </si>
+  <si>
+    <t>SCRUM-5</t>
+  </si>
+  <si>
+    <t>Database: define enumerations</t>
+  </si>
+  <si>
+    <t>SCRUM-7</t>
+  </si>
+  <si>
+    <t>Database: build test framework</t>
+  </si>
+  <si>
+    <t>SCRUM-37</t>
+  </si>
+  <si>
+    <t>Insights, working demo and presentation</t>
+  </si>
+  <si>
+    <t>SCRUM-9</t>
+  </si>
+  <si>
+    <t>Dashboard: write query code</t>
+  </si>
+  <si>
+    <t>SCRUM-10</t>
+  </si>
+  <si>
+    <t>Dashboard: build visualisations</t>
+  </si>
+  <si>
+    <t>SCRUM-22</t>
+  </si>
+  <si>
+    <t>Make presentation deck</t>
+  </si>
+  <si>
+    <t>SCRUM-34</t>
+  </si>
+  <si>
+    <t>Check human-review flagging works correctly</t>
+  </si>
+  <si>
+    <t>SCRUM-31</t>
+  </si>
+  <si>
+    <t>Prepare presentation</t>
+  </si>
+  <si>
+    <t>SCRUM-32</t>
+  </si>
+  <si>
+    <t>Agree on data format/structure and Work with mock data initially while the first part of implementation is built</t>
+  </si>
+  <si>
+    <t>EPIC- TIMELINE View</t>
+  </si>
+  <si>
+    <t>EPIC-1 : Develop and deploy project</t>
+  </si>
+  <si>
+    <t>EPIC-2 : Plan and set up (kick-off, requirements, GitHub, cloud access)</t>
+  </si>
+  <si>
+    <t>EPIC-3 :Insights, working demo and presentation</t>
   </si>
   <si>
     <t>TEAM JIRA SCRUM BOARD 
 (FINAL-SPRINT VIEW)
-(story points estimated; priority updated; epic, story and tasks updated &amp; closed; sprint completed, etc.)</t>
+(story points estimated (1/2/3); priority updated; epic, story and tasks updated &amp; closed; sprint completed, etc.)</t>
+  </si>
+  <si>
+    <t>Build visualizations and insights</t>
+  </si>
+  <si>
+    <t>Agent now has access to delete data and change whatever it wants in all the schemas it can access</t>
+  </si>
+  <si>
+    <t>Implement roles and permissions and review database and schema to ensure impact is minimized in transactions</t>
+  </si>
+  <si>
+    <t>Review team availability for the next two days and assign Named backup per role as needed</t>
+  </si>
+  <si>
+    <t>communicate with team regularly to check on the submission timelines or any updates</t>
+  </si>
+  <si>
+    <t>Implementations by other members may impact or override anyone else' work</t>
+  </si>
+  <si>
+    <t>communicate with team regularly when working on similar functionalities, do peer implementation reviews, share updates in regular scrum calss</t>
   </si>
 </sst>
 </file>
@@ -2080,7 +2348,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2097,6 +2365,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2141,9 +2412,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2380,6 +2648,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2422,6 +2696,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2430,7 +2717,42 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{14932F8F-D927-485B-AB53-AFE965104563}"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="59">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2456,6 +2778,27 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC9E7C1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE0A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4B6B6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2788,14 +3131,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2815,55 +3150,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>621686</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1562100</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>12662</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A36FC43-7427-419C-AD28-12466BF883D2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9022736" y="7099300"/>
-          <a:ext cx="9316064" cy="5226012"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2912,7 +3198,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3137,20 +3423,20 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>514350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2139950</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>2465</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>97715</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3173,7 +3459,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="603250" y="8102600"/>
+          <a:off x="603250" y="8013700"/>
           <a:ext cx="6616700" cy="2885365"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3186,15 +3472,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>69851</xdr:rowOff>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>508001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>21078</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>554478</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>69851</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3217,7 +3503,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9569450" y="8108951"/>
+          <a:off x="9493250" y="8007351"/>
           <a:ext cx="7317228" cy="3232150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3230,15 +3516,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>31749</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>87882</xdr:rowOff>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>145006</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3261,8 +3547,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11423650" y="1263650"/>
-          <a:ext cx="6356350" cy="3745482"/>
+          <a:off x="10960100" y="1085849"/>
+          <a:ext cx="7067550" cy="4164557"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3274,15 +3560,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>546101</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1022349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>232030</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>7484</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3305,8 +3591,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="546101" y="1079500"/>
-          <a:ext cx="8417179" cy="4419600"/>
+          <a:off x="0" y="1022349"/>
+          <a:ext cx="9544050" cy="5011285"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3317,16 +3603,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>158001</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>44449</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>450101</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>88899</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3349,8 +3635,189 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20027900" y="1193800"/>
+          <a:off x="18478500" y="1054100"/>
           <a:ext cx="10419601" cy="5060949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>3054964</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76162</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5957CC2F-7E65-4AD3-86FD-DFEDBA9BC0A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30346650" y="1060450"/>
+          <a:ext cx="9316064" cy="5226012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>31751</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>383019</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41CAF88-4913-4A08-B541-8F7556944E85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19051" y="8147051"/>
+          <a:ext cx="11146268" cy="5359399"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>387351</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>69851</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>543893</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>146051</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF8640D-3F36-4136-9891-D7B62F9223F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11715751" y="8185151"/>
+          <a:ext cx="10576892" cy="1917700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>133673</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C72B9F4-1400-4495-85CC-3F994429960F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11595100" y="11474450"/>
+          <a:ext cx="11112500" cy="1746573"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4180,7 +4647,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="54.5" customHeight="1">
       <c r="A1" s="111" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B1" s="112"/>
       <c r="C1" s="112"/>
@@ -4189,7 +4656,7 @@
       <c r="F1" s="112"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="12" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4202,7 +4669,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="17" t="s">
         <v>157</v>
       </c>
     </row>
@@ -4215,7 +4682,7 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="16" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4224,11 +4691,11 @@
         <v>148</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="15" t="s">
         <v>160</v>
       </c>
     </row>
@@ -4250,12 +4717,12 @@
     </row>
     <row r="10" spans="1:11" ht="62.5" customHeight="1">
       <c r="A10" s="81" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B10" s="81"/>
       <c r="C10" s="81"/>
       <c r="D10" s="81" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E10" s="81"/>
       <c r="F10" s="81"/>
@@ -4271,13 +4738,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="83" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E11" s="83" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="F11" s="83" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="43.5">
@@ -4291,13 +4758,13 @@
         <v>15</v>
       </c>
       <c r="D12" s="79" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E12" s="80" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="72.5">
@@ -4305,19 +4772,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C13" s="62" t="s">
         <v>13</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E13" s="64" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="F13" s="65" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="43.5">
@@ -4325,7 +4792,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C14" s="62" t="s">
         <v>16</v>
@@ -4337,7 +4804,7 @@
         <v>170</v>
       </c>
       <c r="F14" s="64" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="29">
@@ -4354,10 +4821,10 @@
         <v>168</v>
       </c>
       <c r="E15" s="63" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4375,7 +4842,7 @@
       </c>
       <c r="E16" s="63"/>
       <c r="F16" s="66" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4389,60 +4856,55 @@
         <v>19</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="F17" s="66" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="49" customHeight="1">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="46" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B20" s="47"/>
-      <c r="D20" s="72" t="s">
-        <v>390</v>
-      </c>
-      <c r="E20" s="73"/>
-      <c r="F20" s="74"/>
     </row>
     <row r="21" spans="1:6" ht="22.5" customHeight="1">
       <c r="A21" s="83" t="s">
         <v>18</v>
       </c>
       <c r="B21" s="83" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="29">
-      <c r="A22" s="115" t="s">
-        <v>368</v>
+      <c r="A22" s="117" t="s">
+        <v>361</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="C22" s="10"/>
+        <v>334</v>
+      </c>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="114" t="s">
-        <v>339</v>
+      <c r="A23" s="116" t="s">
+        <v>332</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>340</v>
-      </c>
-      <c r="C23" s="10"/>
+        <v>333</v>
+      </c>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="114" t="s">
+      <c r="A24" s="116" t="s">
         <v>151</v>
       </c>
       <c r="B24" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="53" t="s">
@@ -4451,7 +4913,7 @@
       <c r="B25" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="53" t="s">
@@ -4460,7 +4922,7 @@
       <c r="B26" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="53" t="s">
@@ -4469,63 +4931,62 @@
       <c r="B27" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="53" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B28" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="C28" s="10"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="C29" s="10"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="C30" s="10"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="116" t="s">
+      <c r="A31" s="118" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="116" t="s">
+      <c r="B31" s="118" t="s">
         <v>143</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="B32" s="117" t="s">
+      <c r="A32" s="119" t="s">
+        <v>384</v>
+      </c>
+      <c r="B32" s="119" t="s">
         <v>144</v>
       </c>
-      <c r="C32" s="10"/>
+      <c r="C32" s="11"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="117" t="s">
+      <c r="A33" s="119" t="s">
         <v>145</v>
       </c>
-      <c r="B33" s="117" t="s">
+      <c r="B33" s="119" t="s">
         <v>146</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="117" t="s">
-        <v>393</v>
-      </c>
-      <c r="B34" s="117" t="s">
-        <v>394</v>
+      <c r="A34" s="119" t="s">
+        <v>386</v>
+      </c>
+      <c r="B34" s="119" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="14.5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:F20"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="A1:F1"/>
@@ -4534,7 +4995,6 @@
     <hyperlink ref="B28" r:id="rId1" display="https://drive.google.com/drive/u/6/folders/1Bw7lSWdOExDDpihTWeozwxtdz5_t1KNN" xr:uid="{CF98AABD-B6DF-493B-8DB4-3101713010F5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4616,26 +5076,26 @@
   <sheetData>
     <row r="1" spans="1:9" ht="43" customHeight="1">
       <c r="A1" s="49" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B1" s="50" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>361</v>
-      </c>
-      <c r="D1" s="26"/>
+        <v>354</v>
+      </c>
+      <c r="D1" s="27"/>
       <c r="F1" s="52" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G1" s="52" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="52" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="I1" s="52" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="43.5">
@@ -4643,23 +5103,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C2" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="27"/>
+      <c r="D2" s="28"/>
       <c r="F2" s="58" t="s">
         <v>30</v>
       </c>
       <c r="G2" s="59" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="H2" s="58" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="I2" s="58" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="29">
@@ -4667,23 +5127,23 @@
         <v>2</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C3" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="27"/>
+      <c r="D3" s="28"/>
       <c r="F3" s="58" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="H3" s="58" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="I3" s="58" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="29">
@@ -4691,23 +5151,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C4" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="27"/>
+      <c r="D4" s="28"/>
       <c r="F4" s="58" t="s">
         <v>31</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="H4" s="58" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I4" s="58" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29">
@@ -4715,23 +5175,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="C5" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="27"/>
+      <c r="D5" s="28"/>
       <c r="F5" s="58" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -4739,23 +5199,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C6" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="28"/>
       <c r="F6" s="58" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="29">
@@ -4768,18 +5228,18 @@
       <c r="C7" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="28"/>
       <c r="F7" s="58" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="59" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="87">
@@ -4790,23 +5250,23 @@
         <v>37</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>360</v>
-      </c>
-      <c r="D8" s="27"/>
+        <v>353</v>
+      </c>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" spans="1:9" ht="72.5">
       <c r="A9" s="53">
         <v>8</v>
       </c>
       <c r="B9" s="54" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C9" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="28"/>
       <c r="F9" s="108" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="G9" s="109"/>
       <c r="H9" s="109"/>
@@ -4817,22 +5277,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C10" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="28"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="53">
         <v>10</v>
       </c>
       <c r="B11" s="54" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4840,15 +5300,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C12" s="53" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.5" customHeight="1">
       <c r="B14" s="29" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C14" s="29"/>
     </row>
@@ -4897,10 +5357,10 @@
       <c r="B27" s="3"/>
     </row>
     <row r="28" spans="2:3" ht="72.5" customHeight="1">
-      <c r="B28" s="28" t="s">
-        <v>407</v>
-      </c>
-      <c r="C28" s="28"/>
+      <c r="B28" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" s="3"/>
@@ -4962,7 +5422,7 @@
   <sheetData>
     <row r="1" spans="2:10" ht="30.5" customHeight="1">
       <c r="B1" s="45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C1" s="52" t="s">
         <v>169</v>
@@ -4970,110 +5430,110 @@
       <c r="D1" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="26"/>
+      <c r="E1" s="27"/>
     </row>
     <row r="2" spans="2:10" ht="29" customHeight="1">
       <c r="B2" s="57" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>305</v>
-      </c>
-      <c r="D2" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="118" t="s">
-        <v>389</v>
-      </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="120"/>
+      <c r="G2" s="120" t="s">
+        <v>382</v>
+      </c>
+      <c r="H2" s="121"/>
+      <c r="I2" s="121"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="2:10" ht="14.5" customHeight="1">
       <c r="B3" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C3" s="68">
         <v>46288</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E3" s="39"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="125"/>
     </row>
     <row r="4" spans="2:10" ht="14.5" customHeight="1">
       <c r="B4" s="57" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E4" s="39"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="123"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="125"/>
     </row>
     <row r="5" spans="2:10" ht="14.5" customHeight="1">
       <c r="B5" s="57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E5" s="39"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="2:10" ht="29">
       <c r="B6" s="57" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E6" s="39"/>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E7" s="39"/>
     </row>
     <row r="8" spans="2:10" ht="14.5" customHeight="1">
       <c r="B8" s="57" t="s">
-        <v>172</v>
+        <v>495</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="30" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
@@ -5084,9 +5544,9 @@
         <v>171</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>330</v>
-      </c>
-      <c r="D9" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E9" s="39"/>
@@ -5097,12 +5557,12 @@
     </row>
     <row r="10" spans="2:10" ht="14.5" customHeight="1">
       <c r="B10" s="57" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>332</v>
-      </c>
-      <c r="D10" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E10" s="39"/>
@@ -5126,7 +5586,7 @@
     <row r="13" spans="2:10" ht="14.5" customHeight="1"/>
     <row r="14" spans="2:10" ht="14.5" customHeight="1">
       <c r="G14" s="29" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="H14" s="29"/>
       <c r="I14" s="29"/>
@@ -5153,7 +5613,7 @@
     <row r="18" spans="7:10" ht="14.5" customHeight="1"/>
     <row r="19" spans="7:10" ht="14.5" customHeight="1">
       <c r="G19" s="29" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H19" s="29"/>
       <c r="I19" s="29"/>
@@ -5178,42 +5638,42 @@
       <c r="J22" s="29"/>
     </row>
     <row r="25" spans="7:10" ht="14.5" customHeight="1">
-      <c r="G25" s="113" t="s">
-        <v>366</v>
-      </c>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
+      <c r="G25" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
     </row>
     <row r="26" spans="7:10">
-      <c r="G26" s="113"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="113"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="115"/>
     </row>
     <row r="27" spans="7:10">
-      <c r="G27" s="113"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="113"/>
-      <c r="J27" s="113"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
     </row>
     <row r="28" spans="7:10" ht="14.5" customHeight="1">
-      <c r="G28" s="113"/>
-      <c r="H28" s="113"/>
-      <c r="I28" s="113"/>
-      <c r="J28" s="113"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="115"/>
     </row>
     <row r="29" spans="7:10">
-      <c r="G29" s="113"/>
-      <c r="H29" s="113"/>
-      <c r="I29" s="113"/>
-      <c r="J29" s="113"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
     </row>
     <row r="30" spans="7:10">
-      <c r="G30" s="113"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="113"/>
-      <c r="J30" s="113"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5289,87 +5749,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6A8ABF-E61F-4C75-ADCE-19B4345AB4F4}">
-  <dimension ref="A1:AE37"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
-    <col min="2" max="2" width="35.1796875" customWidth="1"/>
-    <col min="3" max="3" width="43.54296875" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="8" max="8" width="41.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:31" ht="83" customHeight="1">
-      <c r="A1" s="127" t="s">
-        <v>412</v>
-      </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="128" t="s">
-        <v>408</v>
-      </c>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="P1" s="127" t="s">
-        <v>411</v>
-      </c>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="128"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
-      <c r="W1" s="128"/>
-      <c r="X1" s="128"/>
-      <c r="Y1" s="128"/>
-      <c r="Z1" s="128"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="128"/>
-      <c r="AC1" s="128"/>
-      <c r="AD1" s="128"/>
-      <c r="AE1" s="128"/>
-    </row>
-    <row r="37" spans="1:12" ht="42.5" customHeight="1">
-      <c r="A37" s="72" t="s">
-        <v>409</v>
-      </c>
-      <c r="B37" s="73"/>
-      <c r="C37" s="74"/>
-      <c r="F37" s="72" t="s">
-        <v>410</v>
-      </c>
-      <c r="G37" s="73"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
-      <c r="J37" s="73"/>
-      <c r="K37" s="73"/>
-      <c r="L37" s="73"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="P1:AE1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="F37:L37"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T77"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -5381,7 +5761,7 @@
     <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.6328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.26953125" customWidth="1"/>
+    <col min="10" max="10" width="31.54296875" customWidth="1"/>
     <col min="11" max="11" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.7265625" customWidth="1"/>
     <col min="13" max="13" width="13.81640625" customWidth="1"/>
@@ -5392,7 +5772,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26">
       <c r="A1" s="48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1" s="48" t="s">
         <v>44</v>
@@ -5401,57 +5781,57 @@
         <v>47</v>
       </c>
       <c r="D1" s="94" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E1" s="48" t="s">
         <v>141</v>
       </c>
       <c r="F1" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="H1" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="48" t="s">
+      <c r="I1" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="J1" s="48" t="s">
         <v>186</v>
-      </c>
-      <c r="J1" s="48" t="s">
-        <v>187</v>
       </c>
       <c r="K1" s="48" t="s">
         <v>140</v>
       </c>
       <c r="L1" s="48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>357</v>
-      </c>
-      <c r="R1" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="S1" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="T1" s="20" t="s">
         <v>189</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="37.5">
       <c r="A2" s="97" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="98" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="D2" s="95" t="s">
         <v>194</v>
-      </c>
-      <c r="D2" s="95" t="s">
-        <v>195</v>
       </c>
       <c r="E2" s="99" t="s">
         <v>4</v>
@@ -5471,7 +5851,7 @@
         <v>Red</v>
       </c>
       <c r="J2" s="99" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K2" s="103" t="s">
         <v>159</v>
@@ -5482,26 +5862,26 @@
       <c r="M2" s="104">
         <v>46289</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="S2" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="S2" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="T2" s="20"/>
+      <c r="T2" s="21"/>
     </row>
     <row r="3" spans="1:20" ht="29">
       <c r="A3" s="97" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C3" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="95" t="s">
         <v>203</v>
-      </c>
-      <c r="D3" s="95" t="s">
-        <v>204</v>
       </c>
       <c r="E3" s="99" t="s">
         <v>9</v>
@@ -5521,7 +5901,7 @@
         <v>Red</v>
       </c>
       <c r="J3" s="99" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K3" s="103" t="s">
         <v>159</v>
@@ -5532,26 +5912,26 @@
       <c r="M3" s="104">
         <v>46289</v>
       </c>
-      <c r="R3" s="20" t="s">
+      <c r="R3" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="S3" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="S3" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="T3" s="20"/>
+      <c r="T3" s="21"/>
     </row>
     <row r="4" spans="1:20" ht="43.5">
       <c r="A4" s="97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B4" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C4" s="99" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="95" t="s">
         <v>209</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>210</v>
       </c>
       <c r="E4" s="99" t="s">
         <v>9</v>
@@ -5571,7 +5951,7 @@
         <v>Red</v>
       </c>
       <c r="J4" s="99" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="K4" s="103" t="s">
         <v>159</v>
@@ -5582,26 +5962,26 @@
       <c r="M4" s="104">
         <v>46289</v>
       </c>
-      <c r="R4" s="20" t="s">
+      <c r="R4" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="S4" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="S4" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="T4" s="20"/>
+      <c r="T4" s="21"/>
     </row>
     <row r="5" spans="1:20" ht="43.5">
       <c r="A5" s="97" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C5" s="99" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D5" s="95" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E5" s="99" t="s">
         <v>4</v>
@@ -5621,7 +6001,7 @@
         <v>Amber</v>
       </c>
       <c r="J5" s="99" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K5" s="103" t="s">
         <v>159</v>
@@ -5632,29 +6012,29 @@
       <c r="M5" s="104">
         <v>46289</v>
       </c>
-      <c r="R5" s="20" t="s">
+      <c r="R5" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="S5" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="S5" s="20" t="s">
+      <c r="T5" s="21"/>
+    </row>
+    <row r="6" spans="1:20" ht="58">
+      <c r="A6" s="87" t="s">
         <v>212</v>
       </c>
-      <c r="T5" s="20"/>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" hidden="1">
-      <c r="A6" s="87" t="s">
+      <c r="B6" s="88" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>496</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="88" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>216</v>
+      <c r="E6" s="13" t="s">
+        <v>6</v>
       </c>
       <c r="F6" s="89">
         <v>5</v>
@@ -5670,8 +6050,8 @@
         <f t="shared" si="0"/>
         <v>Red</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>217</v>
+      <c r="J6" s="13" t="s">
+        <v>497</v>
       </c>
       <c r="K6" s="92" t="s">
         <v>159</v>
@@ -5682,26 +6062,26 @@
       <c r="M6" s="93">
         <v>46289</v>
       </c>
-      <c r="R6" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="S6" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="T6" s="20"/>
+      <c r="R6" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="S6" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="T6" s="21"/>
     </row>
     <row r="7" spans="1:20" ht="43.5">
       <c r="A7" s="97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B7" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" s="99" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D7" s="95" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E7" s="99" t="s">
         <v>8</v>
@@ -5721,7 +6101,7 @@
         <v>Green</v>
       </c>
       <c r="J7" s="99" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="K7" s="103" t="s">
         <v>159</v>
@@ -5732,26 +6112,26 @@
       <c r="M7" s="104">
         <v>46289</v>
       </c>
-      <c r="R7" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="S7" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="T7" s="20"/>
-    </row>
-    <row r="8" spans="1:20" ht="25">
+      <c r="R7" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="T7" s="21"/>
+    </row>
+    <row r="8" spans="1:20" ht="43.5">
       <c r="A8" s="97" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B8" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C8" s="99" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D8" s="95" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E8" s="99" t="s">
         <v>9</v>
@@ -5771,7 +6151,7 @@
         <v>Green</v>
       </c>
       <c r="J8" s="99" t="s">
-        <v>244</v>
+        <v>498</v>
       </c>
       <c r="K8" s="103" t="s">
         <v>159</v>
@@ -5782,26 +6162,26 @@
       <c r="M8" s="104">
         <v>46289</v>
       </c>
-      <c r="R8" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="S8" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="T8" s="20"/>
-    </row>
-    <row r="9" spans="1:20" ht="29">
+      <c r="R8" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="S8" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="T8" s="21"/>
+    </row>
+    <row r="9" spans="1:20" ht="43.5">
       <c r="A9" s="105" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B9" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C9" s="99" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D9" s="95" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E9" s="99" t="s">
         <v>9</v>
@@ -5821,7 +6201,7 @@
         <v>Green</v>
       </c>
       <c r="J9" s="99" t="s">
-        <v>251</v>
+        <v>499</v>
       </c>
       <c r="K9" s="103" t="s">
         <v>159</v>
@@ -5832,39 +6212,43 @@
       <c r="M9" s="104">
         <v>46289</v>
       </c>
-      <c r="R9" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="S9" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="T9" s="20"/>
-    </row>
-    <row r="10" spans="1:20" ht="29">
-      <c r="A10" s="97" t="s">
-        <v>247</v>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+    </row>
+    <row r="10" spans="1:20" ht="72.5">
+      <c r="A10" s="105" t="s">
+        <v>222</v>
       </c>
       <c r="B10" s="98" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="C10" s="99" t="s">
-        <v>253</v>
+        <v>500</v>
       </c>
       <c r="D10" s="95" t="s">
-        <v>254</v>
-      </c>
-      <c r="E10" s="99"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="101" t="str">
+        <v>245</v>
+      </c>
+      <c r="E10" s="99" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="100">
+        <v>3</v>
+      </c>
+      <c r="G10" s="100">
+        <v>4</v>
+      </c>
+      <c r="H10" s="101">
         <f>IF(AND(B10="Risk",ISNUMBER(F10),ISNUMBER(G10)),F10*G10,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="I10" s="102" t="str">
         <f>IF(H10="","",IF(H10&gt;=15,"Red",IF(H10&gt;=8,"Amber","Green")))</f>
-        <v/>
-      </c>
-      <c r="J10" s="99"/>
+        <v>Amber</v>
+      </c>
+      <c r="J10" s="99" t="s">
+        <v>501</v>
+      </c>
       <c r="K10" s="103" t="s">
         <v>159</v>
       </c>
@@ -5874,26 +6258,26 @@
       <c r="M10" s="104">
         <v>46289</v>
       </c>
-      <c r="R10" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="S10" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="T10" s="20"/>
+      <c r="R10" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="S10" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="T10" s="21"/>
     </row>
     <row r="11" spans="1:20" ht="29">
       <c r="A11" s="97" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B11" s="98" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="99" t="s">
         <v>248</v>
       </c>
-      <c r="C11" s="99" t="s">
-        <v>256</v>
-      </c>
       <c r="D11" s="95" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="E11" s="99"/>
       <c r="F11" s="106"/>
@@ -5916,29 +6300,38 @@
       <c r="M11" s="104">
         <v>46289</v>
       </c>
-      <c r="R11" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="S11" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="T11" s="20"/>
-    </row>
-    <row r="12" spans="1:20" ht="25">
+      <c r="R11" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="S11" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="T11" s="21"/>
+    </row>
+    <row r="12" spans="1:20" ht="29">
       <c r="A12" s="97" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B12" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C12" s="99" t="s">
-        <v>127</v>
+        <v>251</v>
+      </c>
+      <c r="D12" s="95" t="s">
+        <v>252</v>
       </c>
       <c r="E12" s="99"/>
       <c r="F12" s="106"/>
       <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="107"/>
+      <c r="H12" s="101" t="str">
+        <f>IF(AND(B12="Risk",ISNUMBER(F12),ISNUMBER(G12)),F12*G12,"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="102" t="str">
+        <f>IF(H12="","",IF(H12&gt;=15,"Red",IF(H12&gt;=8,"Amber","Green")))</f>
+        <v/>
+      </c>
       <c r="J12" s="99"/>
       <c r="K12" s="103" t="s">
         <v>159</v>
@@ -5949,23 +6342,23 @@
       <c r="M12" s="104">
         <v>46289</v>
       </c>
-      <c r="R12" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="S12" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="T12" s="20"/>
-    </row>
-    <row r="13" spans="1:20" ht="29">
-      <c r="A13" s="105" t="s">
-        <v>258</v>
+      <c r="R12" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="S12" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="T12" s="21"/>
+    </row>
+    <row r="13" spans="1:20" ht="25">
+      <c r="A13" s="97" t="s">
+        <v>250</v>
       </c>
       <c r="B13" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C13" s="99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" s="99"/>
       <c r="F13" s="106"/>
@@ -5982,30 +6375,29 @@
       <c r="M13" s="104">
         <v>46289</v>
       </c>
-      <c r="R13" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="S13" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="T13" s="20"/>
+      <c r="R13" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="S13" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="T13" s="21"/>
     </row>
     <row r="14" spans="1:20" ht="29">
-      <c r="A14" s="97" t="s">
-        <v>259</v>
+      <c r="A14" s="105" t="s">
+        <v>253</v>
       </c>
       <c r="B14" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C14" s="99" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="95"/>
+        <v>128</v>
+      </c>
       <c r="E14" s="99"/>
       <c r="F14" s="106"/>
       <c r="G14" s="106"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="102"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="107"/>
       <c r="J14" s="99"/>
       <c r="K14" s="103" t="s">
         <v>159</v>
@@ -6016,23 +6408,23 @@
       <c r="M14" s="104">
         <v>46289</v>
       </c>
-      <c r="R14" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="S14" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="T14" s="20"/>
+      <c r="R14" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="S14" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="T14" s="21"/>
     </row>
     <row r="15" spans="1:20" ht="29">
       <c r="A15" s="97" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B15" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C15" s="99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D15" s="95"/>
       <c r="E15" s="99"/>
@@ -6050,23 +6442,23 @@
       <c r="M15" s="104">
         <v>46289</v>
       </c>
-      <c r="R15" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="S15" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="T15" s="20"/>
-    </row>
-    <row r="16" spans="1:20" ht="58">
+      <c r="R15" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="S15" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="T15" s="21"/>
+    </row>
+    <row r="16" spans="1:20" ht="29">
       <c r="A16" s="97" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B16" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C16" s="99" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D16" s="95"/>
       <c r="E16" s="99"/>
@@ -6084,19 +6476,23 @@
       <c r="M16" s="104">
         <v>46289</v>
       </c>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-    </row>
-    <row r="17" spans="1:20" ht="29">
+      <c r="R16" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="S16" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="T16" s="21"/>
+    </row>
+    <row r="17" spans="1:20" ht="58">
       <c r="A17" s="97" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B17" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C17" s="99" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17" s="95"/>
       <c r="E17" s="99"/>
@@ -6114,25 +6510,26 @@
       <c r="M17" s="104">
         <v>46289</v>
       </c>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-    </row>
-    <row r="18" spans="1:20" ht="43.5">
-      <c r="A18" s="105" t="s">
-        <v>263</v>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+    </row>
+    <row r="18" spans="1:20" ht="29">
+      <c r="A18" s="97" t="s">
+        <v>257</v>
       </c>
       <c r="B18" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C18" s="99" t="s">
-        <v>133</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="D18" s="95"/>
       <c r="E18" s="99"/>
       <c r="F18" s="106"/>
       <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="107"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="102"/>
       <c r="J18" s="99"/>
       <c r="K18" s="103" t="s">
         <v>159</v>
@@ -6143,26 +6540,25 @@
       <c r="M18" s="104">
         <v>46289</v>
       </c>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
+      <c r="R18" s="21"/>
+      <c r="S18" s="21"/>
+      <c r="T18" s="21"/>
     </row>
     <row r="19" spans="1:20" ht="43.5">
-      <c r="A19" s="97" t="s">
-        <v>378</v>
+      <c r="A19" s="105" t="s">
+        <v>258</v>
       </c>
       <c r="B19" s="98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C19" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="D19" s="95"/>
+        <v>133</v>
+      </c>
       <c r="E19" s="99"/>
       <c r="F19" s="106"/>
       <c r="G19" s="106"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="102"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="107"/>
       <c r="J19" s="99"/>
       <c r="K19" s="103" t="s">
         <v>159</v>
@@ -6173,31 +6569,27 @@
       <c r="M19" s="104">
         <v>46289</v>
       </c>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-    </row>
-    <row r="20" spans="1:20" ht="29">
-      <c r="A20" s="105" t="s">
-        <v>264</v>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+    </row>
+    <row r="20" spans="1:20" ht="43.5">
+      <c r="A20" s="97" t="s">
+        <v>371</v>
       </c>
       <c r="B20" s="98" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="C20" s="99" t="s">
-        <v>385</v>
-      </c>
-      <c r="D20"/>
-      <c r="E20" s="99" t="s">
-        <v>8</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="D20" s="95"/>
+      <c r="E20" s="99"/>
       <c r="F20" s="106"/>
       <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="107"/>
-      <c r="J20" s="99" t="s">
-        <v>377</v>
-      </c>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="99"/>
       <c r="K20" s="103" t="s">
         <v>159</v>
       </c>
@@ -6207,19 +6599,19 @@
       <c r="M20" s="104">
         <v>46289</v>
       </c>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-    </row>
-    <row r="21" spans="1:20" ht="43.5">
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+    </row>
+    <row r="21" spans="1:20" ht="29">
       <c r="A21" s="105" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B21" s="98" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C21" s="99" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D21"/>
       <c r="E21" s="99" t="s">
@@ -6230,7 +6622,7 @@
       <c r="H21" s="106"/>
       <c r="I21" s="107"/>
       <c r="J21" s="99" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="K21" s="103" t="s">
         <v>159</v>
@@ -6241,30 +6633,30 @@
       <c r="M21" s="104">
         <v>46289</v>
       </c>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21"/>
+      <c r="T21" s="21"/>
     </row>
     <row r="22" spans="1:20" ht="43.5">
       <c r="A22" s="105" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B22" s="98" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C22" s="99" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D22"/>
       <c r="E22" s="99" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
+      <c r="I22" s="107"/>
       <c r="J22" s="99" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="K22" s="103" t="s">
         <v>159</v>
@@ -6275,30 +6667,30 @@
       <c r="M22" s="104">
         <v>46289</v>
       </c>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
+      <c r="R22" s="21"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
     </row>
     <row r="23" spans="1:20" ht="43.5">
       <c r="A23" s="105" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B23" s="98" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C23" s="99" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D23"/>
       <c r="E23" s="99" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F23" s="106"/>
       <c r="G23" s="106"/>
       <c r="H23" s="106"/>
       <c r="I23" s="106"/>
       <c r="J23" s="99" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="K23" s="103" t="s">
         <v>159</v>
@@ -6309,32 +6701,30 @@
       <c r="M23" s="104">
         <v>46289</v>
       </c>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-    </row>
-    <row r="24" spans="1:20" ht="29">
-      <c r="A24" s="97" t="s">
-        <v>269</v>
+      <c r="R23" s="21"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="21"/>
+    </row>
+    <row r="24" spans="1:20" ht="43.5">
+      <c r="A24" s="105" t="s">
+        <v>263</v>
       </c>
       <c r="B24" s="98" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C24" s="99" t="s">
-        <v>280</v>
-      </c>
-      <c r="D24" s="96" t="s">
+        <v>374</v>
+      </c>
+      <c r="D24"/>
+      <c r="E24" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="E24" s="99"/>
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
-      <c r="H24" s="102" t="s">
-        <v>250</v>
-      </c>
-      <c r="I24" s="107"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="106"/>
       <c r="J24" s="99" t="s">
-        <v>271</v>
+        <v>375</v>
       </c>
       <c r="K24" s="103" t="s">
         <v>159</v>
@@ -6345,32 +6735,32 @@
       <c r="M24" s="104">
         <v>46289</v>
       </c>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="T24" s="21"/>
+    </row>
+    <row r="25" spans="1:20" ht="29">
       <c r="A25" s="97" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B25" s="98" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C25" s="99" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D25" s="96" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25" s="99"/>
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
       <c r="H25" s="102" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I25" s="107"/>
       <c r="J25" s="99" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="K25" s="103" t="s">
         <v>159</v>
@@ -6381,19 +6771,19 @@
       <c r="M25" s="104">
         <v>46289</v>
       </c>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-    </row>
-    <row r="26" spans="1:20" ht="29">
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26" s="97" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B26" s="98" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D26" s="96" t="s">
         <v>9</v>
@@ -6402,11 +6792,11 @@
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
       <c r="H26" s="102" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I26" s="107"/>
       <c r="J26" s="99" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="K26" s="103" t="s">
         <v>159</v>
@@ -6417,19 +6807,19 @@
       <c r="M26" s="104">
         <v>46289</v>
       </c>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-    </row>
-    <row r="27" spans="1:20" ht="43.5">
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+    </row>
+    <row r="27" spans="1:20" ht="58">
       <c r="A27" s="105" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B27" s="98" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C27" s="99" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D27" s="86"/>
       <c r="E27" s="99"/>
@@ -6437,7 +6827,9 @@
       <c r="G27" s="99"/>
       <c r="H27" s="106"/>
       <c r="I27" s="106"/>
-      <c r="J27" s="99"/>
+      <c r="J27" s="99" t="s">
+        <v>489</v>
+      </c>
       <c r="K27" s="103" t="s">
         <v>159</v>
       </c>
@@ -6447,19 +6839,19 @@
       <c r="M27" s="104">
         <v>46289</v>
       </c>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-    </row>
-    <row r="28" spans="1:20" ht="29">
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+    </row>
+    <row r="28" spans="1:20" ht="58">
       <c r="A28" s="105" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B28" s="98" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C28" s="99" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="D28" s="86"/>
       <c r="E28" s="99"/>
@@ -6467,7 +6859,9 @@
       <c r="G28" s="99"/>
       <c r="H28" s="106"/>
       <c r="I28" s="106"/>
-      <c r="J28" s="99"/>
+      <c r="J28" s="99" t="s">
+        <v>489</v>
+      </c>
       <c r="K28" s="103" t="s">
         <v>159</v>
       </c>
@@ -6477,61 +6871,61 @@
       <c r="M28" s="104">
         <v>46289</v>
       </c>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
     </row>
     <row r="29" spans="1:20">
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
     </row>
     <row r="30" spans="1:20">
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="21"/>
+      <c r="T30" s="21"/>
     </row>
     <row r="31" spans="1:20">
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20" t="s">
-        <v>272</v>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="C32"/>
-      <c r="D32" s="20"/>
+      <c r="D32" s="21"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="I32"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20" t="s">
-        <v>274</v>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="C33"/>
-      <c r="D33" s="20"/>
+      <c r="D33" s="21"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="I33"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20" t="s">
-        <v>276</v>
+      <c r="R33" s="21"/>
+      <c r="S33" s="21"/>
+      <c r="T33" s="21" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="C34"/>
-      <c r="D34" s="20"/>
+      <c r="D34" s="21"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="I34"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20" t="s">
-        <v>278</v>
+      <c r="R34" s="21"/>
+      <c r="S34" s="21"/>
+      <c r="T34" s="21" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="25">
@@ -6539,28 +6933,28 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="I35"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20" t="s">
-        <v>281</v>
+      <c r="R35" s="21"/>
+      <c r="S35" s="21"/>
+      <c r="T35" s="21" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20" t="s">
-        <v>283</v>
+      <c r="R36" s="21"/>
+      <c r="S36" s="21"/>
+      <c r="T36" s="21" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20" t="s">
-        <v>285</v>
+      <c r="R37" s="21"/>
+      <c r="S37" s="21"/>
+      <c r="T37" s="21" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -6568,20 +6962,20 @@
       <c r="G38" s="3"/>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="18"/>
-      <c r="B39" s="17"/>
+      <c r="A39" s="19"/>
+      <c r="B39" s="18"/>
       <c r="D39" s="85"/>
-      <c r="E39" s="17"/>
+      <c r="E39" s="18"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="17"/>
+      <c r="H39" s="18"/>
       <c r="I39" s="71"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
     </row>
     <row r="40" spans="1:20">
       <c r="F40" s="3"/>
@@ -6625,10 +7019,10 @@
     </row>
     <row r="50" spans="2:7">
       <c r="B50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -6747,30 +7141,37 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M37" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}">
-    <filterColumn colId="2">
-      <colorFilter dxfId="51"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="I14:I17 I2:I11 I19">
-    <cfRule type="cellIs" dxfId="42" priority="58" operator="equal">
+  <autoFilter ref="A1:M37" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}"/>
+  <conditionalFormatting sqref="I15:I18 I2:I8 I20 I10:I12">
+    <cfRule type="cellIs" dxfId="50" priority="70" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="71" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="72" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H24:H26">
-    <cfRule type="cellIs" dxfId="15" priority="22" operator="equal">
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="cellIs" dxfId="23" priority="34" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="35" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="36" operator="equal">
+      <formula>"Green"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+      <formula>"Red"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+      <formula>"Amber"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6779,7 +7180,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="54" operator="equal" id="{57F63839-4A9F-4432-A6BA-F8036C3FDB7B}">
+          <x14:cfRule type="cellIs" priority="66" operator="equal" id="{57F63839-4A9F-4432-A6BA-F8036C3FDB7B}">
             <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
             <x14:dxf>
               <fill>
@@ -6789,7 +7190,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="55" operator="equal" id="{ACE905DF-63B2-45FF-953F-7B6626631D89}">
+          <x14:cfRule type="cellIs" priority="67" operator="equal" id="{ACE905DF-63B2-45FF-953F-7B6626631D89}">
             <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
             <x14:dxf>
               <fill>
@@ -6799,7 +7200,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="56" operator="equal" id="{21721EF6-7E8E-40CB-9C57-65A973A31421}">
+          <x14:cfRule type="cellIs" priority="68" operator="equal" id="{21721EF6-7E8E-40CB-9C57-65A973A31421}">
             <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6809,7 +7210,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="57" operator="equal" id="{4112797C-ACDE-447B-82AE-D4BB44D66DB8}">
+          <x14:cfRule type="cellIs" priority="69" operator="equal" id="{4112797C-ACDE-447B-82AE-D4BB44D66DB8}">
             <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
             <x14:dxf>
               <fill>
@@ -6819,10 +7220,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K6:K28</xm:sqref>
+          <xm:sqref>K6:K8 K10:K28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="49" operator="equal" id="{B5B9D27F-84B7-408D-B0EF-A1192C5B811D}">
+          <x14:cfRule type="cellIs" priority="61" operator="equal" id="{B5B9D27F-84B7-408D-B0EF-A1192C5B811D}">
             <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
             <x14:dxf>
               <fill>
@@ -6832,7 +7233,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="50" operator="equal" id="{D9F59AF5-8011-4431-BA42-AA154A2E67EC}">
+          <x14:cfRule type="cellIs" priority="62" operator="equal" id="{D9F59AF5-8011-4431-BA42-AA154A2E67EC}">
             <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
             <x14:dxf>
               <fill>
@@ -6842,7 +7243,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="51" operator="equal" id="{734DDEB5-AE68-4214-B5A1-9B795FA2B741}">
+          <x14:cfRule type="cellIs" priority="63" operator="equal" id="{734DDEB5-AE68-4214-B5A1-9B795FA2B741}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6852,7 +7253,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="53" operator="equal" id="{26F3D79F-0B06-470C-9B2F-54F198740B50}">
+          <x14:cfRule type="cellIs" priority="65" operator="equal" id="{26F3D79F-0B06-470C-9B2F-54F198740B50}">
             <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
             <x14:dxf>
               <fill>
@@ -6862,10 +7263,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:B11</xm:sqref>
+          <xm:sqref>B2:B8 B10:B12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="52" operator="equal" id="{43E7C21A-4FE6-4067-9F57-0277CE258974}">
+          <x14:cfRule type="cellIs" priority="64" operator="equal" id="{43E7C21A-4FE6-4067-9F57-0277CE258974}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6875,10 +7276,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B9:B11</xm:sqref>
+          <xm:sqref>B10:B12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="35" operator="equal" id="{75FC84F2-F511-4903-8AE6-A7947E485406}">
+          <x14:cfRule type="cellIs" priority="47" operator="equal" id="{75FC84F2-F511-4903-8AE6-A7947E485406}">
             <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
             <x14:dxf>
               <fill>
@@ -6888,7 +7289,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="36" operator="equal" id="{10835EE7-C995-4E21-BCE3-A20CF35568AB}">
+          <x14:cfRule type="cellIs" priority="48" operator="equal" id="{10835EE7-C995-4E21-BCE3-A20CF35568AB}">
             <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
             <x14:dxf>
               <fill>
@@ -6898,7 +7299,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{0C3B5A95-8589-475F-B004-4E80EF474F17}">
+          <x14:cfRule type="cellIs" priority="49" operator="equal" id="{0C3B5A95-8589-475F-B004-4E80EF474F17}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6908,7 +7309,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{CCF08C97-65B6-4E34-8A5D-160A264ACC00}">
+          <x14:cfRule type="cellIs" priority="51" operator="equal" id="{CCF08C97-65B6-4E34-8A5D-160A264ACC00}">
             <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
             <x14:dxf>
               <fill>
@@ -6918,10 +7319,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B12:B19</xm:sqref>
+          <xm:sqref>B13:B20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{B7A2EBBA-CD73-401B-A8D5-36EF73E21204}">
+          <x14:cfRule type="cellIs" priority="50" operator="equal" id="{B7A2EBBA-CD73-401B-A8D5-36EF73E21204}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6931,10 +7332,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B12:B19</xm:sqref>
+          <xm:sqref>B13:B20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="30" operator="equal" id="{A935A616-B09F-434C-B686-E45FCC0F3845}">
+          <x14:cfRule type="cellIs" priority="42" operator="equal" id="{A935A616-B09F-434C-B686-E45FCC0F3845}">
             <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
             <x14:dxf>
               <fill>
@@ -6944,7 +7345,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="31" operator="equal" id="{D6939982-6790-420A-88C4-6E4051C457EC}">
+          <x14:cfRule type="cellIs" priority="43" operator="equal" id="{D6939982-6790-420A-88C4-6E4051C457EC}">
             <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
             <x14:dxf>
               <fill>
@@ -6954,7 +7355,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="32" operator="equal" id="{6A2E298D-8B55-4F63-9AA8-3D11C2F24F48}">
+          <x14:cfRule type="cellIs" priority="44" operator="equal" id="{6A2E298D-8B55-4F63-9AA8-3D11C2F24F48}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6964,7 +7365,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="34" operator="equal" id="{059CCA81-DAF4-49B7-ABE1-F33CA500E424}">
+          <x14:cfRule type="cellIs" priority="46" operator="equal" id="{059CCA81-DAF4-49B7-ABE1-F33CA500E424}">
             <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
             <x14:dxf>
               <fill>
@@ -6974,10 +7375,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B20:B23</xm:sqref>
+          <xm:sqref>B21:B24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="33" operator="equal" id="{C4AE0AF5-C3C9-4B33-9D81-6895D68E7587}">
+          <x14:cfRule type="cellIs" priority="45" operator="equal" id="{C4AE0AF5-C3C9-4B33-9D81-6895D68E7587}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -6987,10 +7388,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B20:B23</xm:sqref>
+          <xm:sqref>B21:B24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{A315016E-77AB-422C-832A-D7E3C6CF679F}">
+          <x14:cfRule type="cellIs" priority="37" operator="equal" id="{A315016E-77AB-422C-832A-D7E3C6CF679F}">
             <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
             <x14:dxf>
               <fill>
@@ -7000,7 +7401,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{1C7B341B-7734-422C-817A-E1C00F81ACF0}">
+          <x14:cfRule type="cellIs" priority="38" operator="equal" id="{1C7B341B-7734-422C-817A-E1C00F81ACF0}">
             <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
             <x14:dxf>
               <fill>
@@ -7010,7 +7411,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{C32128CB-8C92-4883-B016-494D99312149}">
+          <x14:cfRule type="cellIs" priority="39" operator="equal" id="{C32128CB-8C92-4883-B016-494D99312149}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -7020,7 +7421,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{1BDA13F1-9A8A-4763-8648-9AD0021686B6}">
+          <x14:cfRule type="cellIs" priority="41" operator="equal" id="{1BDA13F1-9A8A-4763-8648-9AD0021686B6}">
             <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
             <x14:dxf>
               <fill>
@@ -7030,10 +7431,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B24:B26</xm:sqref>
+          <xm:sqref>B25:B26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{EE298F77-ABFB-4E88-BD13-DD86ABEC8EB7}">
+          <x14:cfRule type="cellIs" priority="40" operator="equal" id="{EE298F77-ABFB-4E88-BD13-DD86ABEC8EB7}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -7043,10 +7444,10 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B24:B26</xm:sqref>
+          <xm:sqref>B25:B26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{CB0D0C7D-67CD-4D99-BA4B-41995F51C4D6}">
+          <x14:cfRule type="cellIs" priority="25" operator="equal" id="{CB0D0C7D-67CD-4D99-BA4B-41995F51C4D6}">
             <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
             <x14:dxf>
               <fill>
@@ -7056,7 +7457,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{0A3FBA08-EC09-46D7-9AA1-0F8223238DB3}">
+          <x14:cfRule type="cellIs" priority="26" operator="equal" id="{0A3FBA08-EC09-46D7-9AA1-0F8223238DB3}">
             <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
             <x14:dxf>
               <fill>
@@ -7066,7 +7467,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{5EE9050F-25E7-4861-BAD4-793E7F3B8433}">
+          <x14:cfRule type="cellIs" priority="27" operator="equal" id="{5EE9050F-25E7-4861-BAD4-793E7F3B8433}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -7076,7 +7477,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="17" operator="equal" id="{9F4C58C7-89AA-4332-85EF-D8018E67E41B}">
+          <x14:cfRule type="cellIs" priority="29" operator="equal" id="{9F4C58C7-89AA-4332-85EF-D8018E67E41B}">
             <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
             <x14:dxf>
               <fill>
@@ -7089,7 +7490,7 @@
           <xm:sqref>B27:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{C96A7840-E8FC-4926-A088-208EC893F985}">
+          <x14:cfRule type="cellIs" priority="28" operator="equal" id="{C96A7840-E8FC-4926-A088-208EC893F985}">
             <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
             <x14:dxf>
               <fill>
@@ -7102,7 +7503,7 @@
           <xm:sqref>B27:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{9D83211C-BFDE-4E12-B616-7753D9FD10A3}">
+          <x14:cfRule type="cellIs" priority="13" operator="equal" id="{12A4F610-8F0D-47DB-80B3-AABA0446F3BE}">
             <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
             <x14:dxf>
               <fill>
@@ -7112,7 +7513,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{03B42228-A5CC-4C3E-9575-986686D1EE1E}">
+          <x14:cfRule type="cellIs" priority="14" operator="equal" id="{9BCEEC92-204D-4F1E-B91D-A86674902C0E}">
             <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
             <x14:dxf>
               <fill>
@@ -7122,7 +7523,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{2D14FD9A-8888-4347-9E84-D81BF99FE3F2}">
+          <x14:cfRule type="cellIs" priority="15" operator="equal" id="{1B48D0CE-8C6A-4380-920A-09AF17944213}">
             <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
             <x14:dxf>
               <fill>
@@ -7132,50 +7533,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{E29D84BA-B848-4C57-8461-9C16AC91714B}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="4" tint="0.39994506668294322"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>K24:K28</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{12A4F610-8F0D-47DB-80B3-AABA0446F3BE}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{9BCEEC92-204D-4F1E-B91D-A86674902C0E}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{1B48D0CE-8C6A-4380-920A-09AF17944213}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFFF00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{2ABCFA83-7166-4F1D-ADE5-1ADDF56C8450}">
+          <x14:cfRule type="cellIs" priority="16" operator="equal" id="{2ABCFA83-7166-4F1D-ADE5-1ADDF56C8450}">
             <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
             <x14:dxf>
               <fill>
@@ -7186,6 +7544,105 @@
             </x14:dxf>
           </x14:cfRule>
           <xm:sqref>K2:K5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="6" operator="equal" id="{344CC581-A1A3-486A-9628-9C3640970D2A}">
+            <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF92D050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="7" operator="equal" id="{996E347F-2D7A-4E82-909A-0552EAB66B5A}">
+            <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF0000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="8" operator="equal" id="{2794A480-20AF-4750-BB33-AE5AFB6EC6A1}">
+            <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="9" operator="equal" id="{8E978570-7E82-47D0-B51E-82BC3737C8E9}">
+            <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="4" tint="0.39994506668294322"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>K9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{981E1B3E-06CD-4E01-8081-22EA37FE816B}">
+            <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{CC91F5C6-12E2-4C70-BDE1-41D28F789B3C}">
+            <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFCCCC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{4B2553DE-3827-417C-AAEF-48EE05247D0B}">
+            <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="cellIs" priority="5" operator="equal" id="{8C367ECA-8C5D-48A5-A5F1-EADADEA57874}">
+            <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="5" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B9</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="4" operator="equal" id="{0ED405A8-86EE-4C95-8322-399F42C0FB1B}">
+            <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="8" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B9</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7209,7 +7666,1335 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6A8ABF-E61F-4C75-ADCE-19B4345AB4F4}">
+  <dimension ref="A1:AK33"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="37.54296875" customWidth="1"/>
+    <col min="2" max="2" width="35.1796875" customWidth="1"/>
+    <col min="3" max="3" width="43.54296875" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="8" max="8" width="41.08984375" customWidth="1"/>
+    <col min="35" max="35" width="42.26953125" customWidth="1"/>
+    <col min="36" max="36" width="48.36328125" customWidth="1"/>
+    <col min="37" max="37" width="66.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" ht="83" customHeight="1">
+      <c r="A1" s="129" t="s">
+        <v>494</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="130" t="s">
+        <v>401</v>
+      </c>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="P1" s="129" t="s">
+        <v>403</v>
+      </c>
+      <c r="Q1" s="130"/>
+      <c r="R1" s="130"/>
+      <c r="S1" s="130"/>
+      <c r="T1" s="130"/>
+      <c r="U1" s="130"/>
+      <c r="V1" s="130"/>
+      <c r="W1" s="130"/>
+      <c r="X1" s="130"/>
+      <c r="Y1" s="130"/>
+      <c r="Z1" s="130"/>
+      <c r="AA1" s="130"/>
+      <c r="AB1" s="130"/>
+      <c r="AC1" s="130"/>
+      <c r="AD1" s="130"/>
+      <c r="AE1" s="130"/>
+      <c r="AI1" s="72" t="s">
+        <v>383</v>
+      </c>
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="74"/>
+    </row>
+    <row r="33" spans="1:12" ht="42.5" customHeight="1">
+      <c r="A33" s="72" t="s">
+        <v>402</v>
+      </c>
+      <c r="B33" s="73"/>
+      <c r="C33" s="74"/>
+      <c r="F33" s="72" t="s">
+        <v>490</v>
+      </c>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="AI1:AK1"/>
+    <mergeCell ref="P1:AE1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="F33:L33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569F1412-D6F6-4C33-BE23-573808AF6A8E}">
+  <dimension ref="A1:X61"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" customWidth="1"/>
+    <col min="5" max="5" width="61.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="131" t="s">
+        <v>404</v>
+      </c>
+      <c r="B1" s="132" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1" s="132" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1" s="132" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="132" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="132" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="132" t="s">
+        <v>408</v>
+      </c>
+      <c r="H1" s="132" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" s="132" t="s">
+        <v>409</v>
+      </c>
+      <c r="J1" s="133" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C2" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="D2" s="119" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="F2" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H2" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I2" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J2" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C3" s="119" t="s">
+        <v>415</v>
+      </c>
+      <c r="D3" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="119" t="s">
+        <v>416</v>
+      </c>
+      <c r="F3" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H3" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I3" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J3" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B4" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E4" s="119" t="s">
+        <v>420</v>
+      </c>
+      <c r="F4" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H4" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I4" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J4" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B5" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C5" s="119" t="s">
+        <v>421</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="119" t="s">
+        <v>422</v>
+      </c>
+      <c r="F5" s="119" t="s">
+        <v>423</v>
+      </c>
+      <c r="G5" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H5" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I5" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J5" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B6" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C6" s="119" t="s">
+        <v>424</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E6" s="119" t="s">
+        <v>425</v>
+      </c>
+      <c r="F6" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H6" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I6" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J6" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C7" s="119" t="s">
+        <v>426</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E7" s="119" t="s">
+        <v>427</v>
+      </c>
+      <c r="F7" s="119" t="s">
+        <v>428</v>
+      </c>
+      <c r="G7" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H7" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I7" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J7" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B8" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C8" s="119" t="s">
+        <v>429</v>
+      </c>
+      <c r="D8" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="119" t="s">
+        <v>430</v>
+      </c>
+      <c r="F8" s="119" t="s">
+        <v>423</v>
+      </c>
+      <c r="G8" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H8" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I8" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J8" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B9" s="119" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="119" t="s">
+        <v>431</v>
+      </c>
+      <c r="D9" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="119" t="s">
+        <v>432</v>
+      </c>
+      <c r="F9" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="119" t="s">
+        <v>433</v>
+      </c>
+      <c r="H9" s="119" t="s">
+        <v>434</v>
+      </c>
+      <c r="I9" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J9" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="D10" s="119" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="F10" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H10" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I10" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J10" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B11" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C11" s="119" t="s">
+        <v>437</v>
+      </c>
+      <c r="D11" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="119" t="s">
+        <v>438</v>
+      </c>
+      <c r="F11" s="119" t="s">
+        <v>423</v>
+      </c>
+      <c r="G11" s="119" t="s">
+        <v>439</v>
+      </c>
+      <c r="H11" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I11" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J11" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="119" t="s">
+        <v>440</v>
+      </c>
+      <c r="D12" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="119" t="s">
+        <v>441</v>
+      </c>
+      <c r="F12" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G12" s="119" t="s">
+        <v>439</v>
+      </c>
+      <c r="H12" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I12" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J12" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B13" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="119" t="s">
+        <v>443</v>
+      </c>
+      <c r="D13" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" s="119" t="s">
+        <v>444</v>
+      </c>
+      <c r="F13" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G13" s="119" t="s">
+        <v>439</v>
+      </c>
+      <c r="H13" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I13" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J13" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B14" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C14" s="119" t="s">
+        <v>445</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E14" s="119" t="s">
+        <v>446</v>
+      </c>
+      <c r="F14" s="119" t="s">
+        <v>447</v>
+      </c>
+      <c r="G14" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H14" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I14" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J14" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B15" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E15" s="119" t="s">
+        <v>449</v>
+      </c>
+      <c r="F15" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G15" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H15" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I15" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J15" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B16" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C16" s="119" t="s">
+        <v>450</v>
+      </c>
+      <c r="D16" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E16" s="119" t="s">
+        <v>451</v>
+      </c>
+      <c r="F16" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H16" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I16" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J16" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B17" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C17" s="119" t="s">
+        <v>452</v>
+      </c>
+      <c r="D17" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="119" t="s">
+        <v>453</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>423</v>
+      </c>
+      <c r="G17" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H17" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I17" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J17" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B18" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>454</v>
+      </c>
+      <c r="D18" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E18" s="119" t="s">
+        <v>455</v>
+      </c>
+      <c r="F18" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G18" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H18" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I18" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J18" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B19" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E19" s="119" t="s">
+        <v>457</v>
+      </c>
+      <c r="F19" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H19" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I19" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J19" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B20" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>458</v>
+      </c>
+      <c r="D20" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E20" s="119" t="s">
+        <v>459</v>
+      </c>
+      <c r="F20" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G20" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H20" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I20" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J20" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B21" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C21" s="119" t="s">
+        <v>460</v>
+      </c>
+      <c r="D21" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E21" s="119" t="s">
+        <v>461</v>
+      </c>
+      <c r="F21" s="119" t="s">
+        <v>428</v>
+      </c>
+      <c r="G21" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H21" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I21" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J21" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B22" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C22" s="119" t="s">
+        <v>462</v>
+      </c>
+      <c r="D22" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="119" t="s">
+        <v>463</v>
+      </c>
+      <c r="F22" s="119" t="s">
+        <v>423</v>
+      </c>
+      <c r="G22" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H22" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I22" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J22" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B23" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C23" s="119" t="s">
+        <v>464</v>
+      </c>
+      <c r="D23" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="119" t="s">
+        <v>465</v>
+      </c>
+      <c r="F23" s="119" t="s">
+        <v>423</v>
+      </c>
+      <c r="G23" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H23" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I23" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J23" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B24" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C24" s="119" t="s">
+        <v>466</v>
+      </c>
+      <c r="D24" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E24" s="119" t="s">
+        <v>467</v>
+      </c>
+      <c r="F24" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G24" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H24" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I24" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J24" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B25" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C25" s="119" t="s">
+        <v>468</v>
+      </c>
+      <c r="D25" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="119" t="s">
+        <v>469</v>
+      </c>
+      <c r="F25" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H25" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I25" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J25" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B26" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C26" s="119" t="s">
+        <v>470</v>
+      </c>
+      <c r="D26" s="119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="119" t="s">
+        <v>471</v>
+      </c>
+      <c r="F26" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H26" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I26" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J26" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B27" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C27" s="119" t="s">
+        <v>472</v>
+      </c>
+      <c r="D27" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E27" s="119" t="s">
+        <v>473</v>
+      </c>
+      <c r="F27" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G27" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H27" s="119" t="s">
+        <v>434</v>
+      </c>
+      <c r="I27" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J27" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="119" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28" s="119" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="119" t="s">
+        <v>474</v>
+      </c>
+      <c r="D28" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E28" s="119" t="s">
+        <v>475</v>
+      </c>
+      <c r="F28" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G28" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H28" s="119" t="s">
+        <v>434</v>
+      </c>
+      <c r="I28" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J28" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B29" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C29" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="D29" s="119" t="s">
+        <v>405</v>
+      </c>
+      <c r="E29" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="F29" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H29" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I29" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J29" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B30" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C30" s="119" t="s">
+        <v>478</v>
+      </c>
+      <c r="D30" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E30" s="119" t="s">
+        <v>479</v>
+      </c>
+      <c r="F30" s="119" t="s">
+        <v>447</v>
+      </c>
+      <c r="G30" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H30" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I30" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J30" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B31" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C31" s="119" t="s">
+        <v>480</v>
+      </c>
+      <c r="D31" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E31" s="119" t="s">
+        <v>481</v>
+      </c>
+      <c r="F31" s="119" t="s">
+        <v>447</v>
+      </c>
+      <c r="G31" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H31" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I31" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J31" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B32" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C32" s="119" t="s">
+        <v>482</v>
+      </c>
+      <c r="D32" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E32" s="119" t="s">
+        <v>483</v>
+      </c>
+      <c r="F32" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G32" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H32" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I32" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J32" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24">
+      <c r="A33" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B33" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C33" s="119" t="s">
+        <v>484</v>
+      </c>
+      <c r="D33" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E33" s="119" t="s">
+        <v>485</v>
+      </c>
+      <c r="F33" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="119" t="s">
+        <v>417</v>
+      </c>
+      <c r="H33" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I33" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J33" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24">
+      <c r="A34" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B34" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C34" s="119" t="s">
+        <v>486</v>
+      </c>
+      <c r="D34" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E34" s="119" t="s">
+        <v>487</v>
+      </c>
+      <c r="F34" s="119" t="s">
+        <v>442</v>
+      </c>
+      <c r="G34" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H34" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I34" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J34" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24">
+      <c r="A35" s="119" t="s">
+        <v>476</v>
+      </c>
+      <c r="B35" s="119" t="s">
+        <v>477</v>
+      </c>
+      <c r="C35" s="119" t="s">
+        <v>488</v>
+      </c>
+      <c r="D35" s="119" t="s">
+        <v>419</v>
+      </c>
+      <c r="E35" s="119" t="s">
+        <v>487</v>
+      </c>
+      <c r="F35" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="H35" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="I35" s="134">
+        <v>46288</v>
+      </c>
+      <c r="J35" s="134">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="14.5" customHeight="1">
+      <c r="A42" s="135" t="s">
+        <v>491</v>
+      </c>
+      <c r="B42" s="135"/>
+      <c r="C42" s="135"/>
+      <c r="D42" s="135"/>
+      <c r="E42" s="135"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="135"/>
+      <c r="I42" s="113" t="s">
+        <v>492</v>
+      </c>
+      <c r="J42" s="114"/>
+      <c r="K42" s="114"/>
+      <c r="L42" s="114"/>
+      <c r="M42" s="114"/>
+      <c r="N42" s="114"/>
+      <c r="O42" s="114"/>
+      <c r="P42" s="114"/>
+      <c r="Q42" s="114"/>
+      <c r="R42" s="114"/>
+      <c r="S42" s="114"/>
+      <c r="T42" s="114"/>
+      <c r="U42" s="114"/>
+      <c r="V42" s="114"/>
+      <c r="W42" s="114"/>
+      <c r="X42" s="114"/>
+    </row>
+    <row r="43" spans="1:24">
+      <c r="A43" s="135"/>
+      <c r="B43" s="135"/>
+      <c r="C43" s="135"/>
+      <c r="D43" s="135"/>
+      <c r="E43" s="135"/>
+      <c r="F43" s="135"/>
+      <c r="G43" s="135"/>
+      <c r="I43" s="113"/>
+      <c r="J43" s="114"/>
+      <c r="K43" s="114"/>
+      <c r="L43" s="114"/>
+      <c r="M43" s="114"/>
+      <c r="N43" s="114"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="114"/>
+      <c r="Q43" s="114"/>
+      <c r="R43" s="114"/>
+      <c r="S43" s="114"/>
+      <c r="T43" s="114"/>
+      <c r="U43" s="114"/>
+      <c r="V43" s="114"/>
+      <c r="W43" s="114"/>
+      <c r="X43" s="114"/>
+    </row>
+    <row r="60" spans="9:24" ht="14.5" customHeight="1">
+      <c r="I60" s="135" t="s">
+        <v>493</v>
+      </c>
+      <c r="J60" s="135"/>
+      <c r="K60" s="135"/>
+      <c r="L60" s="135"/>
+      <c r="M60" s="135"/>
+      <c r="N60" s="135"/>
+      <c r="O60" s="135"/>
+      <c r="P60" s="135"/>
+      <c r="Q60" s="135"/>
+      <c r="R60" s="135"/>
+      <c r="S60" s="135"/>
+      <c r="T60" s="135"/>
+      <c r="U60" s="135"/>
+      <c r="V60" s="135"/>
+      <c r="W60" s="135"/>
+      <c r="X60" s="135"/>
+    </row>
+    <row r="61" spans="9:24">
+      <c r="I61" s="135"/>
+      <c r="J61" s="135"/>
+      <c r="K61" s="135"/>
+      <c r="L61" s="135"/>
+      <c r="M61" s="135"/>
+      <c r="N61" s="135"/>
+      <c r="O61" s="135"/>
+      <c r="P61" s="135"/>
+      <c r="Q61" s="135"/>
+      <c r="R61" s="135"/>
+      <c r="S61" s="135"/>
+      <c r="T61" s="135"/>
+      <c r="U61" s="135"/>
+      <c r="V61" s="135"/>
+      <c r="W61" s="135"/>
+      <c r="X61" s="135"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A42:G43"/>
+    <mergeCell ref="I42:X43"/>
+    <mergeCell ref="I60:X61"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7F1919-2543-40B0-86E7-ADC6C70417C2}">
   <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -7223,13 +9008,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.5" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
       <c r="H1" s="1" t="s">
         <v>126</v>
       </c>
@@ -7244,12 +9029,12 @@
       <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
       <c r="H3" t="s">
         <v>128</v>
       </c>
@@ -7258,12 +9043,12 @@
       <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
       <c r="H4" t="s">
         <v>129</v>
       </c>
@@ -7366,23 +9151,23 @@
       <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="6" t="s">
@@ -7433,23 +9218,23 @@
       <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
@@ -7500,23 +9285,23 @@
       <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
@@ -7599,23 +9384,23 @@
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
@@ -7666,23 +9451,23 @@
       <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
@@ -7733,23 +9518,23 @@
       <c r="A43" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
@@ -7800,23 +9585,23 @@
       <c r="A50" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
@@ -7884,23 +9669,23 @@
       <c r="A57" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
@@ -7968,23 +9753,23 @@
       <c r="A64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
@@ -8035,23 +9820,23 @@
       <c r="A70" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
@@ -8115,23 +9900,23 @@
       <c r="A77" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
@@ -8182,23 +9967,23 @@
       <c r="A83" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
+      <c r="C83" s="10"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
@@ -8283,23 +10068,23 @@
       <c r="A91" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
+      <c r="C91" s="10"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
@@ -8400,7 +10185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F8DE2A-76E6-452A-AE90-13C80C3D40F2}">
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -8522,7 +10307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DCDC7C-55B3-416C-9E03-05A0A063B246}">
   <dimension ref="A1:T17"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -8565,23 +10350,23 @@
         <v>9</v>
       </c>
       <c r="I1" s="48" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="J1" s="48" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K1" s="48"/>
       <c r="L1" s="48"/>
       <c r="M1" s="48"/>
       <c r="N1" s="48"/>
       <c r="P1" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -8606,25 +10391,25 @@
       </c>
       <c r="I2" s="48"/>
       <c r="J2" s="48" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="L2" s="48" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="M2" s="48" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="N2" s="48" t="s">
-        <v>290</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="R2" s="21" t="s">
-        <v>193</v>
+        <v>283</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>192</v>
       </c>
       <c r="T2" s="63" t="s">
         <v>34</v>
@@ -8645,7 +10430,7 @@
       <c r="F3" s="63"/>
       <c r="G3" s="63"/>
       <c r="I3" s="42" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="J3" s="41">
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
@@ -8667,14 +10452,14 @@
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="16" t="s">
+      <c r="P3" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="R3" s="22" t="s">
-        <v>248</v>
+      <c r="R3" s="23" t="s">
+        <v>244</v>
       </c>
       <c r="T3" s="63" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -8692,7 +10477,7 @@
       <c r="F4" s="63"/>
       <c r="G4" s="63"/>
       <c r="I4" s="42" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="J4" s="41">
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
@@ -8714,14 +10499,14 @@
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
         <v>1</v>
       </c>
-      <c r="P4" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="R4" s="23" t="s">
-        <v>265</v>
+      <c r="P4" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>260</v>
       </c>
       <c r="T4" s="63" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -8741,7 +10526,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="42" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="J5" s="41">
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
@@ -8763,19 +10548,19 @@
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
         <v>1</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="R5" s="24" t="s">
-        <v>270</v>
+      <c r="R5" s="25" t="s">
+        <v>265</v>
       </c>
       <c r="T5" s="63" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="I6" s="42" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="J6" s="41">
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
@@ -8800,7 +10585,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="I7" s="42" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="J7" s="41">
         <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
@@ -8825,7 +10610,7 @@
     </row>
     <row r="9" spans="1:20" ht="29" customHeight="1">
       <c r="I9" s="40" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="J9" s="40"/>
       <c r="K9" s="40"/>
@@ -8834,16 +10619,16 @@
       <c r="N9" s="40"/>
     </row>
     <row r="11" spans="1:20" ht="15.5">
-      <c r="I11" s="25" t="s">
-        <v>297</v>
+      <c r="I11" s="26" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="I12" s="48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J12" s="48" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -8851,7 +10636,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="63" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -8859,7 +10644,7 @@
         <v>2</v>
       </c>
       <c r="J14" s="63" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -8867,7 +10652,7 @@
         <v>3</v>
       </c>
       <c r="J15" s="63" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -8875,7 +10660,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="63" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="9:10" ht="43.5">
@@ -8883,7 +10668,7 @@
         <v>5</v>
       </c>
       <c r="J17" s="69" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Datathon Project.xlsx
+++ b/docs/Datathon Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoa-my.sharepoint.com/personal/ghin287_uoa_auckland_ac_nz/Documents/Documents/University/Datathon temp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11450F02-EE81-4929-8FBE-319E30382959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{11450F02-EE81-4929-8FBE-319E30382959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F1E792-5F51-4658-971C-86D2D19E5EB6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Overview" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="588">
   <si>
     <t>court</t>
   </si>
@@ -2044,6 +2044,9 @@
   </si>
   <si>
     <t>This is the extraction used by fct_judgment</t>
+  </si>
+  <si>
+    <t>6 Gramss - Team 4</t>
   </si>
 </sst>
 </file>
@@ -2603,7 +2606,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2826,19 +2829,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2855,6 +2846,21 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2937,16 +2943,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4639,7 +4645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70241A6B-2CF1-42DB-9288-7E14FFCD0A5F}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
@@ -4649,89 +4655,94 @@
     <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="90" t="s">
         <v>263</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K2" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>78</v>
       </c>
       <c r="B3" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="D3" s="90" t="s">
+        <v>587</v>
+      </c>
+      <c r="E3" s="127"/>
       <c r="F3" s="3"/>
-      <c r="K3" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G3" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>75</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="127"/>
       <c r="F4" s="3"/>
-      <c r="K4" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G4" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="E5" s="3"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="127"/>
       <c r="F5" s="3"/>
-      <c r="K5" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G5" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="39" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="127"/>
       <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G6" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="50"/>
       <c r="B7" s="51"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="127"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="93" t="s">
+    <row r="10" spans="1:7" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="89" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93" t="s">
+      <c r="B10" s="89"/>
+      <c r="C10" s="89"/>
+      <c r="D10" s="89" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-    </row>
-    <row r="11" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="89"/>
+      <c r="F10" s="89"/>
+    </row>
+    <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
         <v>18</v>
       </c>
@@ -4751,7 +4762,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="52" t="s">
         <v>8</v>
       </c>
@@ -4771,7 +4782,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>9</v>
       </c>
@@ -4791,7 +4802,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>6</v>
       </c>
@@ -4811,7 +4822,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>7</v>
       </c>
@@ -4831,7 +4842,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>4</v>
       </c>
@@ -4870,10 +4881,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="91" t="s">
+      <c r="A20" s="87" t="s">
         <v>258</v>
       </c>
-      <c r="B20" s="92"/>
+      <c r="B20" s="88"/>
     </row>
     <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
@@ -4973,11 +4984,12 @@
     </row>
     <row r="36" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D3:E7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B28" r:id="rId1" display="https://drive.google.com/drive/u/6/folders/1Bw7lSWdOExDDpihTWeozwxtdz5_t1KNN" xr:uid="{CF98AABD-B6DF-493B-8DB4-3101713010F5}"/>
@@ -5245,12 +5257,12 @@
       <c r="C9" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="92" t="s">
         <v>308</v>
       </c>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="88"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="94"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
@@ -5286,60 +5298,60 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="95" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="89"/>
+      <c r="C14" s="95"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="89"/>
-      <c r="C15" s="89"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="95"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="89"/>
-      <c r="C17" s="89"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="89"/>
-      <c r="C18" s="89"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="89"/>
-      <c r="C20" s="89"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="95"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="89"/>
-      <c r="C21" s="89"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="95"/>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="89"/>
-      <c r="C22" s="89"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="95"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="95"/>
+      <c r="C23" s="95"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
     </row>
     <row r="26" spans="2:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
     </row>
     <row r="28" spans="2:3" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="90" t="s">
+      <c r="B28" s="96" t="s">
         <v>327</v>
       </c>
-      <c r="C28" s="90"/>
+      <c r="C28" s="96"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
@@ -5421,12 +5433,12 @@
       <c r="D2" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="97" t="s">
+      <c r="G2" s="98" t="s">
         <v>309</v>
       </c>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="36" t="s">
@@ -5438,10 +5450,10 @@
       <c r="D3" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="102"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
@@ -5453,10 +5465,10 @@
       <c r="D4" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="100"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="102"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="103"/>
     </row>
     <row r="5" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="36" t="s">
@@ -5468,10 +5480,10 @@
       <c r="D5" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="105"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="106"/>
     </row>
     <row r="6" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="36" t="s">
@@ -5505,12 +5517,12 @@
       <c r="D8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="106" t="s">
+      <c r="G8" s="107" t="s">
         <v>248</v>
       </c>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="108"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="108"/>
+      <c r="J8" s="109"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
@@ -5522,10 +5534,10 @@
       <c r="D9" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="109"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="111"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="112"/>
     </row>
     <row r="10" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
@@ -5537,114 +5549,114 @@
       <c r="D10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="109"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="111"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="112"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G11" s="109"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="111"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="112"/>
     </row>
     <row r="12" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G12" s="112"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="114"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="114"/>
+      <c r="I12" s="114"/>
+      <c r="J12" s="115"/>
     </row>
     <row r="13" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="89" t="s">
+      <c r="G14" s="95" t="s">
         <v>249</v>
       </c>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="89"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="95"/>
     </row>
     <row r="16" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G16" s="89"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
     </row>
     <row r="17" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G17" s="89"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="89"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
     </row>
     <row r="18" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G19" s="89" t="s">
+      <c r="G19" s="95" t="s">
         <v>250</v>
       </c>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="89"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="89"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="95"/>
     </row>
     <row r="22" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G22" s="89"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="95"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
     </row>
     <row r="25" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G25" s="96" t="s">
+      <c r="G25" s="97" t="s">
         <v>287</v>
       </c>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
     </row>
     <row r="26" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="97"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="97"/>
     </row>
     <row r="27" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G27" s="96"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="97"/>
     </row>
     <row r="28" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G28" s="96"/>
-      <c r="H28" s="96"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="96"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
     </row>
     <row r="29" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="97"/>
+      <c r="I29" s="97"/>
+      <c r="J29" s="97"/>
     </row>
     <row r="30" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
-      <c r="J30" s="96"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="97"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7274,62 +7286,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="83.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>421</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="G1" s="119" t="s">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="G1" s="120" t="s">
         <v>328</v>
       </c>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="P1" s="118" t="s">
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="P1" s="119" t="s">
         <v>330</v>
       </c>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AI1" s="115" t="s">
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AI1" s="116" t="s">
         <v>310</v>
       </c>
-      <c r="AJ1" s="116"/>
-      <c r="AK1" s="117"/>
+      <c r="AJ1" s="117"/>
+      <c r="AK1" s="118"/>
     </row>
     <row r="33" spans="1:12" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="115" t="s">
+      <c r="A33" s="116" t="s">
         <v>329</v>
       </c>
-      <c r="B33" s="116"/>
-      <c r="C33" s="117"/>
-      <c r="F33" s="115" t="s">
+      <c r="B33" s="117"/>
+      <c r="C33" s="118"/>
+      <c r="F33" s="116" t="s">
         <v>417</v>
       </c>
-      <c r="G33" s="116"/>
-      <c r="H33" s="116"/>
-      <c r="I33" s="116"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="116"/>
-      <c r="L33" s="116"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8482,96 +8494,96 @@
       </c>
     </row>
     <row r="42" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="120" t="s">
+      <c r="A42" s="121" t="s">
         <v>418</v>
       </c>
-      <c r="B42" s="120"/>
-      <c r="C42" s="120"/>
-      <c r="D42" s="120"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
-      <c r="I42" s="121" t="s">
+      <c r="B42" s="121"/>
+      <c r="C42" s="121"/>
+      <c r="D42" s="121"/>
+      <c r="E42" s="121"/>
+      <c r="F42" s="121"/>
+      <c r="G42" s="121"/>
+      <c r="I42" s="122" t="s">
         <v>419</v>
       </c>
-      <c r="J42" s="122"/>
-      <c r="K42" s="122"/>
-      <c r="L42" s="122"/>
-      <c r="M42" s="122"/>
-      <c r="N42" s="122"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="122"/>
-      <c r="Q42" s="122"/>
-      <c r="R42" s="122"/>
-      <c r="S42" s="122"/>
-      <c r="T42" s="122"/>
-      <c r="U42" s="122"/>
-      <c r="V42" s="122"/>
-      <c r="W42" s="122"/>
-      <c r="X42" s="122"/>
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="123"/>
+      <c r="R42" s="123"/>
+      <c r="S42" s="123"/>
+      <c r="T42" s="123"/>
+      <c r="U42" s="123"/>
+      <c r="V42" s="123"/>
+      <c r="W42" s="123"/>
+      <c r="X42" s="123"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A43" s="120"/>
-      <c r="B43" s="120"/>
-      <c r="C43" s="120"/>
-      <c r="D43" s="120"/>
-      <c r="E43" s="120"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="120"/>
-      <c r="I43" s="121"/>
-      <c r="J43" s="122"/>
-      <c r="K43" s="122"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="122"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="122"/>
-      <c r="Q43" s="122"/>
-      <c r="R43" s="122"/>
-      <c r="S43" s="122"/>
-      <c r="T43" s="122"/>
-      <c r="U43" s="122"/>
-      <c r="V43" s="122"/>
-      <c r="W43" s="122"/>
-      <c r="X43" s="122"/>
+      <c r="A43" s="121"/>
+      <c r="B43" s="121"/>
+      <c r="C43" s="121"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="121"/>
+      <c r="I43" s="122"/>
+      <c r="J43" s="123"/>
+      <c r="K43" s="123"/>
+      <c r="L43" s="123"/>
+      <c r="M43" s="123"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="123"/>
+      <c r="Q43" s="123"/>
+      <c r="R43" s="123"/>
+      <c r="S43" s="123"/>
+      <c r="T43" s="123"/>
+      <c r="U43" s="123"/>
+      <c r="V43" s="123"/>
+      <c r="W43" s="123"/>
+      <c r="X43" s="123"/>
     </row>
     <row r="60" spans="9:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I60" s="120" t="s">
+      <c r="I60" s="121" t="s">
         <v>420</v>
       </c>
-      <c r="J60" s="120"/>
-      <c r="K60" s="120"/>
-      <c r="L60" s="120"/>
-      <c r="M60" s="120"/>
-      <c r="N60" s="120"/>
-      <c r="O60" s="120"/>
-      <c r="P60" s="120"/>
-      <c r="Q60" s="120"/>
-      <c r="R60" s="120"/>
-      <c r="S60" s="120"/>
-      <c r="T60" s="120"/>
-      <c r="U60" s="120"/>
-      <c r="V60" s="120"/>
-      <c r="W60" s="120"/>
-      <c r="X60" s="120"/>
+      <c r="J60" s="121"/>
+      <c r="K60" s="121"/>
+      <c r="L60" s="121"/>
+      <c r="M60" s="121"/>
+      <c r="N60" s="121"/>
+      <c r="O60" s="121"/>
+      <c r="P60" s="121"/>
+      <c r="Q60" s="121"/>
+      <c r="R60" s="121"/>
+      <c r="S60" s="121"/>
+      <c r="T60" s="121"/>
+      <c r="U60" s="121"/>
+      <c r="V60" s="121"/>
+      <c r="W60" s="121"/>
+      <c r="X60" s="121"/>
     </row>
     <row r="61" spans="9:24" x14ac:dyDescent="0.25">
-      <c r="I61" s="120"/>
-      <c r="J61" s="120"/>
-      <c r="K61" s="120"/>
-      <c r="L61" s="120"/>
-      <c r="M61" s="120"/>
-      <c r="N61" s="120"/>
-      <c r="O61" s="120"/>
-      <c r="P61" s="120"/>
-      <c r="Q61" s="120"/>
-      <c r="R61" s="120"/>
-      <c r="S61" s="120"/>
-      <c r="T61" s="120"/>
-      <c r="U61" s="120"/>
-      <c r="V61" s="120"/>
-      <c r="W61" s="120"/>
-      <c r="X61" s="120"/>
+      <c r="I61" s="121"/>
+      <c r="J61" s="121"/>
+      <c r="K61" s="121"/>
+      <c r="L61" s="121"/>
+      <c r="M61" s="121"/>
+      <c r="N61" s="121"/>
+      <c r="O61" s="121"/>
+      <c r="P61" s="121"/>
+      <c r="Q61" s="121"/>
+      <c r="R61" s="121"/>
+      <c r="S61" s="121"/>
+      <c r="T61" s="121"/>
+      <c r="U61" s="121"/>
+      <c r="V61" s="121"/>
+      <c r="W61" s="121"/>
+      <c r="X61" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8599,36 +8611,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
       <c r="H1" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="124" t="s">
         <v>429</v>
       </c>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="124" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -8872,23 +8884,23 @@
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="125" t="s">
+      <c r="B23" s="124" t="s">
         <v>473</v>
       </c>
-      <c r="C23" s="126"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="125" t="s">
+      <c r="B24" s="124" t="s">
         <v>474</v>
       </c>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -8972,23 +8984,23 @@
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="125" t="s">
+      <c r="B32" s="124" t="s">
         <v>484</v>
       </c>
-      <c r="C32" s="126"/>
-      <c r="D32" s="126"/>
-      <c r="E32" s="126"/>
+      <c r="C32" s="125"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="125" t="s">
+      <c r="B33" s="124" t="s">
         <v>485</v>
       </c>
-      <c r="C33" s="126"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="126"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -9042,23 +9054,23 @@
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="125" t="s">
+      <c r="B38" s="124" t="s">
         <v>487</v>
       </c>
-      <c r="C38" s="126"/>
-      <c r="D38" s="126"/>
-      <c r="E38" s="126"/>
+      <c r="C38" s="125"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="125"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="125" t="s">
+      <c r="B39" s="124" t="s">
         <v>488</v>
       </c>
-      <c r="C39" s="126"/>
-      <c r="D39" s="126"/>
-      <c r="E39" s="126"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="125"/>
+      <c r="E39" s="125"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -9112,23 +9124,23 @@
       <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="125" t="s">
+      <c r="B44" s="124" t="s">
         <v>492</v>
       </c>
-      <c r="C44" s="126"/>
-      <c r="D44" s="126"/>
-      <c r="E44" s="126"/>
+      <c r="C44" s="125"/>
+      <c r="D44" s="125"/>
+      <c r="E44" s="125"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="125" t="s">
+      <c r="B45" s="124" t="s">
         <v>493</v>
       </c>
-      <c r="C45" s="126"/>
-      <c r="D45" s="126"/>
-      <c r="E45" s="126"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
+      <c r="E45" s="125"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -9185,23 +9197,23 @@
       <c r="A50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="125" t="s">
+      <c r="B50" s="124" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="126"/>
-      <c r="D50" s="126"/>
-      <c r="E50" s="126"/>
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="125" t="s">
+      <c r="B51" s="124" t="s">
         <v>499</v>
       </c>
-      <c r="C51" s="126"/>
-      <c r="D51" s="126"/>
-      <c r="E51" s="126"/>
+      <c r="C51" s="125"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="125"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -9280,23 +9292,23 @@
       <c r="A58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="125" t="s">
+      <c r="B58" s="124" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="126"/>
-      <c r="D58" s="126"/>
-      <c r="E58" s="126"/>
+      <c r="C58" s="125"/>
+      <c r="D58" s="125"/>
+      <c r="E58" s="125"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="125" t="s">
+      <c r="B59" s="124" t="s">
         <v>507</v>
       </c>
-      <c r="C59" s="126"/>
-      <c r="D59" s="126"/>
-      <c r="E59" s="126"/>
+      <c r="C59" s="125"/>
+      <c r="D59" s="125"/>
+      <c r="E59" s="125"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -9350,23 +9362,23 @@
       <c r="A64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="125" t="s">
+      <c r="B64" s="124" t="s">
         <v>512</v>
       </c>
-      <c r="C64" s="126"/>
-      <c r="D64" s="126"/>
-      <c r="E64" s="126"/>
+      <c r="C64" s="125"/>
+      <c r="D64" s="125"/>
+      <c r="E64" s="125"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="125" t="s">
+      <c r="B65" s="124" t="s">
         <v>513</v>
       </c>
-      <c r="C65" s="126"/>
-      <c r="D65" s="126"/>
-      <c r="E65" s="126"/>
+      <c r="C65" s="125"/>
+      <c r="D65" s="125"/>
+      <c r="E65" s="125"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
@@ -9445,23 +9457,23 @@
       <c r="A72" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B72" s="125" t="s">
+      <c r="B72" s="124" t="s">
         <v>519</v>
       </c>
-      <c r="C72" s="126"/>
-      <c r="D72" s="126"/>
-      <c r="E72" s="126"/>
+      <c r="C72" s="125"/>
+      <c r="D72" s="125"/>
+      <c r="E72" s="125"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B73" s="125" t="s">
+      <c r="B73" s="124" t="s">
         <v>520</v>
       </c>
-      <c r="C73" s="126"/>
-      <c r="D73" s="126"/>
-      <c r="E73" s="126"/>
+      <c r="C73" s="125"/>
+      <c r="D73" s="125"/>
+      <c r="E73" s="125"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
@@ -9515,23 +9527,23 @@
       <c r="A78" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B78" s="125" t="s">
+      <c r="B78" s="124" t="s">
         <v>525</v>
       </c>
-      <c r="C78" s="126"/>
-      <c r="D78" s="126"/>
-      <c r="E78" s="126"/>
+      <c r="C78" s="125"/>
+      <c r="D78" s="125"/>
+      <c r="E78" s="125"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B79" s="125" t="s">
+      <c r="B79" s="124" t="s">
         <v>526</v>
       </c>
-      <c r="C79" s="126"/>
-      <c r="D79" s="126"/>
-      <c r="E79" s="126"/>
+      <c r="C79" s="125"/>
+      <c r="D79" s="125"/>
+      <c r="E79" s="125"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
@@ -9643,23 +9655,23 @@
       <c r="A89" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B89" s="125" t="s">
+      <c r="B89" s="124" t="s">
         <v>538</v>
       </c>
-      <c r="C89" s="126"/>
-      <c r="D89" s="126"/>
-      <c r="E89" s="126"/>
+      <c r="C89" s="125"/>
+      <c r="D89" s="125"/>
+      <c r="E89" s="125"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B90" s="125" t="s">
+      <c r="B90" s="124" t="s">
         <v>539</v>
       </c>
-      <c r="C90" s="126"/>
-      <c r="D90" s="126"/>
-      <c r="E90" s="126"/>
+      <c r="C90" s="125"/>
+      <c r="D90" s="125"/>
+      <c r="E90" s="125"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
@@ -9741,23 +9753,23 @@
       <c r="A97" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B97" s="125" t="s">
+      <c r="B97" s="124" t="s">
         <v>548</v>
       </c>
-      <c r="C97" s="126"/>
-      <c r="D97" s="126"/>
-      <c r="E97" s="126"/>
+      <c r="C97" s="125"/>
+      <c r="D97" s="125"/>
+      <c r="E97" s="125"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B98" s="125" t="s">
+      <c r="B98" s="124" t="s">
         <v>549</v>
       </c>
-      <c r="C98" s="126"/>
-      <c r="D98" s="126"/>
-      <c r="E98" s="126"/>
+      <c r="C98" s="125"/>
+      <c r="D98" s="125"/>
+      <c r="E98" s="125"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
@@ -9864,23 +9876,23 @@
       <c r="A107" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B107" s="125" t="s">
+      <c r="B107" s="124" t="s">
         <v>555</v>
       </c>
-      <c r="C107" s="126"/>
-      <c r="D107" s="126"/>
-      <c r="E107" s="126"/>
+      <c r="C107" s="125"/>
+      <c r="D107" s="125"/>
+      <c r="E107" s="125"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B108" s="125" t="s">
+      <c r="B108" s="124" t="s">
         <v>556</v>
       </c>
-      <c r="C108" s="126"/>
-      <c r="D108" s="126"/>
-      <c r="E108" s="126"/>
+      <c r="C108" s="125"/>
+      <c r="D108" s="125"/>
+      <c r="E108" s="125"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
@@ -9956,23 +9968,23 @@
       <c r="A115" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B115" s="125" t="s">
+      <c r="B115" s="124" t="s">
         <v>563</v>
       </c>
-      <c r="C115" s="126"/>
-      <c r="D115" s="126"/>
-      <c r="E115" s="126"/>
+      <c r="C115" s="125"/>
+      <c r="D115" s="125"/>
+      <c r="E115" s="125"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B116" s="125" t="s">
+      <c r="B116" s="124" t="s">
         <v>564</v>
       </c>
-      <c r="C116" s="126"/>
-      <c r="D116" s="126"/>
-      <c r="E116" s="126"/>
+      <c r="C116" s="125"/>
+      <c r="D116" s="125"/>
+      <c r="E116" s="125"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
@@ -10062,23 +10074,23 @@
       <c r="A124" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B124" s="125" t="s">
+      <c r="B124" s="124" t="s">
         <v>572</v>
       </c>
-      <c r="C124" s="126"/>
-      <c r="D124" s="126"/>
-      <c r="E124" s="126"/>
+      <c r="C124" s="125"/>
+      <c r="D124" s="125"/>
+      <c r="E124" s="125"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B125" s="125" t="s">
+      <c r="B125" s="124" t="s">
         <v>573</v>
       </c>
-      <c r="C125" s="126"/>
-      <c r="D125" s="126"/>
-      <c r="E125" s="126"/>
+      <c r="C125" s="125"/>
+      <c r="D125" s="125"/>
+      <c r="E125" s="125"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
@@ -10165,23 +10177,23 @@
       <c r="A133" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="125" t="s">
+      <c r="B133" s="124" t="s">
         <v>580</v>
       </c>
-      <c r="C133" s="126"/>
-      <c r="D133" s="126"/>
-      <c r="E133" s="126"/>
+      <c r="C133" s="125"/>
+      <c r="D133" s="125"/>
+      <c r="E133" s="125"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B134" s="125" t="s">
+      <c r="B134" s="124" t="s">
         <v>581</v>
       </c>
-      <c r="C134" s="126"/>
-      <c r="D134" s="126"/>
-      <c r="E134" s="126"/>
+      <c r="C134" s="125"/>
+      <c r="D134" s="125"/>
+      <c r="E134" s="125"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
@@ -10333,39 +10345,39 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B133:E133"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B89:E89"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="B78:E78"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B72:E72"/>
     <mergeCell ref="B73:E73"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B133:E133"/>
+    <mergeCell ref="B134:E134"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10796,14 +10808,14 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="124" t="s">
+      <c r="I9" s="86" t="s">
         <v>217</v>
       </c>
-      <c r="J9" s="124"/>
-      <c r="K9" s="124"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="M9" s="86"/>
+      <c r="N9" s="86"/>
     </row>
     <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="I11" s="21" t="s">
@@ -10865,4 +10877,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" enabled="0" method="" siteId="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/docs/Datathon Project.xlsx
+++ b/docs/Datathon Project.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoa-my.sharepoint.com/personal/ghin287_uoa_auckland_ac_nz/Documents/Documents/University/Datathon temp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anchit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{11450F02-EE81-4929-8FBE-319E30382959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F1E792-5F51-4658-971C-86D2D19E5EB6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3FBC14-72BA-42A7-A028-E7A78C040042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Overview" sheetId="2" r:id="rId1"/>
     <sheet name="MVP Requirements + Design" sheetId="1" r:id="rId2"/>
     <sheet name="Project Plan &amp; Sprint Meetings" sheetId="3" r:id="rId3"/>
-    <sheet name="RAID Logs " sheetId="9" r:id="rId4"/>
-    <sheet name="Team Progress View- JIRA SCRUM" sheetId="11" r:id="rId5"/>
-    <sheet name="JIRA Task Breakdown" sheetId="12" r:id="rId6"/>
-    <sheet name="Data Model" sheetId="7" r:id="rId7"/>
-    <sheet name="Tasks" sheetId="6" state="hidden" r:id="rId8"/>
-    <sheet name="Team votes &amp; Misc Info" sheetId="5" r:id="rId9"/>
+    <sheet name="Team Progress View- JIRA SCRUM" sheetId="11" r:id="rId4"/>
+    <sheet name="RAID Logs " sheetId="9" r:id="rId5"/>
+    <sheet name="Risk Matrix" sheetId="13" r:id="rId6"/>
+    <sheet name="JIRA Task Breakdown" sheetId="12" r:id="rId7"/>
+    <sheet name="Data Model" sheetId="7" r:id="rId8"/>
+    <sheet name="Tasks" sheetId="6" state="hidden" r:id="rId9"/>
+    <sheet name="Team votes &amp; Misc Info" sheetId="5" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RAID Logs '!$A$1:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RAID Logs '!$A$1:$M$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2046,7 +2047,7 @@
     <t>This is the extraction used by fct_judgment</t>
   </si>
   <si>
-    <t>6 Gramss - Team 4</t>
+    <t>6 gramss- Team 4</t>
   </si>
 </sst>
 </file>
@@ -2056,7 +2057,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2077,6 +2078,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -2104,38 +2106,38 @@
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF2E2A6B"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2606,7 +2608,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2829,9 +2831,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2950,8 +2949,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2985,6 +2984,34 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3048,34 +3075,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4B6B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3572,7 +3571,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>7484</xdr:rowOff>
+      <xdr:rowOff>39234</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3660,7 +3659,7 @@
       <xdr:col>36</xdr:col>
       <xdr:colOff>3054964</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>76162</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3683,8 +3682,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30346650" y="1060450"/>
-          <a:ext cx="9316064" cy="5226012"/>
+          <a:off x="30353000" y="482600"/>
+          <a:ext cx="9322414" cy="5162550"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3933,7 +3932,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Summary"/>
@@ -4349,9 +4348,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4389,7 +4388,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4495,7 +4494,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4637,7 +4636,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4646,103 +4645,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70241A6B-2CF1-42DB-9288-7E14FFCD0A5F}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.26953125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.42578125" customWidth="1"/>
-    <col min="2" max="2" width="73.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="73.54296875" customWidth="1"/>
     <col min="4" max="4" width="70" customWidth="1"/>
-    <col min="5" max="5" width="49.85546875" customWidth="1"/>
-    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.81640625" customWidth="1"/>
+    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:7" ht="54.65" customHeight="1">
+      <c r="A1" s="89" t="s">
         <v>263</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="39" t="s">
         <v>78</v>
       </c>
       <c r="B3" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="89" t="s">
         <v>587</v>
       </c>
-      <c r="E3" s="127"/>
+      <c r="E3" s="90"/>
       <c r="F3" s="3"/>
       <c r="G3" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="39" t="s">
         <v>75</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="90"/>
-      <c r="E4" s="127"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="90"/>
       <c r="F4" s="3"/>
       <c r="G4" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="39" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="127"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="90"/>
       <c r="F5" s="3"/>
       <c r="G5" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="39" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="90"/>
-      <c r="E6" s="127"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="90"/>
       <c r="F6" s="3"/>
       <c r="G6" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="50"/>
       <c r="B7" s="51"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="127"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="90"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="10" spans="1:7" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="89" t="s">
+    <row r="10" spans="1:7" ht="62.5" customHeight="1">
+      <c r="A10" s="88" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89" t="s">
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-    </row>
-    <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+    </row>
+    <row r="11" spans="1:7" ht="27" customHeight="1">
       <c r="A11" s="56" t="s">
         <v>18</v>
       </c>
@@ -4762,7 +4761,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.5">
       <c r="A12" s="52" t="s">
         <v>8</v>
       </c>
@@ -4782,7 +4781,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="72.5">
       <c r="A13" s="32" t="s">
         <v>9</v>
       </c>
@@ -4802,7 +4801,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.5">
       <c r="A14" s="32" t="s">
         <v>6</v>
       </c>
@@ -4822,7 +4821,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="29">
       <c r="A15" s="32" t="s">
         <v>7</v>
       </c>
@@ -4842,7 +4841,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="32" t="s">
         <v>4</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="32" t="s">
         <v>5</v>
       </c>
@@ -4880,13 +4879,13 @@
         <v>315</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="87" t="s">
+    <row r="20" spans="1:6">
+      <c r="A20" s="86" t="s">
         <v>258</v>
       </c>
-      <c r="B20" s="88"/>
-    </row>
-    <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="87"/>
+    </row>
+    <row r="21" spans="1:6" ht="22.5" customHeight="1">
       <c r="A21" s="57" t="s">
         <v>18</v>
       </c>
@@ -4894,7 +4893,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="29">
       <c r="A22" s="79" t="s">
         <v>289</v>
       </c>
@@ -4902,7 +4901,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" s="78" t="s">
         <v>260</v>
       </c>
@@ -4910,7 +4909,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="78" t="s">
         <v>79</v>
       </c>
@@ -4918,7 +4917,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" s="32" t="s">
         <v>90</v>
       </c>
@@ -4926,7 +4925,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" s="32" t="s">
         <v>89</v>
       </c>
@@ -4934,7 +4933,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" s="32" t="s">
         <v>91</v>
       </c>
@@ -4942,7 +4941,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" s="32" t="s">
         <v>288</v>
       </c>
@@ -4950,7 +4949,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" s="80" t="s">
         <v>70</v>
       </c>
@@ -4958,7 +4957,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" s="81" t="s">
         <v>311</v>
       </c>
@@ -4966,7 +4965,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2">
       <c r="A33" s="81" t="s">
         <v>73</v>
       </c>
@@ -4974,7 +4973,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="A34" s="81" t="s">
         <v>313</v>
       </c>
@@ -4982,7 +4981,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:2" ht="14.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A20:B20"/>
@@ -5000,7 +4999,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="17" operator="equal" id="{7BD1A13A-120D-40DD-B12D-5F9AB267715E}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$5</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5010,7 +5009,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="18" operator="equal" id="{076DA4E1-6EA3-4736-A521-E55519746227}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$4</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5020,7 +5019,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="19" operator="equal" id="{79C7FFBE-7047-4DE6-BD27-F3176BD03C10}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$3</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5030,7 +5029,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="20" operator="equal" id="{EA3FC8D4-0F37-461D-91BA-BA636672330C}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$2</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5047,7 +5046,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{202D5370-0CA3-4D2C-8044-CEDD61DF71E6}">
           <x14:formula1>
-            <xm:f>'Team votes &amp; Misc Info'!$P$2:$P$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$2:$J$5</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B7</xm:sqref>
         </x14:dataValidation>
@@ -5057,24 +5056,181 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DCDC7C-55B3-416C-9E03-05A0A063B246}">
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.453125" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="6.1796875" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" customWidth="1"/>
+    <col min="17" max="17" width="18.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="42">
+        <v>1</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42">
+        <v>2</v>
+      </c>
+      <c r="E2" s="42">
+        <v>1</v>
+      </c>
+      <c r="F2" s="42">
+        <v>2</v>
+      </c>
+      <c r="G2" s="42">
+        <v>2</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="N2" s="42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="42">
+        <v>2</v>
+      </c>
+      <c r="C3" s="42">
+        <v>1</v>
+      </c>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="J3" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="N3" s="42" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42">
+        <v>2</v>
+      </c>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42">
+        <v>2</v>
+      </c>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="J4" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="N4" s="42" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42">
+        <v>1</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42">
+        <v>1</v>
+      </c>
+      <c r="G5" s="42">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="N5" s="42" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="29.15" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB583F5E-2C32-4E7A-802B-32AB9008611B}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="110.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.453125" customWidth="1"/>
+    <col min="2" max="2" width="110.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.453125" customWidth="1"/>
     <col min="9" max="9" width="51" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.54296875" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="43" customHeight="1">
       <c r="A1" s="28" t="s">
         <v>277</v>
       </c>
@@ -5098,7 +5254,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="43.5">
       <c r="A2" s="32">
         <v>1</v>
       </c>
@@ -5121,7 +5277,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="29">
       <c r="A3" s="32">
         <v>2</v>
       </c>
@@ -5144,7 +5300,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="29">
       <c r="A4" s="32">
         <v>3</v>
       </c>
@@ -5167,7 +5323,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="29">
       <c r="A5" s="32">
         <v>4</v>
       </c>
@@ -5190,7 +5346,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="32">
         <v>5</v>
       </c>
@@ -5213,7 +5369,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="29">
       <c r="A7" s="32">
         <v>6</v>
       </c>
@@ -5236,7 +5392,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="87">
       <c r="A8" s="32">
         <v>7</v>
       </c>
@@ -5247,7 +5403,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="72.5">
       <c r="A9" s="32">
         <v>8</v>
       </c>
@@ -5257,14 +5413,14 @@
       <c r="C9" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="92" t="s">
+      <c r="F9" s="91" t="s">
         <v>308</v>
       </c>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="94"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="93"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="32">
         <v>9</v>
       </c>
@@ -5275,7 +5431,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="32">
         <v>10</v>
       </c>
@@ -5286,7 +5442,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="32">
         <v>11</v>
       </c>
@@ -5297,81 +5453,81 @@
         <v>273</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="95" t="s">
+    <row r="14" spans="1:9" ht="14.5" customHeight="1">
+      <c r="B14" s="94" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="95"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="95"/>
-      <c r="C15" s="95"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="95"/>
-      <c r="C16" s="95"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="95"/>
-      <c r="C20" s="95"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="95"/>
-      <c r="C21" s="95"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="95"/>
-      <c r="C22" s="95"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="95"/>
-      <c r="C23" s="95"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="95"/>
-      <c r="C24" s="95"/>
-    </row>
-    <row r="26" spans="2:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="94"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="94"/>
+      <c r="C17" s="94"/>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="94"/>
+      <c r="C18" s="94"/>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" s="94"/>
+      <c r="C20" s="94"/>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" s="94"/>
+      <c r="C21" s="94"/>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" s="94"/>
+      <c r="C22" s="94"/>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" s="94"/>
+      <c r="C23" s="94"/>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+    </row>
+    <row r="26" spans="2:3" ht="14.5" customHeight="1"/>
+    <row r="27" spans="2:3">
       <c r="B27" s="3"/>
     </row>
-    <row r="28" spans="2:3" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="96" t="s">
+    <row r="28" spans="2:3" ht="72.650000000000006" customHeight="1">
+      <c r="B28" s="95" t="s">
         <v>327</v>
       </c>
-      <c r="C28" s="96"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="95"/>
+    </row>
+    <row r="29" spans="2:3">
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3">
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3">
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3">
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2">
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2">
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2">
       <c r="B35" s="3"/>
     </row>
   </sheetData>
@@ -5388,7 +5544,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{31D5797D-E614-4CAC-B58E-5CEC9DEBE9E5}">
           <x14:formula1>
-            <xm:f>'Team votes &amp; Misc Info'!$T$2:$T$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$N$2:$N$5</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C12</xm:sqref>
         </x14:dataValidation>
@@ -5401,17 +5557,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA72A998-9D73-4F3B-A55F-A4F70ED3DBFB}">
   <dimension ref="B1:J30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="2" width="44.42578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.1796875" customWidth="1"/>
+    <col min="2" max="2" width="44.453125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="39.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" customWidth="1"/>
+    <col min="6" max="6" width="23.81640625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:10" ht="30.65" customHeight="1">
       <c r="B1" s="26" t="s">
         <v>107</v>
       </c>
@@ -5423,7 +5579,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="2:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" ht="29.15" customHeight="1">
       <c r="B2" s="36" t="s">
         <v>227</v>
       </c>
@@ -5433,14 +5589,14 @@
       <c r="D2" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G2" s="98" t="s">
+      <c r="G2" s="97" t="s">
         <v>309</v>
       </c>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="100"/>
-    </row>
-    <row r="3" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="99"/>
+    </row>
+    <row r="3" spans="2:10" ht="14.5" customHeight="1">
       <c r="B3" s="36" t="s">
         <v>100</v>
       </c>
@@ -5450,12 +5606,12 @@
       <c r="D3" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="103"/>
-    </row>
-    <row r="4" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="100"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="102"/>
+    </row>
+    <row r="4" spans="2:10" ht="14.5" customHeight="1">
       <c r="B4" s="36" t="s">
         <v>317</v>
       </c>
@@ -5465,12 +5621,12 @@
       <c r="D4" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G4" s="101"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="103"/>
-    </row>
-    <row r="5" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="100"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
+    </row>
+    <row r="5" spans="2:10" ht="14.5" customHeight="1">
       <c r="B5" s="36" t="s">
         <v>104</v>
       </c>
@@ -5480,12 +5636,12 @@
       <c r="D5" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G5" s="104"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="106"/>
-    </row>
-    <row r="6" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="G5" s="103"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="105"/>
+    </row>
+    <row r="6" spans="2:10" ht="29">
       <c r="B6" s="36" t="s">
         <v>318</v>
       </c>
@@ -5496,7 +5652,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10">
       <c r="B7" s="36" t="s">
         <v>105</v>
       </c>
@@ -5507,7 +5663,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="14.5" customHeight="1">
       <c r="B8" s="36" t="s">
         <v>422</v>
       </c>
@@ -5517,14 +5673,14 @@
       <c r="D8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="107" t="s">
+      <c r="G8" s="106" t="s">
         <v>248</v>
       </c>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="109"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="108"/>
+    </row>
+    <row r="9" spans="2:10">
       <c r="B9" s="36" t="s">
         <v>99</v>
       </c>
@@ -5534,12 +5690,12 @@
       <c r="D9" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="110"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="112"/>
-    </row>
-    <row r="10" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="109"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="111"/>
+    </row>
+    <row r="10" spans="2:10" ht="14.5" customHeight="1">
       <c r="B10" s="36" t="s">
         <v>252</v>
       </c>
@@ -5549,114 +5705,114 @@
       <c r="D10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="110"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="112"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G11" s="110"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="112"/>
-    </row>
-    <row r="12" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G12" s="113"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="115"/>
-    </row>
-    <row r="13" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G14" s="95" t="s">
+      <c r="G10" s="109"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="111"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="G11" s="109"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="111"/>
+    </row>
+    <row r="12" spans="2:10" ht="14.5" customHeight="1">
+      <c r="G12" s="112"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="114"/>
+    </row>
+    <row r="13" spans="2:10" ht="14.5" customHeight="1"/>
+    <row r="14" spans="2:10" ht="14.5" customHeight="1">
+      <c r="G14" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="95"/>
-    </row>
-    <row r="16" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-    </row>
-    <row r="17" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-    </row>
-    <row r="18" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G19" s="95" t="s">
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+    </row>
+    <row r="16" spans="2:10" ht="14.5" customHeight="1">
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+    </row>
+    <row r="17" spans="7:10" ht="14.5" customHeight="1">
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+    </row>
+    <row r="18" spans="7:10" ht="14.5" customHeight="1"/>
+    <row r="19" spans="7:10" ht="14.5" customHeight="1">
+      <c r="G19" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
-    </row>
-    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-    </row>
-    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G21" s="95"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="95"/>
-    </row>
-    <row r="22" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G22" s="95"/>
-      <c r="H22" s="95"/>
-      <c r="I22" s="95"/>
-      <c r="J22" s="95"/>
-    </row>
-    <row r="25" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G25" s="97" t="s">
+      <c r="H19" s="94"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+    </row>
+    <row r="20" spans="7:10">
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="94"/>
+      <c r="J20" s="94"/>
+    </row>
+    <row r="21" spans="7:10">
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+    </row>
+    <row r="22" spans="7:10" ht="14.5" customHeight="1">
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+    </row>
+    <row r="25" spans="7:10" ht="14.5" customHeight="1">
+      <c r="G25" s="96" t="s">
         <v>287</v>
       </c>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="97"/>
-    </row>
-    <row r="26" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="97"/>
-    </row>
-    <row r="27" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G27" s="97"/>
-      <c r="H27" s="97"/>
-      <c r="I27" s="97"/>
-      <c r="J27" s="97"/>
-    </row>
-    <row r="28" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G28" s="97"/>
-      <c r="H28" s="97"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-    </row>
-    <row r="29" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G29" s="97"/>
-      <c r="H29" s="97"/>
-      <c r="I29" s="97"/>
-      <c r="J29" s="97"/>
-    </row>
-    <row r="30" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G30" s="97"/>
-      <c r="H30" s="97"/>
-      <c r="I30" s="97"/>
-      <c r="J30" s="97"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+    </row>
+    <row r="26" spans="7:10">
+      <c r="G26" s="96"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96"/>
+    </row>
+    <row r="27" spans="7:10">
+      <c r="G27" s="96"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+    </row>
+    <row r="28" spans="7:10" ht="14.5" customHeight="1">
+      <c r="G28" s="96"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+    </row>
+    <row r="29" spans="7:10">
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+    </row>
+    <row r="30" spans="7:10">
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5674,7 +5830,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="21" operator="equal" id="{16C90F88-1C9A-4B9F-A9E7-62974754B8D2}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$5</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5684,7 +5840,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="22" operator="equal" id="{647C75D8-A125-43F4-A4DC-49E0A81342C2}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$4</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5694,7 +5850,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="23" operator="equal" id="{0B57660D-79DF-4A49-8F18-61E239F80CC1}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$3</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5704,7 +5860,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="24" operator="equal" id="{EF17B7A9-88EE-4B8B-A2AA-A1011EA02AFB}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$2</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5721,7 +5877,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{327C2ED6-6BDC-4E31-8F6D-8D1611429568}">
           <x14:formula1>
-            <xm:f>'Team votes &amp; Misc Info'!$P$2:$P$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$2:$J$5</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D10</xm:sqref>
         </x14:dataValidation>
@@ -5732,28 +5888,115 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6A8ABF-E61F-4C75-ADCE-19B4345AB4F4}">
+  <dimension ref="A1:AK33"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="37.54296875" customWidth="1"/>
+    <col min="2" max="2" width="35.1796875" customWidth="1"/>
+    <col min="3" max="3" width="43.54296875" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="8" max="8" width="41.1796875" customWidth="1"/>
+    <col min="35" max="35" width="42.26953125" customWidth="1"/>
+    <col min="36" max="36" width="48.453125" customWidth="1"/>
+    <col min="37" max="37" width="66.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" ht="37.5" customHeight="1">
+      <c r="A1" s="118" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="G1" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="P1" s="118" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AI1" s="115" t="s">
+        <v>310</v>
+      </c>
+      <c r="AJ1" s="116"/>
+      <c r="AK1" s="117"/>
+    </row>
+    <row r="33" spans="1:12" ht="42.65" customHeight="1">
+      <c r="A33" s="115" t="s">
+        <v>329</v>
+      </c>
+      <c r="B33" s="116"/>
+      <c r="C33" s="117"/>
+      <c r="F33" s="115" t="s">
+        <v>417</v>
+      </c>
+      <c r="G33" s="116"/>
+      <c r="H33" s="116"/>
+      <c r="I33" s="116"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="116"/>
+      <c r="L33" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="AI1:AK1"/>
+    <mergeCell ref="P1:AE1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:N1"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="F33:L33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}">
   <dimension ref="A1:T77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="3" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" customWidth="1"/>
-    <col min="18" max="18" width="20.42578125" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="21.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.26953125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" style="3" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.54296875" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" customWidth="1"/>
+    <col min="18" max="18" width="20.453125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="21.54296875" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="26">
       <c r="A1" s="27" t="s">
         <v>108</v>
       </c>
@@ -5803,7 +6046,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="37.5">
       <c r="A2" s="71" t="s">
         <v>119</v>
       </c>
@@ -5853,7 +6096,7 @@
       </c>
       <c r="T2" s="16"/>
     </row>
-    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="29">
       <c r="A3" s="71" t="s">
         <v>126</v>
       </c>
@@ -5903,7 +6146,7 @@
       </c>
       <c r="T3" s="16"/>
     </row>
-    <row r="4" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="43.5">
       <c r="A4" s="71" t="s">
         <v>129</v>
       </c>
@@ -5953,7 +6196,7 @@
       </c>
       <c r="T4" s="16"/>
     </row>
-    <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="43.5">
       <c r="A5" s="71" t="s">
         <v>135</v>
       </c>
@@ -6003,7 +6246,7 @@
       </c>
       <c r="T5" s="16"/>
     </row>
-    <row r="6" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="58">
       <c r="A6" s="61" t="s">
         <v>140</v>
       </c>
@@ -6053,7 +6296,7 @@
       </c>
       <c r="T6" s="16"/>
     </row>
-    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="43.5">
       <c r="A7" s="71" t="s">
         <v>140</v>
       </c>
@@ -6103,7 +6346,7 @@
       </c>
       <c r="T7" s="16"/>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="43.5">
       <c r="A8" s="71" t="s">
         <v>144</v>
       </c>
@@ -6153,7 +6396,7 @@
       </c>
       <c r="T8" s="16"/>
     </row>
-    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="43.5">
       <c r="A9" s="71" t="s">
         <v>147</v>
       </c>
@@ -6199,7 +6442,7 @@
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
     </row>
-    <row r="10" spans="1:20" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="72.5">
       <c r="A10" s="71" t="s">
         <v>150</v>
       </c>
@@ -6249,7 +6492,7 @@
       </c>
       <c r="T10" s="16"/>
     </row>
-    <row r="11" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="29">
       <c r="A11" s="71" t="s">
         <v>171</v>
       </c>
@@ -6291,7 +6534,7 @@
       </c>
       <c r="T11" s="16"/>
     </row>
-    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="29">
       <c r="A12" s="71" t="s">
         <v>175</v>
       </c>
@@ -6333,7 +6576,7 @@
       </c>
       <c r="T12" s="16"/>
     </row>
-    <row r="13" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="25">
       <c r="A13" s="71" t="s">
         <v>178</v>
       </c>
@@ -6366,7 +6609,7 @@
       </c>
       <c r="T13" s="16"/>
     </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="29">
       <c r="A14" s="71" t="s">
         <v>181</v>
       </c>
@@ -6399,7 +6642,7 @@
       </c>
       <c r="T14" s="16"/>
     </row>
-    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="29">
       <c r="A15" s="71" t="s">
         <v>182</v>
       </c>
@@ -6433,7 +6676,7 @@
       </c>
       <c r="T15" s="16"/>
     </row>
-    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="29">
       <c r="A16" s="71" t="s">
         <v>183</v>
       </c>
@@ -6467,7 +6710,7 @@
       </c>
       <c r="T16" s="16"/>
     </row>
-    <row r="17" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="58">
       <c r="A17" s="71" t="s">
         <v>184</v>
       </c>
@@ -6497,7 +6740,7 @@
       <c r="S17" s="16"/>
       <c r="T17" s="16"/>
     </row>
-    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="29">
       <c r="A18" s="71" t="s">
         <v>185</v>
       </c>
@@ -6527,7 +6770,7 @@
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
     </row>
-    <row r="19" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="43.5">
       <c r="A19" s="71" t="s">
         <v>186</v>
       </c>
@@ -6556,7 +6799,7 @@
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
     </row>
-    <row r="20" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="43.5">
       <c r="A20" s="71" t="s">
         <v>298</v>
       </c>
@@ -6586,7 +6829,7 @@
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
     </row>
-    <row r="21" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="29">
       <c r="A21" s="71" t="s">
         <v>187</v>
       </c>
@@ -6620,7 +6863,7 @@
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
     </row>
-    <row r="22" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="43.5">
       <c r="A22" s="71" t="s">
         <v>189</v>
       </c>
@@ -6654,7 +6897,7 @@
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
     </row>
-    <row r="23" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="43.5">
       <c r="A23" s="71" t="s">
         <v>190</v>
       </c>
@@ -6688,7 +6931,7 @@
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
     </row>
-    <row r="24" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="43.5">
       <c r="A24" s="71" t="s">
         <v>191</v>
       </c>
@@ -6722,7 +6965,7 @@
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
     </row>
-    <row r="25" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="29">
       <c r="A25" s="71" t="s">
         <v>192</v>
       </c>
@@ -6758,7 +7001,7 @@
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20">
       <c r="A26" s="71" t="s">
         <v>196</v>
       </c>
@@ -6794,7 +7037,7 @@
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
     </row>
-    <row r="27" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="58">
       <c r="A27" s="71" t="s">
         <v>199</v>
       </c>
@@ -6826,7 +7069,7 @@
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
     </row>
-    <row r="28" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="58">
       <c r="A28" s="71" t="s">
         <v>201</v>
       </c>
@@ -6858,24 +7101,24 @@
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20">
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20">
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
       <c r="T31" s="16" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20">
       <c r="C32"/>
       <c r="D32" s="16"/>
       <c r="F32" s="3"/>
@@ -6887,7 +7130,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20">
       <c r="C33"/>
       <c r="D33" s="16"/>
       <c r="F33" s="3"/>
@@ -6899,7 +7142,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20">
       <c r="C34"/>
       <c r="D34" s="16"/>
       <c r="F34" s="3"/>
@@ -6911,7 +7154,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="25">
       <c r="C35"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -6922,7 +7165,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20">
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="R36" s="16"/>
@@ -6931,7 +7174,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20">
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="R37" s="16"/>
@@ -6940,11 +7183,11 @@
         <v>206</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20">
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20">
       <c r="A39" s="14"/>
       <c r="B39" s="13"/>
       <c r="D39" s="59"/>
@@ -6960,47 +7203,47 @@
       <c r="S39" s="13"/>
       <c r="T39" s="13"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20">
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20">
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20">
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20">
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20">
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20">
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20">
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20">
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20">
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7">
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7">
       <c r="B50" t="s">
         <v>120</v>
       </c>
@@ -7010,115 +7253,115 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7">
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7">
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7">
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7">
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7">
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7">
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7">
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7">
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7">
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7">
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7">
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7">
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7">
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7">
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
     </row>
-    <row r="65" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7">
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7">
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7">
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
     </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7">
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
     </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7">
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
     </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7">
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
     </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7">
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7">
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
     </row>
-    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:7">
       <c r="D73" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:7">
       <c r="D74" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:7">
       <c r="D75" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:7">
       <c r="D76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:7">
       <c r="D77" s="3" t="s">
         <v>8</v>
       </c>
@@ -7126,35 +7369,35 @@
   </sheetData>
   <autoFilter ref="A1:M37" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}"/>
   <conditionalFormatting sqref="H25:H26">
-    <cfRule type="cellIs" dxfId="12" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="34" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="35" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="36" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I12">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15:I18 I20">
-    <cfRule type="cellIs" dxfId="6" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="70" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="71" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="72" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7164,7 +7407,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="1" operator="equal" id="{981E1B3E-06CD-4E01-8081-22EA37FE816B}">
-            <xm:f>'Team votes &amp; Misc Info'!$R$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$L$5</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7174,7 +7417,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="2" operator="equal" id="{CC91F5C6-12E2-4C70-BDE1-41D28F789B3C}">
-            <xm:f>'Team votes &amp; Misc Info'!$R$2</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$L$2</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7184,7 +7427,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="3" operator="equal" id="{4B2553DE-3827-417C-AAEF-48EE05247D0B}">
-            <xm:f>'Team votes &amp; Misc Info'!$R$3</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$L$3</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7194,7 +7437,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="5" operator="equal" id="{8C367ECA-8C5D-48A5-A5F1-EADADEA57874}">
-            <xm:f>'Team votes &amp; Misc Info'!$R$4</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$L$4</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7207,7 +7450,7 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="6" operator="equal" id="{344CC581-A1A3-486A-9628-9C3640970D2A}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$5</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7217,7 +7460,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="7" operator="equal" id="{996E347F-2D7A-4E82-909A-0552EAB66B5A}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$4</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$4</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7227,7 +7470,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="8" operator="equal" id="{2794A480-20AF-4750-BB33-AE5AFB6EC6A1}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$3</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$3</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7237,7 +7480,7 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="cellIs" priority="9" operator="equal" id="{8E978570-7E82-47D0-B51E-82BC3737C8E9}">
-            <xm:f>'Team votes &amp; Misc Info'!$P$2</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$2</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -7254,13 +7497,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{26307064-1325-4EBA-996D-45D5D7F61598}">
           <x14:formula1>
-            <xm:f>'Team votes &amp; Misc Info'!$P$2:$P$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$J$2:$J$5</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K28</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70105738-C97C-43BB-80BE-8021B63D21DF}">
           <x14:formula1>
-            <xm:f>'Team votes &amp; Misc Info'!$R$2:$R$5</xm:f>
+            <xm:f>'Team votes &amp; Misc Info'!$L$2:$L$5</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B28</xm:sqref>
         </x14:dataValidation>
@@ -7270,110 +7513,262 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6A8ABF-E61F-4C75-ADCE-19B4345AB4F4}">
-  <dimension ref="A1:AK33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA348513-37C3-4823-B24D-B6F996329F0C}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="35.140625" customWidth="1"/>
-    <col min="3" max="3" width="43.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="8" max="8" width="41.140625" customWidth="1"/>
-    <col min="35" max="35" width="42.28515625" customWidth="1"/>
-    <col min="36" max="36" width="48.42578125" customWidth="1"/>
-    <col min="37" max="37" width="66.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="83.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="119" t="s">
-        <v>421</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="G1" s="120" t="s">
-        <v>328</v>
-      </c>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="P1" s="119" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AI1" s="116" t="s">
-        <v>310</v>
-      </c>
-      <c r="AJ1" s="117"/>
-      <c r="AK1" s="118"/>
-    </row>
-    <row r="33" spans="1:12" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="116" t="s">
-        <v>329</v>
-      </c>
-      <c r="B33" s="117"/>
-      <c r="C33" s="118"/>
-      <c r="F33" s="116" t="s">
-        <v>417</v>
-      </c>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
+    <row r="1" spans="1:6">
+      <c r="A1" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="25">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="25">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="25">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="25">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="25">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="25">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>2</v>
+      </c>
+      <c r="E6" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="24">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="22">
+        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32.5" customHeight="1">
+      <c r="A9" s="126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="126"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.5">
+      <c r="A11" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="42">
+        <v>1</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="42">
+        <v>2</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="42">
+        <v>3</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="42">
+        <v>4</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="29">
+      <c r="A17" s="42">
+        <v>5</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>224</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="AI1:AK1"/>
-    <mergeCell ref="P1:AE1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:N1"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="F33:L33"/>
+  <mergeCells count="1">
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569F1412-D6F6-4C33-BE23-573808AF6A8E}">
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" customWidth="1"/>
-    <col min="5" max="5" width="61.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" customWidth="1"/>
+    <col min="5" max="5" width="61.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="82" t="s">
         <v>331</v>
       </c>
@@ -7405,7 +7800,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" s="81" t="s">
         <v>338</v>
       </c>
@@ -7437,7 +7832,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="81" t="s">
         <v>338</v>
       </c>
@@ -7469,7 +7864,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="81" t="s">
         <v>338</v>
       </c>
@@ -7501,7 +7896,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="81" t="s">
         <v>338</v>
       </c>
@@ -7533,7 +7928,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="81" t="s">
         <v>338</v>
       </c>
@@ -7565,7 +7960,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="81" t="s">
         <v>338</v>
       </c>
@@ -7597,7 +7992,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="81" t="s">
         <v>338</v>
       </c>
@@ -7629,7 +8024,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="81" t="s">
         <v>338</v>
       </c>
@@ -7661,7 +8056,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="81" t="s">
         <v>362</v>
       </c>
@@ -7693,7 +8088,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="81" t="s">
         <v>362</v>
       </c>
@@ -7725,7 +8120,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="81" t="s">
         <v>362</v>
       </c>
@@ -7757,7 +8152,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="81" t="s">
         <v>362</v>
       </c>
@@ -7789,7 +8184,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="81" t="s">
         <v>362</v>
       </c>
@@ -7821,7 +8216,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="81" t="s">
         <v>362</v>
       </c>
@@ -7853,7 +8248,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="81" t="s">
         <v>362</v>
       </c>
@@ -7885,7 +8280,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="81" t="s">
         <v>362</v>
       </c>
@@ -7917,7 +8312,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="81" t="s">
         <v>362</v>
       </c>
@@ -7949,7 +8344,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="81" t="s">
         <v>362</v>
       </c>
@@ -7981,7 +8376,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="81" t="s">
         <v>362</v>
       </c>
@@ -8013,7 +8408,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="81" t="s">
         <v>362</v>
       </c>
@@ -8045,7 +8440,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="81" t="s">
         <v>362</v>
       </c>
@@ -8077,7 +8472,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="81" t="s">
         <v>362</v>
       </c>
@@ -8109,7 +8504,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="81" t="s">
         <v>362</v>
       </c>
@@ -8141,7 +8536,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="81" t="s">
         <v>362</v>
       </c>
@@ -8173,7 +8568,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="81" t="s">
         <v>362</v>
       </c>
@@ -8205,7 +8600,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="81" t="s">
         <v>362</v>
       </c>
@@ -8237,7 +8632,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="81" t="s">
         <v>362</v>
       </c>
@@ -8269,7 +8664,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="81" t="s">
         <v>403</v>
       </c>
@@ -8301,7 +8696,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="81" t="s">
         <v>403</v>
       </c>
@@ -8333,7 +8728,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="81" t="s">
         <v>403</v>
       </c>
@@ -8365,7 +8760,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="81" t="s">
         <v>403</v>
       </c>
@@ -8397,7 +8792,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24">
       <c r="A33" s="81" t="s">
         <v>403</v>
       </c>
@@ -8429,7 +8824,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24">
       <c r="A34" s="81" t="s">
         <v>403</v>
       </c>
@@ -8461,7 +8856,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24">
       <c r="A35" s="81" t="s">
         <v>403</v>
       </c>
@@ -8493,97 +8888,97 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="121" t="s">
+    <row r="42" spans="1:24" ht="14.5" customHeight="1">
+      <c r="A42" s="120" t="s">
         <v>418</v>
       </c>
-      <c r="B42" s="121"/>
-      <c r="C42" s="121"/>
-      <c r="D42" s="121"/>
-      <c r="E42" s="121"/>
-      <c r="F42" s="121"/>
-      <c r="G42" s="121"/>
-      <c r="I42" s="122" t="s">
+      <c r="B42" s="120"/>
+      <c r="C42" s="120"/>
+      <c r="D42" s="120"/>
+      <c r="E42" s="120"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="120"/>
+      <c r="I42" s="121" t="s">
         <v>419</v>
       </c>
-      <c r="J42" s="123"/>
-      <c r="K42" s="123"/>
-      <c r="L42" s="123"/>
-      <c r="M42" s="123"/>
-      <c r="N42" s="123"/>
-      <c r="O42" s="123"/>
-      <c r="P42" s="123"/>
-      <c r="Q42" s="123"/>
-      <c r="R42" s="123"/>
-      <c r="S42" s="123"/>
-      <c r="T42" s="123"/>
-      <c r="U42" s="123"/>
-      <c r="V42" s="123"/>
-      <c r="W42" s="123"/>
-      <c r="X42" s="123"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A43" s="121"/>
-      <c r="B43" s="121"/>
-      <c r="C43" s="121"/>
-      <c r="D43" s="121"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="121"/>
-      <c r="G43" s="121"/>
-      <c r="I43" s="122"/>
-      <c r="J43" s="123"/>
-      <c r="K43" s="123"/>
-      <c r="L43" s="123"/>
-      <c r="M43" s="123"/>
-      <c r="N43" s="123"/>
-      <c r="O43" s="123"/>
-      <c r="P43" s="123"/>
-      <c r="Q43" s="123"/>
-      <c r="R43" s="123"/>
-      <c r="S43" s="123"/>
-      <c r="T43" s="123"/>
-      <c r="U43" s="123"/>
-      <c r="V43" s="123"/>
-      <c r="W43" s="123"/>
-      <c r="X43" s="123"/>
-    </row>
-    <row r="60" spans="9:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I60" s="121" t="s">
+      <c r="J42" s="122"/>
+      <c r="K42" s="122"/>
+      <c r="L42" s="122"/>
+      <c r="M42" s="122"/>
+      <c r="N42" s="122"/>
+      <c r="O42" s="122"/>
+      <c r="P42" s="122"/>
+      <c r="Q42" s="122"/>
+      <c r="R42" s="122"/>
+      <c r="S42" s="122"/>
+      <c r="T42" s="122"/>
+      <c r="U42" s="122"/>
+      <c r="V42" s="122"/>
+      <c r="W42" s="122"/>
+      <c r="X42" s="122"/>
+    </row>
+    <row r="43" spans="1:24">
+      <c r="A43" s="120"/>
+      <c r="B43" s="120"/>
+      <c r="C43" s="120"/>
+      <c r="D43" s="120"/>
+      <c r="E43" s="120"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="120"/>
+      <c r="I43" s="121"/>
+      <c r="J43" s="122"/>
+      <c r="K43" s="122"/>
+      <c r="L43" s="122"/>
+      <c r="M43" s="122"/>
+      <c r="N43" s="122"/>
+      <c r="O43" s="122"/>
+      <c r="P43" s="122"/>
+      <c r="Q43" s="122"/>
+      <c r="R43" s="122"/>
+      <c r="S43" s="122"/>
+      <c r="T43" s="122"/>
+      <c r="U43" s="122"/>
+      <c r="V43" s="122"/>
+      <c r="W43" s="122"/>
+      <c r="X43" s="122"/>
+    </row>
+    <row r="60" spans="9:24" ht="14.5" customHeight="1">
+      <c r="I60" s="120" t="s">
         <v>420</v>
       </c>
-      <c r="J60" s="121"/>
-      <c r="K60" s="121"/>
-      <c r="L60" s="121"/>
-      <c r="M60" s="121"/>
-      <c r="N60" s="121"/>
-      <c r="O60" s="121"/>
-      <c r="P60" s="121"/>
-      <c r="Q60" s="121"/>
-      <c r="R60" s="121"/>
-      <c r="S60" s="121"/>
-      <c r="T60" s="121"/>
-      <c r="U60" s="121"/>
-      <c r="V60" s="121"/>
-      <c r="W60" s="121"/>
-      <c r="X60" s="121"/>
-    </row>
-    <row r="61" spans="9:24" x14ac:dyDescent="0.25">
-      <c r="I61" s="121"/>
-      <c r="J61" s="121"/>
-      <c r="K61" s="121"/>
-      <c r="L61" s="121"/>
-      <c r="M61" s="121"/>
-      <c r="N61" s="121"/>
-      <c r="O61" s="121"/>
-      <c r="P61" s="121"/>
-      <c r="Q61" s="121"/>
-      <c r="R61" s="121"/>
-      <c r="S61" s="121"/>
-      <c r="T61" s="121"/>
-      <c r="U61" s="121"/>
-      <c r="V61" s="121"/>
-      <c r="W61" s="121"/>
-      <c r="X61" s="121"/>
+      <c r="J60" s="120"/>
+      <c r="K60" s="120"/>
+      <c r="L60" s="120"/>
+      <c r="M60" s="120"/>
+      <c r="N60" s="120"/>
+      <c r="O60" s="120"/>
+      <c r="P60" s="120"/>
+      <c r="Q60" s="120"/>
+      <c r="R60" s="120"/>
+      <c r="S60" s="120"/>
+      <c r="T60" s="120"/>
+      <c r="U60" s="120"/>
+      <c r="V60" s="120"/>
+      <c r="W60" s="120"/>
+      <c r="X60" s="120"/>
+    </row>
+    <row r="61" spans="9:24">
+      <c r="I61" s="120"/>
+      <c r="J61" s="120"/>
+      <c r="K61" s="120"/>
+      <c r="L61" s="120"/>
+      <c r="M61" s="120"/>
+      <c r="N61" s="120"/>
+      <c r="O61" s="120"/>
+      <c r="P61" s="120"/>
+      <c r="Q61" s="120"/>
+      <c r="R61" s="120"/>
+      <c r="S61" s="120"/>
+      <c r="T61" s="120"/>
+      <c r="U61" s="120"/>
+      <c r="V61" s="120"/>
+      <c r="W61" s="120"/>
+      <c r="X61" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8597,52 +8992,52 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7F1919-2543-40B0-86E7-ADC6C70417C2}">
   <dimension ref="A1:H145"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="122.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="69.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="122.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="126" t="s">
+    <row r="1" spans="1:8" ht="14.5" customHeight="1">
+      <c r="A1" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="123" t="s">
         <v>429</v>
       </c>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="123" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="125"/>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -8659,7 +9054,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>431</v>
       </c>
@@ -8676,7 +9071,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>434</v>
       </c>
@@ -8693,7 +9088,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>437</v>
       </c>
@@ -8707,7 +9102,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>439</v>
       </c>
@@ -8721,7 +9116,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>442</v>
       </c>
@@ -8735,7 +9130,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>445</v>
       </c>
@@ -8746,7 +9141,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>447</v>
       </c>
@@ -8763,7 +9158,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>451</v>
       </c>
@@ -8774,7 +9169,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>453</v>
       </c>
@@ -8785,7 +9180,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>455</v>
       </c>
@@ -8802,7 +9197,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>458</v>
       </c>
@@ -8816,7 +9211,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>461</v>
       </c>
@@ -8830,7 +9225,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>463</v>
       </c>
@@ -8844,7 +9239,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>466</v>
       </c>
@@ -8858,7 +9253,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>468</v>
       </c>
@@ -8869,7 +9264,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>470</v>
       </c>
@@ -8880,29 +9275,29 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="124" t="s">
+      <c r="B23" s="123" t="s">
         <v>473</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="124"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="124" t="s">
+      <c r="B24" s="123" t="s">
         <v>474</v>
       </c>
-      <c r="C24" s="125"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -8919,7 +9314,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
         <v>434</v>
       </c>
@@ -8936,7 +9331,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
         <v>476</v>
       </c>
@@ -8947,7 +9342,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>478</v>
       </c>
@@ -8958,7 +9353,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
         <v>480</v>
       </c>
@@ -8969,7 +9364,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
         <v>482</v>
       </c>
@@ -8980,29 +9375,29 @@
         <v>483</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="124" t="s">
+      <c r="B32" s="123" t="s">
         <v>484</v>
       </c>
-      <c r="C32" s="125"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="125"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="124" t="s">
+      <c r="B33" s="123" t="s">
         <v>485</v>
       </c>
-      <c r="C33" s="125"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="124"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
@@ -9019,7 +9414,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
         <v>439</v>
       </c>
@@ -9036,7 +9431,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -9050,29 +9445,29 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="124" t="s">
+      <c r="B38" s="123" t="s">
         <v>487</v>
       </c>
-      <c r="C38" s="125"/>
-      <c r="D38" s="125"/>
-      <c r="E38" s="125"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="124"/>
+      <c r="D38" s="124"/>
+      <c r="E38" s="124"/>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="124" t="s">
+      <c r="B39" s="123" t="s">
         <v>488</v>
       </c>
-      <c r="C39" s="125"/>
-      <c r="D39" s="125"/>
-      <c r="E39" s="125"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C39" s="124"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="124"/>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -9089,7 +9484,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
         <v>442</v>
       </c>
@@ -9106,7 +9501,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
         <v>490</v>
       </c>
@@ -9120,29 +9515,29 @@
         <v>491</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="124" t="s">
+      <c r="B44" s="123" t="s">
         <v>492</v>
       </c>
-      <c r="C44" s="125"/>
-      <c r="D44" s="125"/>
-      <c r="E44" s="125"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C44" s="124"/>
+      <c r="D44" s="124"/>
+      <c r="E44" s="124"/>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="124" t="s">
+      <c r="B45" s="123" t="s">
         <v>493</v>
       </c>
-      <c r="C45" s="125"/>
-      <c r="D45" s="125"/>
-      <c r="E45" s="125"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C45" s="124"/>
+      <c r="D45" s="124"/>
+      <c r="E45" s="124"/>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
         <v>41</v>
       </c>
@@ -9159,7 +9554,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
         <v>494</v>
       </c>
@@ -9176,7 +9571,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -9193,29 +9588,29 @@
         <v>497</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="124" t="s">
+      <c r="B50" s="123" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="125"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="125"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C50" s="124"/>
+      <c r="D50" s="124"/>
+      <c r="E50" s="124"/>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="124" t="s">
+      <c r="B51" s="123" t="s">
         <v>499</v>
       </c>
-      <c r="C51" s="125"/>
-      <c r="D51" s="125"/>
-      <c r="E51" s="125"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C51" s="124"/>
+      <c r="D51" s="124"/>
+      <c r="E51" s="124"/>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
         <v>41</v>
       </c>
@@ -9232,7 +9627,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
         <v>500</v>
       </c>
@@ -9249,7 +9644,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>431</v>
       </c>
@@ -9263,7 +9658,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
         <v>494</v>
       </c>
@@ -9277,7 +9672,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
         <v>504</v>
       </c>
@@ -9288,29 +9683,29 @@
         <v>505</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="124" t="s">
+      <c r="B58" s="123" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="125"/>
-      <c r="D58" s="125"/>
-      <c r="E58" s="125"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C58" s="124"/>
+      <c r="D58" s="124"/>
+      <c r="E58" s="124"/>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="124" t="s">
+      <c r="B59" s="123" t="s">
         <v>507</v>
       </c>
-      <c r="C59" s="125"/>
-      <c r="D59" s="125"/>
-      <c r="E59" s="125"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C59" s="124"/>
+      <c r="D59" s="124"/>
+      <c r="E59" s="124"/>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" s="1" t="s">
         <v>41</v>
       </c>
@@ -9327,7 +9722,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
         <v>508</v>
       </c>
@@ -9344,7 +9739,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
         <v>510</v>
       </c>
@@ -9358,29 +9753,29 @@
         <v>511</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="124" t="s">
+      <c r="B64" s="123" t="s">
         <v>512</v>
       </c>
-      <c r="C64" s="125"/>
-      <c r="D64" s="125"/>
-      <c r="E64" s="125"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C64" s="124"/>
+      <c r="D64" s="124"/>
+      <c r="E64" s="124"/>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="124" t="s">
+      <c r="B65" s="123" t="s">
         <v>513</v>
       </c>
-      <c r="C65" s="125"/>
-      <c r="D65" s="125"/>
-      <c r="E65" s="125"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C65" s="124"/>
+      <c r="D65" s="124"/>
+      <c r="E65" s="124"/>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>41</v>
       </c>
@@ -9397,7 +9792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
         <v>514</v>
       </c>
@@ -9414,7 +9809,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
         <v>431</v>
       </c>
@@ -9428,7 +9823,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
         <v>508</v>
       </c>
@@ -9442,7 +9837,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
         <v>517</v>
       </c>
@@ -9453,29 +9848,29 @@
         <v>518</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B72" s="124" t="s">
+      <c r="B72" s="123" t="s">
         <v>519</v>
       </c>
-      <c r="C72" s="125"/>
-      <c r="D72" s="125"/>
-      <c r="E72" s="125"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C72" s="124"/>
+      <c r="D72" s="124"/>
+      <c r="E72" s="124"/>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B73" s="124" t="s">
+      <c r="B73" s="123" t="s">
         <v>520</v>
       </c>
-      <c r="C73" s="125"/>
-      <c r="D73" s="125"/>
-      <c r="E73" s="125"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C73" s="124"/>
+      <c r="D73" s="124"/>
+      <c r="E73" s="124"/>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
         <v>41</v>
       </c>
@@ -9492,7 +9887,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
         <v>521</v>
       </c>
@@ -9509,7 +9904,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
         <v>523</v>
       </c>
@@ -9523,29 +9918,29 @@
         <v>524</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B78" s="124" t="s">
+      <c r="B78" s="123" t="s">
         <v>525</v>
       </c>
-      <c r="C78" s="125"/>
-      <c r="D78" s="125"/>
-      <c r="E78" s="125"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C78" s="124"/>
+      <c r="D78" s="124"/>
+      <c r="E78" s="124"/>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B79" s="124" t="s">
+      <c r="B79" s="123" t="s">
         <v>526</v>
       </c>
-      <c r="C79" s="125"/>
-      <c r="D79" s="125"/>
-      <c r="E79" s="125"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C79" s="124"/>
+      <c r="D79" s="124"/>
+      <c r="E79" s="124"/>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
         <v>41</v>
       </c>
@@ -9562,7 +9957,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
         <v>527</v>
       </c>
@@ -9579,7 +9974,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
         <v>431</v>
       </c>
@@ -9593,7 +9988,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
         <v>521</v>
       </c>
@@ -9607,7 +10002,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
         <v>530</v>
       </c>
@@ -9618,7 +10013,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
         <v>532</v>
       </c>
@@ -9629,7 +10024,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
         <v>534</v>
       </c>
@@ -9640,7 +10035,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
         <v>536</v>
       </c>
@@ -9651,29 +10046,29 @@
         <v>537</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B89" s="124" t="s">
+      <c r="B89" s="123" t="s">
         <v>538</v>
       </c>
-      <c r="C89" s="125"/>
-      <c r="D89" s="125"/>
-      <c r="E89" s="125"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C89" s="124"/>
+      <c r="D89" s="124"/>
+      <c r="E89" s="124"/>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B90" s="124" t="s">
+      <c r="B90" s="123" t="s">
         <v>539</v>
       </c>
-      <c r="C90" s="125"/>
-      <c r="D90" s="125"/>
-      <c r="E90" s="125"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C90" s="124"/>
+      <c r="D90" s="124"/>
+      <c r="E90" s="124"/>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" s="1" t="s">
         <v>41</v>
       </c>
@@ -9690,7 +10085,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
         <v>540</v>
       </c>
@@ -9707,7 +10102,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -9721,7 +10116,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
         <v>543</v>
       </c>
@@ -9735,7 +10130,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
         <v>546</v>
       </c>
@@ -9749,29 +10144,29 @@
         <v>547</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B97" s="124" t="s">
+      <c r="B97" s="123" t="s">
         <v>548</v>
       </c>
-      <c r="C97" s="125"/>
-      <c r="D97" s="125"/>
-      <c r="E97" s="125"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C97" s="124"/>
+      <c r="D97" s="124"/>
+      <c r="E97" s="124"/>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B98" s="124" t="s">
+      <c r="B98" s="123" t="s">
         <v>549</v>
       </c>
-      <c r="C98" s="125"/>
-      <c r="D98" s="125"/>
-      <c r="E98" s="125"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C98" s="124"/>
+      <c r="D98" s="124"/>
+      <c r="E98" s="124"/>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" s="1" t="s">
         <v>41</v>
       </c>
@@ -9788,7 +10183,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
         <v>550</v>
       </c>
@@ -9805,7 +10200,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
         <v>431</v>
       </c>
@@ -9822,7 +10217,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
         <v>540</v>
       </c>
@@ -9839,7 +10234,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
         <v>532</v>
       </c>
@@ -9850,7 +10245,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
         <v>534</v>
       </c>
@@ -9861,7 +10256,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
         <v>536</v>
       </c>
@@ -9872,29 +10267,29 @@
         <v>537</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5">
       <c r="A107" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B107" s="124" t="s">
+      <c r="B107" s="123" t="s">
         <v>555</v>
       </c>
-      <c r="C107" s="125"/>
-      <c r="D107" s="125"/>
-      <c r="E107" s="125"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C107" s="124"/>
+      <c r="D107" s="124"/>
+      <c r="E107" s="124"/>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B108" s="124" t="s">
+      <c r="B108" s="123" t="s">
         <v>556</v>
       </c>
-      <c r="C108" s="125"/>
-      <c r="D108" s="125"/>
-      <c r="E108" s="125"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C108" s="124"/>
+      <c r="D108" s="124"/>
+      <c r="E108" s="124"/>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" s="1" t="s">
         <v>41</v>
       </c>
@@ -9911,7 +10306,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
         <v>557</v>
       </c>
@@ -9928,7 +10323,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
         <v>431</v>
       </c>
@@ -9942,7 +10337,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
         <v>559</v>
       </c>
@@ -9953,7 +10348,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
         <v>561</v>
       </c>
@@ -9964,29 +10359,29 @@
         <v>562</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5">
       <c r="A115" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B115" s="124" t="s">
+      <c r="B115" s="123" t="s">
         <v>563</v>
       </c>
-      <c r="C115" s="125"/>
-      <c r="D115" s="125"/>
-      <c r="E115" s="125"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C115" s="124"/>
+      <c r="D115" s="124"/>
+      <c r="E115" s="124"/>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B116" s="124" t="s">
+      <c r="B116" s="123" t="s">
         <v>564</v>
       </c>
-      <c r="C116" s="125"/>
-      <c r="D116" s="125"/>
-      <c r="E116" s="125"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C116" s="124"/>
+      <c r="D116" s="124"/>
+      <c r="E116" s="124"/>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" s="1" t="s">
         <v>41</v>
       </c>
@@ -10003,7 +10398,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
         <v>565</v>
       </c>
@@ -10020,7 +10415,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
         <v>431</v>
       </c>
@@ -10034,7 +10429,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
         <v>567</v>
       </c>
@@ -10048,7 +10443,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
         <v>559</v>
       </c>
@@ -10059,7 +10454,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
         <v>561</v>
       </c>
@@ -10070,29 +10465,29 @@
         <v>571</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5">
       <c r="A124" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B124" s="124" t="s">
+      <c r="B124" s="123" t="s">
         <v>572</v>
       </c>
-      <c r="C124" s="125"/>
-      <c r="D124" s="125"/>
-      <c r="E124" s="125"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C124" s="124"/>
+      <c r="D124" s="124"/>
+      <c r="E124" s="124"/>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B125" s="124" t="s">
+      <c r="B125" s="123" t="s">
         <v>573</v>
       </c>
-      <c r="C125" s="125"/>
-      <c r="D125" s="125"/>
-      <c r="E125" s="125"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C125" s="124"/>
+      <c r="D125" s="124"/>
+      <c r="E125" s="124"/>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
         <v>41</v>
       </c>
@@ -10109,7 +10504,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
         <v>574</v>
       </c>
@@ -10126,7 +10521,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
         <v>431</v>
       </c>
@@ -10140,7 +10535,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
         <v>576</v>
       </c>
@@ -10151,7 +10546,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
         <v>534</v>
       </c>
@@ -10162,7 +10557,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
         <v>536</v>
       </c>
@@ -10173,29 +10568,29 @@
         <v>579</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="124" t="s">
+      <c r="B133" s="123" t="s">
         <v>580</v>
       </c>
-      <c r="C133" s="125"/>
-      <c r="D133" s="125"/>
-      <c r="E133" s="125"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C133" s="124"/>
+      <c r="D133" s="124"/>
+      <c r="E133" s="124"/>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B134" s="124" t="s">
+      <c r="B134" s="123" t="s">
         <v>581</v>
       </c>
-      <c r="C134" s="125"/>
-      <c r="D134" s="125"/>
-      <c r="E134" s="125"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C134" s="124"/>
+      <c r="D134" s="124"/>
+      <c r="E134" s="124"/>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
         <v>41</v>
       </c>
@@ -10212,7 +10607,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
         <v>437</v>
       </c>
@@ -10229,7 +10624,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
         <v>434</v>
       </c>
@@ -10246,7 +10641,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
         <v>468</v>
       </c>
@@ -10257,7 +10652,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
         <v>455</v>
       </c>
@@ -10271,7 +10666,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
         <v>458</v>
       </c>
@@ -10285,7 +10680,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
         <v>461</v>
       </c>
@@ -10296,7 +10691,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>463</v>
       </c>
@@ -10307,7 +10702,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>466</v>
       </c>
@@ -10318,7 +10713,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>470</v>
       </c>
@@ -10329,7 +10724,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>585</v>
       </c>
@@ -10345,18 +10740,19 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B133:E133"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B98:E98"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B24:E24"/>
@@ -10365,36 +10761,35 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B133:E133"/>
-    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B89:E89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F8DE2A-76E6-452A-AE90-13C80C3D40F2}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="57.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
@@ -10405,7 +10800,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -10416,7 +10811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -10424,7 +10819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="29">
       <c r="A4" s="5" t="s">
         <v>25</v>
       </c>
@@ -10435,7 +10830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -10446,436 +10841,63 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="105" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="101.5">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
         <v>94</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DCDC7C-55B3-416C-9E03-05A0A063B246}">
-  <dimension ref="A1:T17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="6.140625" customWidth="1"/>
-    <col min="20" max="20" width="11.85546875" customWidth="1"/>
-    <col min="23" max="23" width="18.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="P1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="42">
-        <v>1</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42">
-        <v>2</v>
-      </c>
-      <c r="E2" s="42">
-        <v>1</v>
-      </c>
-      <c r="F2" s="42">
-        <v>2</v>
-      </c>
-      <c r="G2" s="42">
-        <v>2</v>
-      </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="K2" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="L2" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="T2" s="42" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="42">
-        <v>2</v>
-      </c>
-      <c r="C3" s="42">
-        <v>1</v>
-      </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="I3" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="J3" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="25">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="25">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="25">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,5,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="T3" s="42" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42">
-        <v>2</v>
-      </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42">
-        <v>2</v>
-      </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="I4" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="J4" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="L4" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="M4" s="25">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>2</v>
-      </c>
-      <c r="N4" s="25">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,4,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="R4" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="T4" s="42" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42">
-        <v>1</v>
-      </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42">
-        <v>1</v>
-      </c>
-      <c r="G5" s="42">
-        <v>1</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="J5" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="L5" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>2</v>
-      </c>
-      <c r="N5" s="25">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,3,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="R5" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="T5" s="42" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I6" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>2</v>
-      </c>
-      <c r="M6" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-      <c r="N6" s="24">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,2,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I7" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="J7" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,1,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,2,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,3,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,4,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="22">
-        <f>COUNTIFS('[1]RAID Log'!$B$2:$B$200,"Risk",'[1]RAID Log'!$F$2:$F$200,1,'[1]RAID Log'!$G$2:$G$200,5,'[1]RAID Log'!$N$2:$N$200,"&lt;&gt;Closed")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I9" s="86" t="s">
-        <v>217</v>
-      </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="86"/>
-      <c r="N9" s="86"/>
-    </row>
-    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I11" s="21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I12" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="27" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I13" s="42">
-        <v>1</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I14" s="42">
-        <v>2</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I15" s="42">
-        <v>3</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I16" s="42">
-        <v>4</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="9:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="I17" s="42">
-        <v>5</v>
-      </c>
-      <c r="J17" s="48" t="s">
-        <v>224</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="I9:N9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/Datathon Project.xlsx
+++ b/docs/Datathon Project.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anchit\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoa-my.sharepoint.com/personal/ghin287_uoa_auckland_ac_nz/Documents/Documents/University/Datathon temp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3FBC14-72BA-42A7-A028-E7A78C040042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1F4A7BC-5C27-4579-8900-F0D73B159D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
+    <workbookView xWindow="7536" yWindow="17172" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B8873715-DDF3-4B00-844B-82E399C3542D}"/>
   </bookViews>
   <sheets>
     <sheet name="Team Overview" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RAID Logs '!$A$1:$M$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RAID Logs '!$A$1:$M$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="591">
   <si>
     <t>court</t>
   </si>
@@ -2049,6 +2049,15 @@
   <si>
     <t>6 gramss- Team 4</t>
   </si>
+  <si>
+    <t>R09</t>
+  </si>
+  <si>
+    <t>Hardcoded password in git history in 003_CreateIngestionAgentRoles.sql</t>
+  </si>
+  <si>
+    <t>file provided in github for marking purposes, but would be correctly held in Snowflake and run via python script from .env. Low immediate risk for POC.</t>
+  </si>
 </sst>
 </file>
 
@@ -2057,7 +2066,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2831,6 +2840,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2845,21 +2869,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2933,6 +2942,9 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2947,9 +2959,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2984,34 +2993,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3075,6 +3056,34 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3932,7 +3941,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Summary"/>
@@ -4348,9 +4357,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4388,7 +4397,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4494,7 +4503,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4636,7 +4645,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4645,103 +4654,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70241A6B-2CF1-42DB-9288-7E14FFCD0A5F}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultColWidth="21.26953125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="21.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="73.54296875" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="73.5703125" customWidth="1"/>
     <col min="4" max="4" width="70" customWidth="1"/>
-    <col min="5" max="5" width="49.81640625" customWidth="1"/>
-    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="54.65" customHeight="1">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="94" t="s">
         <v>263</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>78</v>
       </c>
       <c r="B3" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="89" t="s">
+      <c r="D3" s="94" t="s">
         <v>587</v>
       </c>
-      <c r="E3" s="90"/>
+      <c r="E3" s="95"/>
       <c r="F3" s="3"/>
       <c r="G3" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>75</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="90"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
       <c r="F4" s="3"/>
       <c r="G4" s="12" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
         <v>76</v>
       </c>
       <c r="B5" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="D5" s="89"/>
-      <c r="E5" s="90"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="95"/>
       <c r="F5" s="3"/>
       <c r="G5" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="39" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="89"/>
-      <c r="E6" s="90"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="95"/>
       <c r="F6" s="3"/>
       <c r="G6" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="50"/>
       <c r="B7" s="51"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="90"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="95"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="10" spans="1:7" ht="62.5" customHeight="1">
-      <c r="A10" s="88" t="s">
+    <row r="10" spans="1:7" ht="62.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="93" t="s">
         <v>290</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88" t="s">
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-    </row>
-    <row r="11" spans="1:7" ht="27" customHeight="1">
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+    </row>
+    <row r="11" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56" t="s">
         <v>18</v>
       </c>
@@ -4761,7 +4770,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="43.5">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="52" t="s">
         <v>8</v>
       </c>
@@ -4781,7 +4790,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="72.5">
+    <row r="13" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>9</v>
       </c>
@@ -4801,7 +4810,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="43.5">
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>6</v>
       </c>
@@ -4821,7 +4830,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>7</v>
       </c>
@@ -4841,7 +4850,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>4</v>
       </c>
@@ -4859,7 +4868,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>5</v>
       </c>
@@ -4879,13 +4888,13 @@
         <v>315</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="86" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="91" t="s">
         <v>258</v>
       </c>
-      <c r="B20" s="87"/>
-    </row>
-    <row r="21" spans="1:6" ht="22.5" customHeight="1">
+      <c r="B20" s="92"/>
+    </row>
+    <row r="21" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
         <v>18</v>
       </c>
@@ -4893,7 +4902,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="29">
+    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="79" t="s">
         <v>289</v>
       </c>
@@ -4901,7 +4910,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="78" t="s">
         <v>260</v>
       </c>
@@ -4909,7 +4918,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="78" t="s">
         <v>79</v>
       </c>
@@ -4917,7 +4926,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
         <v>90</v>
       </c>
@@ -4925,7 +4934,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
         <v>89</v>
       </c>
@@ -4933,7 +4942,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>91</v>
       </c>
@@ -4941,7 +4950,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
         <v>288</v>
       </c>
@@ -4949,7 +4958,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="80" t="s">
         <v>70</v>
       </c>
@@ -4957,7 +4966,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="81" t="s">
         <v>311</v>
       </c>
@@ -4965,7 +4974,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="81" t="s">
         <v>73</v>
       </c>
@@ -4973,7 +4982,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="81" t="s">
         <v>313</v>
       </c>
@@ -4981,7 +4990,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="14.5" customHeight="1"/>
+    <row r="36" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A20:B20"/>
@@ -5059,18 +5068,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DCDC7C-55B3-416C-9E03-05A0A063B246}">
   <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.453125" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.42578125" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" customWidth="1"/>
-    <col min="17" max="17" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="17" max="17" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>29</v>
       </c>
@@ -5102,7 +5111,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
@@ -5132,7 +5141,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
         <v>1</v>
       </c>
@@ -5156,7 +5165,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>2</v>
       </c>
@@ -5180,7 +5189,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
         <v>3</v>
       </c>
@@ -5206,7 +5215,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="29.15" customHeight="1"/>
+    <row r="9" spans="1:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5216,21 +5225,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB583F5E-2C32-4E7A-802B-32AB9008611B}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.453125" customWidth="1"/>
-    <col min="2" max="2" width="110.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" customWidth="1"/>
     <col min="9" max="9" width="51" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.54296875" customWidth="1"/>
-    <col min="11" max="11" width="8.1796875" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43" customHeight="1">
+    <row r="1" spans="1:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>277</v>
       </c>
@@ -5254,7 +5263,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5">
+    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>1</v>
       </c>
@@ -5277,7 +5286,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="29">
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="32">
         <v>2</v>
       </c>
@@ -5300,7 +5309,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="29">
+    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="32">
         <v>3</v>
       </c>
@@ -5323,7 +5332,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="29">
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
         <v>4</v>
       </c>
@@ -5346,7 +5355,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="32">
         <v>5</v>
       </c>
@@ -5369,7 +5378,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="29">
+    <row r="7" spans="1:9" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A7" s="32">
         <v>6</v>
       </c>
@@ -5392,7 +5401,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="87">
+    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="32">
         <v>7</v>
       </c>
@@ -5403,7 +5412,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="72.5">
+    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="32">
         <v>8</v>
       </c>
@@ -5413,14 +5422,14 @@
       <c r="C9" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="91" t="s">
+      <c r="F9" s="86" t="s">
         <v>308</v>
       </c>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="93"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="88"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32">
         <v>9</v>
       </c>
@@ -5431,7 +5440,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="32">
         <v>10</v>
       </c>
@@ -5442,7 +5451,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="32">
         <v>11</v>
       </c>
@@ -5453,81 +5462,81 @@
         <v>273</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1">
-      <c r="B14" s="94" t="s">
+    <row r="14" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="89" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="94"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="94"/>
-      <c r="C16" s="94"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="94"/>
-      <c r="C17" s="94"/>
-    </row>
-    <row r="18" spans="2:3">
-      <c r="B18" s="94"/>
-      <c r="C18" s="94"/>
-    </row>
-    <row r="19" spans="2:3">
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-    </row>
-    <row r="20" spans="2:3">
-      <c r="B20" s="94"/>
-      <c r="C20" s="94"/>
-    </row>
-    <row r="21" spans="2:3">
-      <c r="B21" s="94"/>
-      <c r="C21" s="94"/>
-    </row>
-    <row r="22" spans="2:3">
-      <c r="B22" s="94"/>
-      <c r="C22" s="94"/>
-    </row>
-    <row r="23" spans="2:3">
-      <c r="B23" s="94"/>
-      <c r="C23" s="94"/>
-    </row>
-    <row r="24" spans="2:3">
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-    </row>
-    <row r="26" spans="2:3" ht="14.5" customHeight="1"/>
-    <row r="27" spans="2:3">
+      <c r="C14" s="89"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="89"/>
+      <c r="C15" s="89"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="89"/>
+      <c r="C17" s="89"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+    </row>
+    <row r="26" spans="2:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
     </row>
-    <row r="28" spans="2:3" ht="72.650000000000006" customHeight="1">
-      <c r="B28" s="95" t="s">
+    <row r="28" spans="2:3" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="90" t="s">
         <v>327</v>
       </c>
-      <c r="C28" s="95"/>
-    </row>
-    <row r="29" spans="2:3">
+      <c r="C28" s="90"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="2:3">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="2:3">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="2:3">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" s="3"/>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="3"/>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="3"/>
     </row>
   </sheetData>
@@ -5557,17 +5566,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA72A998-9D73-4F3B-A55F-A4F70ED3DBFB}">
   <dimension ref="B1:J30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.1796875" customWidth="1"/>
-    <col min="2" max="2" width="44.453125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="39.1796875" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.54296875" customWidth="1"/>
-    <col min="6" max="6" width="23.81640625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="30.65" customHeight="1">
+    <row r="1" spans="2:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="26" t="s">
         <v>107</v>
       </c>
@@ -5579,7 +5588,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="2:10" ht="29.15" customHeight="1">
+    <row r="2" spans="2:10" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>227</v>
       </c>
@@ -5596,7 +5605,7 @@
       <c r="I2" s="98"/>
       <c r="J2" s="99"/>
     </row>
-    <row r="3" spans="2:10" ht="14.5" customHeight="1">
+    <row r="3" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="36" t="s">
         <v>100</v>
       </c>
@@ -5611,7 +5620,7 @@
       <c r="I3" s="101"/>
       <c r="J3" s="102"/>
     </row>
-    <row r="4" spans="2:10" ht="14.5" customHeight="1">
+    <row r="4" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
         <v>317</v>
       </c>
@@ -5626,7 +5635,7 @@
       <c r="I4" s="101"/>
       <c r="J4" s="102"/>
     </row>
-    <row r="5" spans="2:10" ht="14.5" customHeight="1">
+    <row r="5" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="36" t="s">
         <v>104</v>
       </c>
@@ -5641,7 +5650,7 @@
       <c r="I5" s="104"/>
       <c r="J5" s="105"/>
     </row>
-    <row r="6" spans="2:10" ht="29">
+    <row r="6" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="36" t="s">
         <v>318</v>
       </c>
@@ -5652,7 +5661,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="36" t="s">
         <v>105</v>
       </c>
@@ -5663,7 +5672,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="14.5" customHeight="1">
+    <row r="8" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="36" t="s">
         <v>422</v>
       </c>
@@ -5680,7 +5689,7 @@
       <c r="I8" s="107"/>
       <c r="J8" s="108"/>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>99</v>
       </c>
@@ -5695,7 +5704,7 @@
       <c r="I9" s="110"/>
       <c r="J9" s="111"/>
     </row>
-    <row r="10" spans="2:10" ht="14.5" customHeight="1">
+    <row r="10" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="36" t="s">
         <v>252</v>
       </c>
@@ -5710,73 +5719,73 @@
       <c r="I10" s="110"/>
       <c r="J10" s="111"/>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G11" s="109"/>
       <c r="H11" s="110"/>
       <c r="I11" s="110"/>
       <c r="J11" s="111"/>
     </row>
-    <row r="12" spans="2:10" ht="14.5" customHeight="1">
+    <row r="12" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12" s="112"/>
       <c r="H12" s="113"/>
       <c r="I12" s="113"/>
       <c r="J12" s="114"/>
     </row>
-    <row r="13" spans="2:10" ht="14.5" customHeight="1"/>
-    <row r="14" spans="2:10" ht="14.5" customHeight="1">
-      <c r="G14" s="94" t="s">
+    <row r="13" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="89" t="s">
         <v>249</v>
       </c>
-      <c r="H14" s="94"/>
-      <c r="I14" s="94"/>
-      <c r="J14" s="94"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-    </row>
-    <row r="16" spans="2:10" ht="14.5" customHeight="1">
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="94"/>
-    </row>
-    <row r="17" spans="7:10" ht="14.5" customHeight="1">
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-    </row>
-    <row r="18" spans="7:10" ht="14.5" customHeight="1"/>
-    <row r="19" spans="7:10" ht="14.5" customHeight="1">
-      <c r="G19" s="94" t="s">
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="89"/>
+    </row>
+    <row r="16" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="89"/>
+    </row>
+    <row r="17" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="89"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="89"/>
+    </row>
+    <row r="18" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="89" t="s">
         <v>250</v>
       </c>
-      <c r="H19" s="94"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="94"/>
-    </row>
-    <row r="20" spans="7:10">
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="94"/>
-      <c r="J20" s="94"/>
-    </row>
-    <row r="21" spans="7:10">
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-    </row>
-    <row r="22" spans="7:10" ht="14.5" customHeight="1">
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94"/>
-    </row>
-    <row r="25" spans="7:10" ht="14.5" customHeight="1">
+      <c r="H19" s="89"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="89"/>
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="89"/>
+    </row>
+    <row r="22" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G22" s="89"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="89"/>
+    </row>
+    <row r="25" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G25" s="96" t="s">
         <v>287</v>
       </c>
@@ -5784,31 +5793,31 @@
       <c r="I25" s="96"/>
       <c r="J25" s="96"/>
     </row>
-    <row r="26" spans="7:10">
+    <row r="26" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G26" s="96"/>
       <c r="H26" s="96"/>
       <c r="I26" s="96"/>
       <c r="J26" s="96"/>
     </row>
-    <row r="27" spans="7:10">
+    <row r="27" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G27" s="96"/>
       <c r="H27" s="96"/>
       <c r="I27" s="96"/>
       <c r="J27" s="96"/>
     </row>
-    <row r="28" spans="7:10" ht="14.5" customHeight="1">
+    <row r="28" spans="7:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G28" s="96"/>
       <c r="H28" s="96"/>
       <c r="I28" s="96"/>
       <c r="J28" s="96"/>
     </row>
-    <row r="29" spans="7:10">
+    <row r="29" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G29" s="96"/>
       <c r="H29" s="96"/>
       <c r="I29" s="96"/>
       <c r="J29" s="96"/>
     </row>
-    <row r="30" spans="7:10">
+    <row r="30" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G30" s="96"/>
       <c r="H30" s="96"/>
       <c r="I30" s="96"/>
@@ -5890,19 +5899,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6A8ABF-E61F-4C75-ADCE-19B4345AB4F4}">
   <dimension ref="A1:AK33"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.54296875" customWidth="1"/>
-    <col min="2" max="2" width="35.1796875" customWidth="1"/>
-    <col min="3" max="3" width="43.54296875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="43.5703125" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="8" max="8" width="41.1796875" customWidth="1"/>
-    <col min="35" max="35" width="42.26953125" customWidth="1"/>
-    <col min="36" max="36" width="48.453125" customWidth="1"/>
-    <col min="37" max="37" width="66.7265625" customWidth="1"/>
+    <col min="8" max="8" width="41.140625" customWidth="1"/>
+    <col min="35" max="35" width="42.28515625" customWidth="1"/>
+    <col min="36" max="36" width="48.42578125" customWidth="1"/>
+    <col min="37" max="37" width="66.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="37.5" customHeight="1">
+    <row r="1" spans="1:37" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="118" t="s">
         <v>421</v>
       </c>
@@ -5944,7 +5953,7 @@
       <c r="AJ1" s="116"/>
       <c r="AK1" s="117"/>
     </row>
-    <row r="33" spans="1:12" ht="42.65" customHeight="1">
+    <row r="33" spans="1:12" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="115" t="s">
         <v>329</v>
       </c>
@@ -5976,27 +5985,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}">
-  <dimension ref="A1:T77"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:T78"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.26953125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" style="3" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" customWidth="1"/>
-    <col min="6" max="6" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.54296875" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="13.81640625" customWidth="1"/>
-    <col min="18" max="18" width="20.453125" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="21.54296875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="3" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="18" max="18" width="20.42578125" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="21.5703125" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="26">
+    <row r="1" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>108</v>
       </c>
@@ -6046,7 +6055,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="37.5">
+    <row r="2" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
         <v>119</v>
       </c>
@@ -6096,7 +6105,7 @@
       </c>
       <c r="T2" s="16"/>
     </row>
-    <row r="3" spans="1:20" ht="29">
+    <row r="3" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
         <v>126</v>
       </c>
@@ -6146,7 +6155,7 @@
       </c>
       <c r="T3" s="16"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5">
+    <row r="4" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="71" t="s">
         <v>129</v>
       </c>
@@ -6196,7 +6205,7 @@
       </c>
       <c r="T4" s="16"/>
     </row>
-    <row r="5" spans="1:20" ht="43.5">
+    <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
         <v>135</v>
       </c>
@@ -6246,7 +6255,7 @@
       </c>
       <c r="T5" s="16"/>
     </row>
-    <row r="6" spans="1:20" ht="58">
+    <row r="6" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="61" t="s">
         <v>140</v>
       </c>
@@ -6296,7 +6305,7 @@
       </c>
       <c r="T6" s="16"/>
     </row>
-    <row r="7" spans="1:20" ht="43.5">
+    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
         <v>140</v>
       </c>
@@ -6319,11 +6328,11 @@
         <v>2</v>
       </c>
       <c r="H7" s="74">
-        <f t="shared" ref="H7:H12" si="2">IF(AND(B7="Risk",ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
+        <f t="shared" ref="H7:H13" si="2">IF(AND(B7="Risk",ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
         <v>6</v>
       </c>
       <c r="I7" s="75" t="str">
-        <f t="shared" ref="I7:I12" si="3">IF(H7="","",IF(H7&gt;=15,"Red",IF(H7&gt;=8,"Amber","Green")))</f>
+        <f t="shared" ref="I7:I13" si="3">IF(H7="","",IF(H7&gt;=15,"Red",IF(H7&gt;=8,"Amber","Green")))</f>
         <v>Green</v>
       </c>
       <c r="J7" s="8" t="s">
@@ -6346,7 +6355,7 @@
       </c>
       <c r="T7" s="16"/>
     </row>
-    <row r="8" spans="1:20" ht="43.5">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
         <v>144</v>
       </c>
@@ -6396,7 +6405,7 @@
       </c>
       <c r="T8" s="16"/>
     </row>
-    <row r="9" spans="1:20" ht="43.5">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
         <v>147</v>
       </c>
@@ -6442,7 +6451,7 @@
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
     </row>
-    <row r="10" spans="1:20" ht="72.5">
+    <row r="10" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="71" t="s">
         <v>150</v>
       </c>
@@ -6492,60 +6501,62 @@
       </c>
       <c r="T10" s="16"/>
     </row>
-    <row r="11" spans="1:20" ht="29">
+    <row r="11" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="71" t="s">
-        <v>171</v>
+        <v>588</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="74" t="str">
+        <v>589</v>
+      </c>
+      <c r="D11" s="69"/>
+      <c r="E11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="73">
+        <v>4</v>
+      </c>
+      <c r="G11" s="73">
+        <v>4</v>
+      </c>
+      <c r="H11" s="74">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16</v>
       </c>
       <c r="I11" s="75" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="J11" s="8"/>
+        <v>Red</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>590</v>
+      </c>
       <c r="K11" s="37" t="s">
         <v>87</v>
       </c>
       <c r="L11" s="76">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M11" s="76">
-        <v>46289</v>
-      </c>
-      <c r="R11" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="S11" s="16" t="s">
-        <v>157</v>
-      </c>
+        <v>46290</v>
+      </c>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
       <c r="T11" s="16"/>
     </row>
-    <row r="12" spans="1:20" ht="29">
+    <row r="12" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="71" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B12" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D12" s="69" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="6"/>
@@ -6569,28 +6580,37 @@
         <v>46289</v>
       </c>
       <c r="R12" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S12" s="16" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T12" s="16"/>
     </row>
-    <row r="13" spans="1:20" ht="25">
+    <row r="13" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="71" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B13" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>55</v>
+        <v>179</v>
+      </c>
+      <c r="D13" s="69" t="s">
+        <v>180</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="77"/>
+      <c r="H13" s="74" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I13" s="75" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="J13" s="8"/>
       <c r="K13" s="37" t="s">
         <v>87</v>
@@ -6602,22 +6622,22 @@
         <v>46289</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S13" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T13" s="16"/>
     </row>
-    <row r="14" spans="1:20" ht="29">
+    <row r="14" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="71" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B14" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="6"/>
@@ -6635,29 +6655,28 @@
         <v>46289</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S14" s="16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="T14" s="16"/>
     </row>
-    <row r="15" spans="1:20" ht="29">
+    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B15" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="69"/>
+        <v>56</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="75"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="77"/>
       <c r="J15" s="8"/>
       <c r="K15" s="37" t="s">
         <v>87</v>
@@ -6669,22 +6688,22 @@
         <v>46289</v>
       </c>
       <c r="R15" s="16" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="S15" s="16" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="T15" s="16"/>
     </row>
-    <row r="16" spans="1:20" ht="29">
+    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="71" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="69"/>
       <c r="E16" s="8"/>
@@ -6703,22 +6722,22 @@
         <v>46289</v>
       </c>
       <c r="R16" s="16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="S16" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T16" s="16"/>
     </row>
-    <row r="17" spans="1:20" ht="58">
+    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="71" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B17" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" s="69"/>
       <c r="E17" s="8"/>
@@ -6736,19 +6755,23 @@
       <c r="M17" s="76">
         <v>46289</v>
       </c>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
+      <c r="R17" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="S17" s="16" t="s">
+        <v>170</v>
+      </c>
       <c r="T17" s="16"/>
     </row>
-    <row r="18" spans="1:20" ht="29">
+    <row r="18" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B18" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="69"/>
       <c r="E18" s="8"/>
@@ -6770,21 +6793,22 @@
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
     </row>
-    <row r="19" spans="1:20" ht="43.5">
+    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>61</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D19" s="69"/>
       <c r="E19" s="8"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="77"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="75"/>
       <c r="J19" s="8"/>
       <c r="K19" s="37" t="s">
         <v>87</v>
@@ -6799,22 +6823,21 @@
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
     </row>
-    <row r="20" spans="1:20" ht="43.5">
+    <row r="20" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="71" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="B20" s="72" t="s">
         <v>172</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="69"/>
+        <v>61</v>
+      </c>
       <c r="E20" s="8"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="75"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="77"/>
       <c r="J20" s="8"/>
       <c r="K20" s="37" t="s">
         <v>87</v>
@@ -6829,27 +6852,23 @@
       <c r="S20" s="16"/>
       <c r="T20" s="16"/>
     </row>
-    <row r="21" spans="1:20" ht="29">
+    <row r="21" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="71" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="B21" s="72" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="D21"/>
-      <c r="E21" s="8" t="s">
-        <v>8</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D21" s="69"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="8" t="s">
-        <v>297</v>
-      </c>
+      <c r="H21" s="74"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="8"/>
       <c r="K21" s="37" t="s">
         <v>87</v>
       </c>
@@ -6863,15 +6882,15 @@
       <c r="S21" s="16"/>
       <c r="T21" s="16"/>
     </row>
-    <row r="22" spans="1:20" ht="43.5">
+    <row r="22" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="71" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B22" s="72" t="s">
         <v>188</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D22"/>
       <c r="E22" s="8" t="s">
@@ -6882,7 +6901,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="77"/>
       <c r="J22" s="8" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="K22" s="37" t="s">
         <v>87</v>
@@ -6897,26 +6916,26 @@
       <c r="S22" s="16"/>
       <c r="T22" s="16"/>
     </row>
-    <row r="23" spans="1:20" ht="43.5">
+    <row r="23" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="71" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" s="72" t="s">
         <v>188</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D23"/>
       <c r="E23" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="I23" s="77"/>
       <c r="J23" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K23" s="37" t="s">
         <v>87</v>
@@ -6931,26 +6950,26 @@
       <c r="S23" s="16"/>
       <c r="T23" s="16"/>
     </row>
-    <row r="24" spans="1:20" ht="43.5">
+    <row r="24" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="71" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B24" s="72" t="s">
         <v>188</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D24"/>
       <c r="E24" s="8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K24" s="37" t="s">
         <v>87</v>
@@ -6965,28 +6984,26 @@
       <c r="S24" s="16"/>
       <c r="T24" s="16"/>
     </row>
-    <row r="25" spans="1:20" ht="29">
+    <row r="25" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="71" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" s="72" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D25" s="70" t="s">
+        <v>301</v>
+      </c>
+      <c r="D25"/>
+      <c r="E25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="8"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="75" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="77"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
       <c r="J25" s="8" t="s">
-        <v>194</v>
+        <v>302</v>
       </c>
       <c r="K25" s="37" t="s">
         <v>87</v>
@@ -7001,18 +7018,18 @@
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="71" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B26" s="72" t="s">
         <v>193</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D26" s="70" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="6"/>
@@ -7037,24 +7054,28 @@
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
     </row>
-    <row r="27" spans="1:20" ht="58">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="71" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B27" s="72" t="s">
         <v>193</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="D27" s="60"/>
+        <v>204</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>9</v>
+      </c>
       <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="77"/>
       <c r="J27" s="8" t="s">
-        <v>416</v>
+        <v>194</v>
       </c>
       <c r="K27" s="37" t="s">
         <v>87</v>
@@ -7069,15 +7090,15 @@
       <c r="S27" s="16"/>
       <c r="T27" s="16"/>
     </row>
-    <row r="28" spans="1:20" ht="58">
+    <row r="28" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="71" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B28" s="72" t="s">
         <v>193</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D28" s="60"/>
       <c r="E28" s="8"/>
@@ -7101,36 +7122,56 @@
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D29" s="60"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="76">
+        <v>46289</v>
+      </c>
+      <c r="M29" s="76">
+        <v>46289</v>
+      </c>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
-      <c r="T31" s="16" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="C32"/>
-      <c r="D32" s="16"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="I32"/>
+      <c r="T31" s="16"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R32" s="16"/>
       <c r="S32" s="16"/>
       <c r="T32" s="16" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C33"/>
       <c r="D33" s="16"/>
       <c r="F33" s="3"/>
@@ -7139,10 +7180,10 @@
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
       <c r="T33" s="16" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C34"/>
       <c r="D34" s="16"/>
       <c r="F34" s="3"/>
@@ -7151,253 +7192,265 @@
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
       <c r="T34" s="16" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C35"/>
+      <c r="D35" s="16"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="I35"/>
       <c r="R35" s="16"/>
       <c r="S35" s="16"/>
       <c r="T35" s="16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="C36"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
+      <c r="I36"/>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
       <c r="T36" s="16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
       <c r="T37" s="16" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-    </row>
-    <row r="39" spans="1:20">
-      <c r="A39" s="14"/>
-      <c r="B39" s="13"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="13"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="49"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="R39" s="13"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13"/>
-    </row>
-    <row r="40" spans="1:20">
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A40" s="14"/>
+      <c r="B40" s="13"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="13"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="H40" s="13"/>
+      <c r="I40" s="49"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="R40" s="13"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="13"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
     </row>
-    <row r="49" spans="2:7">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="2:7">
-      <c r="B50" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>294</v>
-      </c>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="2:7">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="2:7">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
     </row>
-    <row r="56" spans="2:7">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="2:7">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
     </row>
-    <row r="60" spans="2:7">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
     </row>
-    <row r="61" spans="2:7">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
     </row>
-    <row r="62" spans="2:7">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
     </row>
-    <row r="63" spans="2:7">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
     </row>
-    <row r="64" spans="2:7">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
     </row>
-    <row r="65" spans="4:7">
+    <row r="65" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
     </row>
-    <row r="66" spans="4:7">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
     </row>
-    <row r="67" spans="4:7">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
     </row>
-    <row r="68" spans="4:7">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
     </row>
-    <row r="69" spans="4:7">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
     </row>
-    <row r="70" spans="4:7">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
     </row>
-    <row r="71" spans="4:7">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
     </row>
-    <row r="72" spans="4:7">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
     </row>
-    <row r="73" spans="4:7">
-      <c r="D73" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="4:7">
+    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+    </row>
+    <row r="74" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D74" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="4:7">
+    <row r="75" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D75" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="4:7">
+    <row r="76" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="4:7">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D77" s="3" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D78" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M37" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}"/>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="cellIs" dxfId="16" priority="34" operator="equal">
+  <autoFilter ref="A1:M38" xr:uid="{B61A661B-79AD-4791-9EC8-3651D794C8C6}"/>
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="cellIs" dxfId="12" priority="34" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="35" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="36" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I12">
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+  <conditionalFormatting sqref="I2:I13">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15:I18 I20">
-    <cfRule type="cellIs" dxfId="10" priority="70" operator="equal">
+  <conditionalFormatting sqref="I16:I19 I21">
+    <cfRule type="cellIs" dxfId="6" priority="70" operator="equal">
       <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="71" operator="equal">
       <formula>"Amber"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="72" operator="equal">
       <formula>"Green"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7446,7 +7499,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:B28</xm:sqref>
+          <xm:sqref>B2:B29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="cellIs" priority="6" operator="equal" id="{344CC581-A1A3-486A-9628-9C3640970D2A}">
@@ -7489,7 +7542,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K2:K28</xm:sqref>
+          <xm:sqref>K2:K29</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -7499,13 +7552,13 @@
           <x14:formula1>
             <xm:f>'Team votes &amp; Misc Info'!$J$2:$J$5</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K28</xm:sqref>
+          <xm:sqref>K2:K29</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{70105738-C97C-43BB-80BE-8021B63D21DF}">
           <x14:formula1>
             <xm:f>'Team votes &amp; Misc Info'!$L$2:$L$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B28</xm:sqref>
+          <xm:sqref>B2:B29</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7516,17 +7569,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA348513-37C3-4823-B24D-B6F996329F0C}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
-    <col min="4" max="4" width="14.81640625" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>255</v>
       </c>
@@ -7538,7 +7591,7 @@
       <c r="E1" s="27"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="27"/>
       <c r="B2" s="27" t="s">
         <v>207</v>
@@ -7556,7 +7609,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>212</v>
       </c>
@@ -7581,7 +7634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>213</v>
       </c>
@@ -7606,7 +7659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
         <v>214</v>
       </c>
@@ -7631,7 +7684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>215</v>
       </c>
@@ -7656,7 +7709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>216</v>
       </c>
@@ -7681,22 +7734,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="32.5" customHeight="1">
-      <c r="A9" s="126" t="s">
+    <row r="9" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="120" t="s">
         <v>217</v>
       </c>
-      <c r="B9" s="126"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.5">
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>112</v>
       </c>
@@ -7704,7 +7757,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="42">
         <v>1</v>
       </c>
@@ -7712,7 +7765,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="42">
         <v>2</v>
       </c>
@@ -7720,7 +7773,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="42">
         <v>3</v>
       </c>
@@ -7728,7 +7781,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="42">
         <v>4</v>
       </c>
@@ -7736,7 +7789,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="29">
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="42">
         <v>5</v>
       </c>
@@ -7755,20 +7808,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569F1412-D6F6-4C33-BE23-573808AF6A8E}">
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" customWidth="1"/>
-    <col min="5" max="5" width="61.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" customWidth="1"/>
+    <col min="5" max="5" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="82" t="s">
         <v>331</v>
       </c>
@@ -7800,7 +7853,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="81" t="s">
         <v>338</v>
       </c>
@@ -7832,7 +7885,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="81" t="s">
         <v>338</v>
       </c>
@@ -7864,7 +7917,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="81" t="s">
         <v>338</v>
       </c>
@@ -7896,7 +7949,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="81" t="s">
         <v>338</v>
       </c>
@@ -7928,7 +7981,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="81" t="s">
         <v>338</v>
       </c>
@@ -7960,7 +8013,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="81" t="s">
         <v>338</v>
       </c>
@@ -7992,7 +8045,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="81" t="s">
         <v>338</v>
       </c>
@@ -8024,7 +8077,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="81" t="s">
         <v>338</v>
       </c>
@@ -8056,7 +8109,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="81" t="s">
         <v>362</v>
       </c>
@@ -8088,7 +8141,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="81" t="s">
         <v>362</v>
       </c>
@@ -8120,7 +8173,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="81" t="s">
         <v>362</v>
       </c>
@@ -8152,7 +8205,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="81" t="s">
         <v>362</v>
       </c>
@@ -8184,7 +8237,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="81" t="s">
         <v>362</v>
       </c>
@@ -8216,7 +8269,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="81" t="s">
         <v>362</v>
       </c>
@@ -8248,7 +8301,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="81" t="s">
         <v>362</v>
       </c>
@@ -8280,7 +8333,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="81" t="s">
         <v>362</v>
       </c>
@@ -8312,7 +8365,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="81" t="s">
         <v>362</v>
       </c>
@@ -8344,7 +8397,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="81" t="s">
         <v>362</v>
       </c>
@@ -8376,7 +8429,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="81" t="s">
         <v>362</v>
       </c>
@@ -8408,7 +8461,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="81" t="s">
         <v>362</v>
       </c>
@@ -8440,7 +8493,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="81" t="s">
         <v>362</v>
       </c>
@@ -8472,7 +8525,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="81" t="s">
         <v>362</v>
       </c>
@@ -8504,7 +8557,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="81" t="s">
         <v>362</v>
       </c>
@@ -8536,7 +8589,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="81" t="s">
         <v>362</v>
       </c>
@@ -8568,7 +8621,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="81" t="s">
         <v>362</v>
       </c>
@@ -8600,7 +8653,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="81" t="s">
         <v>362</v>
       </c>
@@ -8632,7 +8685,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="81" t="s">
         <v>362</v>
       </c>
@@ -8664,7 +8717,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="81" t="s">
         <v>403</v>
       </c>
@@ -8696,7 +8749,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="81" t="s">
         <v>403</v>
       </c>
@@ -8728,7 +8781,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="81" t="s">
         <v>403</v>
       </c>
@@ -8760,7 +8813,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="81" t="s">
         <v>403</v>
       </c>
@@ -8792,7 +8845,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="81" t="s">
         <v>403</v>
       </c>
@@ -8824,7 +8877,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="81" t="s">
         <v>403</v>
       </c>
@@ -8856,7 +8909,7 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="81" t="s">
         <v>403</v>
       </c>
@@ -8888,97 +8941,97 @@
         <v>46290</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.5" customHeight="1">
-      <c r="A42" s="120" t="s">
+    <row r="42" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="121" t="s">
         <v>418</v>
       </c>
-      <c r="B42" s="120"/>
-      <c r="C42" s="120"/>
-      <c r="D42" s="120"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
-      <c r="I42" s="121" t="s">
+      <c r="B42" s="121"/>
+      <c r="C42" s="121"/>
+      <c r="D42" s="121"/>
+      <c r="E42" s="121"/>
+      <c r="F42" s="121"/>
+      <c r="G42" s="121"/>
+      <c r="I42" s="122" t="s">
         <v>419</v>
       </c>
-      <c r="J42" s="122"/>
-      <c r="K42" s="122"/>
-      <c r="L42" s="122"/>
-      <c r="M42" s="122"/>
-      <c r="N42" s="122"/>
-      <c r="O42" s="122"/>
-      <c r="P42" s="122"/>
-      <c r="Q42" s="122"/>
-      <c r="R42" s="122"/>
-      <c r="S42" s="122"/>
-      <c r="T42" s="122"/>
-      <c r="U42" s="122"/>
-      <c r="V42" s="122"/>
-      <c r="W42" s="122"/>
-      <c r="X42" s="122"/>
-    </row>
-    <row r="43" spans="1:24">
-      <c r="A43" s="120"/>
-      <c r="B43" s="120"/>
-      <c r="C43" s="120"/>
-      <c r="D43" s="120"/>
-      <c r="E43" s="120"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="120"/>
-      <c r="I43" s="121"/>
-      <c r="J43" s="122"/>
-      <c r="K43" s="122"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="122"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="122"/>
-      <c r="Q43" s="122"/>
-      <c r="R43" s="122"/>
-      <c r="S43" s="122"/>
-      <c r="T43" s="122"/>
-      <c r="U43" s="122"/>
-      <c r="V43" s="122"/>
-      <c r="W43" s="122"/>
-      <c r="X43" s="122"/>
-    </row>
-    <row r="60" spans="9:24" ht="14.5" customHeight="1">
-      <c r="I60" s="120" t="s">
+      <c r="J42" s="123"/>
+      <c r="K42" s="123"/>
+      <c r="L42" s="123"/>
+      <c r="M42" s="123"/>
+      <c r="N42" s="123"/>
+      <c r="O42" s="123"/>
+      <c r="P42" s="123"/>
+      <c r="Q42" s="123"/>
+      <c r="R42" s="123"/>
+      <c r="S42" s="123"/>
+      <c r="T42" s="123"/>
+      <c r="U42" s="123"/>
+      <c r="V42" s="123"/>
+      <c r="W42" s="123"/>
+      <c r="X42" s="123"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="121"/>
+      <c r="B43" s="121"/>
+      <c r="C43" s="121"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="121"/>
+      <c r="G43" s="121"/>
+      <c r="I43" s="122"/>
+      <c r="J43" s="123"/>
+      <c r="K43" s="123"/>
+      <c r="L43" s="123"/>
+      <c r="M43" s="123"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="123"/>
+      <c r="Q43" s="123"/>
+      <c r="R43" s="123"/>
+      <c r="S43" s="123"/>
+      <c r="T43" s="123"/>
+      <c r="U43" s="123"/>
+      <c r="V43" s="123"/>
+      <c r="W43" s="123"/>
+      <c r="X43" s="123"/>
+    </row>
+    <row r="60" spans="9:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I60" s="121" t="s">
         <v>420</v>
       </c>
-      <c r="J60" s="120"/>
-      <c r="K60" s="120"/>
-      <c r="L60" s="120"/>
-      <c r="M60" s="120"/>
-      <c r="N60" s="120"/>
-      <c r="O60" s="120"/>
-      <c r="P60" s="120"/>
-      <c r="Q60" s="120"/>
-      <c r="R60" s="120"/>
-      <c r="S60" s="120"/>
-      <c r="T60" s="120"/>
-      <c r="U60" s="120"/>
-      <c r="V60" s="120"/>
-      <c r="W60" s="120"/>
-      <c r="X60" s="120"/>
-    </row>
-    <row r="61" spans="9:24">
-      <c r="I61" s="120"/>
-      <c r="J61" s="120"/>
-      <c r="K61" s="120"/>
-      <c r="L61" s="120"/>
-      <c r="M61" s="120"/>
-      <c r="N61" s="120"/>
-      <c r="O61" s="120"/>
-      <c r="P61" s="120"/>
-      <c r="Q61" s="120"/>
-      <c r="R61" s="120"/>
-      <c r="S61" s="120"/>
-      <c r="T61" s="120"/>
-      <c r="U61" s="120"/>
-      <c r="V61" s="120"/>
-      <c r="W61" s="120"/>
-      <c r="X61" s="120"/>
+      <c r="J60" s="121"/>
+      <c r="K60" s="121"/>
+      <c r="L60" s="121"/>
+      <c r="M60" s="121"/>
+      <c r="N60" s="121"/>
+      <c r="O60" s="121"/>
+      <c r="P60" s="121"/>
+      <c r="Q60" s="121"/>
+      <c r="R60" s="121"/>
+      <c r="S60" s="121"/>
+      <c r="T60" s="121"/>
+      <c r="U60" s="121"/>
+      <c r="V60" s="121"/>
+      <c r="W60" s="121"/>
+      <c r="X60" s="121"/>
+    </row>
+    <row r="61" spans="9:24" x14ac:dyDescent="0.25">
+      <c r="I61" s="121"/>
+      <c r="J61" s="121"/>
+      <c r="K61" s="121"/>
+      <c r="L61" s="121"/>
+      <c r="M61" s="121"/>
+      <c r="N61" s="121"/>
+      <c r="O61" s="121"/>
+      <c r="P61" s="121"/>
+      <c r="Q61" s="121"/>
+      <c r="R61" s="121"/>
+      <c r="S61" s="121"/>
+      <c r="T61" s="121"/>
+      <c r="U61" s="121"/>
+      <c r="V61" s="121"/>
+      <c r="W61" s="121"/>
+      <c r="X61" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8995,49 +9048,49 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7F1919-2543-40B0-86E7-ADC6C70417C2}">
   <dimension ref="A1:H145"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="122.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="69.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="122.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.5" customHeight="1">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="126" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="123" t="s">
+      <c r="B3" s="124" t="s">
         <v>429</v>
       </c>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="C3" s="125"/>
+      <c r="D3" s="125"/>
+      <c r="E3" s="125"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="124" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="C4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
@@ -9054,7 +9107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>431</v>
       </c>
@@ -9071,7 +9124,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>434</v>
       </c>
@@ -9088,7 +9141,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>437</v>
       </c>
@@ -9102,7 +9155,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>439</v>
       </c>
@@ -9116,7 +9169,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>442</v>
       </c>
@@ -9130,7 +9183,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>445</v>
       </c>
@@ -9141,7 +9194,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>447</v>
       </c>
@@ -9158,7 +9211,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>451</v>
       </c>
@@ -9169,7 +9222,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>453</v>
       </c>
@@ -9180,7 +9233,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>455</v>
       </c>
@@ -9197,7 +9250,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>458</v>
       </c>
@@ -9211,7 +9264,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>461</v>
       </c>
@@ -9225,7 +9278,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>463</v>
       </c>
@@ -9239,7 +9292,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>466</v>
       </c>
@@ -9253,7 +9306,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>468</v>
       </c>
@@ -9264,7 +9317,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>470</v>
       </c>
@@ -9275,29 +9328,29 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="123" t="s">
+      <c r="B23" s="124" t="s">
         <v>473</v>
       </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="124" t="s">
         <v>474</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="C24" s="125"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="125"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -9314,7 +9367,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>434</v>
       </c>
@@ -9331,7 +9384,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>476</v>
       </c>
@@ -9342,7 +9395,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>478</v>
       </c>
@@ -9353,7 +9406,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>480</v>
       </c>
@@ -9364,7 +9417,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>482</v>
       </c>
@@ -9375,29 +9428,29 @@
         <v>483</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="123" t="s">
+      <c r="B32" s="124" t="s">
         <v>484</v>
       </c>
-      <c r="C32" s="124"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="C32" s="125"/>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="123" t="s">
+      <c r="B33" s="124" t="s">
         <v>485</v>
       </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="C33" s="125"/>
+      <c r="D33" s="125"/>
+      <c r="E33" s="125"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
@@ -9414,7 +9467,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>439</v>
       </c>
@@ -9431,7 +9484,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -9445,29 +9498,29 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="123" t="s">
+      <c r="B38" s="124" t="s">
         <v>487</v>
       </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="124"/>
-      <c r="E38" s="124"/>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="C38" s="125"/>
+      <c r="D38" s="125"/>
+      <c r="E38" s="125"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="123" t="s">
+      <c r="B39" s="124" t="s">
         <v>488</v>
       </c>
-      <c r="C39" s="124"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="124"/>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="C39" s="125"/>
+      <c r="D39" s="125"/>
+      <c r="E39" s="125"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -9484,7 +9537,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>442</v>
       </c>
@@ -9501,7 +9554,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>490</v>
       </c>
@@ -9515,29 +9568,29 @@
         <v>491</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="123" t="s">
+      <c r="B44" s="124" t="s">
         <v>492</v>
       </c>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="C44" s="125"/>
+      <c r="D44" s="125"/>
+      <c r="E44" s="125"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="123" t="s">
+      <c r="B45" s="124" t="s">
         <v>493</v>
       </c>
-      <c r="C45" s="124"/>
-      <c r="D45" s="124"/>
-      <c r="E45" s="124"/>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
+      <c r="E45" s="125"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>41</v>
       </c>
@@ -9554,7 +9607,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>494</v>
       </c>
@@ -9571,7 +9624,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -9588,29 +9641,29 @@
         <v>497</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="123" t="s">
+      <c r="B50" s="124" t="s">
         <v>498</v>
       </c>
-      <c r="C50" s="124"/>
-      <c r="D50" s="124"/>
-      <c r="E50" s="124"/>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="123" t="s">
+      <c r="B51" s="124" t="s">
         <v>499</v>
       </c>
-      <c r="C51" s="124"/>
-      <c r="D51" s="124"/>
-      <c r="E51" s="124"/>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="C51" s="125"/>
+      <c r="D51" s="125"/>
+      <c r="E51" s="125"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>41</v>
       </c>
@@ -9627,7 +9680,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>500</v>
       </c>
@@ -9644,7 +9697,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>431</v>
       </c>
@@ -9658,7 +9711,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>494</v>
       </c>
@@ -9672,7 +9725,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>504</v>
       </c>
@@ -9683,29 +9736,29 @@
         <v>505</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="123" t="s">
+      <c r="B58" s="124" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="124"/>
-      <c r="D58" s="124"/>
-      <c r="E58" s="124"/>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="C58" s="125"/>
+      <c r="D58" s="125"/>
+      <c r="E58" s="125"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="123" t="s">
+      <c r="B59" s="124" t="s">
         <v>507</v>
       </c>
-      <c r="C59" s="124"/>
-      <c r="D59" s="124"/>
-      <c r="E59" s="124"/>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="C59" s="125"/>
+      <c r="D59" s="125"/>
+      <c r="E59" s="125"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>41</v>
       </c>
@@ -9722,7 +9775,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>508</v>
       </c>
@@ -9739,7 +9792,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>510</v>
       </c>
@@ -9753,29 +9806,29 @@
         <v>511</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="123" t="s">
+      <c r="B64" s="124" t="s">
         <v>512</v>
       </c>
-      <c r="C64" s="124"/>
-      <c r="D64" s="124"/>
-      <c r="E64" s="124"/>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="C64" s="125"/>
+      <c r="D64" s="125"/>
+      <c r="E64" s="125"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B65" s="123" t="s">
+      <c r="B65" s="124" t="s">
         <v>513</v>
       </c>
-      <c r="C65" s="124"/>
-      <c r="D65" s="124"/>
-      <c r="E65" s="124"/>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="C65" s="125"/>
+      <c r="D65" s="125"/>
+      <c r="E65" s="125"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>41</v>
       </c>
@@ -9792,7 +9845,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>514</v>
       </c>
@@ -9809,7 +9862,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>431</v>
       </c>
@@ -9823,7 +9876,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>508</v>
       </c>
@@ -9837,7 +9890,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>517</v>
       </c>
@@ -9848,29 +9901,29 @@
         <v>518</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B72" s="123" t="s">
+      <c r="B72" s="124" t="s">
         <v>519</v>
       </c>
-      <c r="C72" s="124"/>
-      <c r="D72" s="124"/>
-      <c r="E72" s="124"/>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="C72" s="125"/>
+      <c r="D72" s="125"/>
+      <c r="E72" s="125"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B73" s="123" t="s">
+      <c r="B73" s="124" t="s">
         <v>520</v>
       </c>
-      <c r="C73" s="124"/>
-      <c r="D73" s="124"/>
-      <c r="E73" s="124"/>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="C73" s="125"/>
+      <c r="D73" s="125"/>
+      <c r="E73" s="125"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>41</v>
       </c>
@@ -9887,7 +9940,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>521</v>
       </c>
@@ -9904,7 +9957,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>523</v>
       </c>
@@ -9918,29 +9971,29 @@
         <v>524</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B78" s="123" t="s">
+      <c r="B78" s="124" t="s">
         <v>525</v>
       </c>
-      <c r="C78" s="124"/>
-      <c r="D78" s="124"/>
-      <c r="E78" s="124"/>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="C78" s="125"/>
+      <c r="D78" s="125"/>
+      <c r="E78" s="125"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B79" s="123" t="s">
+      <c r="B79" s="124" t="s">
         <v>526</v>
       </c>
-      <c r="C79" s="124"/>
-      <c r="D79" s="124"/>
-      <c r="E79" s="124"/>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="C79" s="125"/>
+      <c r="D79" s="125"/>
+      <c r="E79" s="125"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>41</v>
       </c>
@@ -9957,7 +10010,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>527</v>
       </c>
@@ -9974,7 +10027,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>431</v>
       </c>
@@ -9988,7 +10041,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>521</v>
       </c>
@@ -10002,7 +10055,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>530</v>
       </c>
@@ -10013,7 +10066,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>532</v>
       </c>
@@ -10024,7 +10077,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>534</v>
       </c>
@@ -10035,7 +10088,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>536</v>
       </c>
@@ -10046,29 +10099,29 @@
         <v>537</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B89" s="123" t="s">
+      <c r="B89" s="124" t="s">
         <v>538</v>
       </c>
-      <c r="C89" s="124"/>
-      <c r="D89" s="124"/>
-      <c r="E89" s="124"/>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="C89" s="125"/>
+      <c r="D89" s="125"/>
+      <c r="E89" s="125"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B90" s="123" t="s">
+      <c r="B90" s="124" t="s">
         <v>539</v>
       </c>
-      <c r="C90" s="124"/>
-      <c r="D90" s="124"/>
-      <c r="E90" s="124"/>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="C90" s="125"/>
+      <c r="D90" s="125"/>
+      <c r="E90" s="125"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>41</v>
       </c>
@@ -10085,7 +10138,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>540</v>
       </c>
@@ -10102,7 +10155,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -10116,7 +10169,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>543</v>
       </c>
@@ -10130,7 +10183,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>546</v>
       </c>
@@ -10144,29 +10197,29 @@
         <v>547</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B97" s="123" t="s">
+      <c r="B97" s="124" t="s">
         <v>548</v>
       </c>
-      <c r="C97" s="124"/>
-      <c r="D97" s="124"/>
-      <c r="E97" s="124"/>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="C97" s="125"/>
+      <c r="D97" s="125"/>
+      <c r="E97" s="125"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B98" s="123" t="s">
+      <c r="B98" s="124" t="s">
         <v>549</v>
       </c>
-      <c r="C98" s="124"/>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="C98" s="125"/>
+      <c r="D98" s="125"/>
+      <c r="E98" s="125"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>41</v>
       </c>
@@ -10183,7 +10236,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>550</v>
       </c>
@@ -10200,7 +10253,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>431</v>
       </c>
@@ -10217,7 +10270,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>540</v>
       </c>
@@ -10234,7 +10287,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>532</v>
       </c>
@@ -10245,7 +10298,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>534</v>
       </c>
@@ -10256,7 +10309,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>536</v>
       </c>
@@ -10267,29 +10320,29 @@
         <v>537</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B107" s="123" t="s">
+      <c r="B107" s="124" t="s">
         <v>555</v>
       </c>
-      <c r="C107" s="124"/>
-      <c r="D107" s="124"/>
-      <c r="E107" s="124"/>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="C107" s="125"/>
+      <c r="D107" s="125"/>
+      <c r="E107" s="125"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B108" s="123" t="s">
+      <c r="B108" s="124" t="s">
         <v>556</v>
       </c>
-      <c r="C108" s="124"/>
-      <c r="D108" s="124"/>
-      <c r="E108" s="124"/>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="C108" s="125"/>
+      <c r="D108" s="125"/>
+      <c r="E108" s="125"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>41</v>
       </c>
@@ -10306,7 +10359,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>557</v>
       </c>
@@ -10323,7 +10376,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>431</v>
       </c>
@@ -10337,7 +10390,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>559</v>
       </c>
@@ -10348,7 +10401,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>561</v>
       </c>
@@ -10359,29 +10412,29 @@
         <v>562</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B115" s="123" t="s">
+      <c r="B115" s="124" t="s">
         <v>563</v>
       </c>
-      <c r="C115" s="124"/>
-      <c r="D115" s="124"/>
-      <c r="E115" s="124"/>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="C115" s="125"/>
+      <c r="D115" s="125"/>
+      <c r="E115" s="125"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B116" s="123" t="s">
+      <c r="B116" s="124" t="s">
         <v>564</v>
       </c>
-      <c r="C116" s="124"/>
-      <c r="D116" s="124"/>
-      <c r="E116" s="124"/>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="C116" s="125"/>
+      <c r="D116" s="125"/>
+      <c r="E116" s="125"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>41</v>
       </c>
@@ -10398,7 +10451,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>565</v>
       </c>
@@ -10415,7 +10468,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>431</v>
       </c>
@@ -10429,7 +10482,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>567</v>
       </c>
@@ -10443,7 +10496,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>559</v>
       </c>
@@ -10454,7 +10507,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>561</v>
       </c>
@@ -10465,29 +10518,29 @@
         <v>571</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B124" s="123" t="s">
+      <c r="B124" s="124" t="s">
         <v>572</v>
       </c>
-      <c r="C124" s="124"/>
-      <c r="D124" s="124"/>
-      <c r="E124" s="124"/>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="C124" s="125"/>
+      <c r="D124" s="125"/>
+      <c r="E124" s="125"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B125" s="123" t="s">
+      <c r="B125" s="124" t="s">
         <v>573</v>
       </c>
-      <c r="C125" s="124"/>
-      <c r="D125" s="124"/>
-      <c r="E125" s="124"/>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="C125" s="125"/>
+      <c r="D125" s="125"/>
+      <c r="E125" s="125"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>41</v>
       </c>
@@ -10504,7 +10557,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>574</v>
       </c>
@@ -10521,7 +10574,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>431</v>
       </c>
@@ -10535,7 +10588,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>576</v>
       </c>
@@ -10546,7 +10599,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>534</v>
       </c>
@@ -10557,7 +10610,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>536</v>
       </c>
@@ -10568,29 +10621,29 @@
         <v>579</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="123" t="s">
+      <c r="B133" s="124" t="s">
         <v>580</v>
       </c>
-      <c r="C133" s="124"/>
-      <c r="D133" s="124"/>
-      <c r="E133" s="124"/>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="C133" s="125"/>
+      <c r="D133" s="125"/>
+      <c r="E133" s="125"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B134" s="123" t="s">
+      <c r="B134" s="124" t="s">
         <v>581</v>
       </c>
-      <c r="C134" s="124"/>
-      <c r="D134" s="124"/>
-      <c r="E134" s="124"/>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="C134" s="125"/>
+      <c r="D134" s="125"/>
+      <c r="E134" s="125"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>41</v>
       </c>
@@ -10607,7 +10660,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>437</v>
       </c>
@@ -10624,7 +10677,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>434</v>
       </c>
@@ -10641,7 +10694,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>468</v>
       </c>
@@ -10652,7 +10705,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>455</v>
       </c>
@@ -10666,7 +10719,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>458</v>
       </c>
@@ -10680,7 +10733,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>461</v>
       </c>
@@ -10691,7 +10744,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>463</v>
       </c>
@@ -10702,7 +10755,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>466</v>
       </c>
@@ -10713,7 +10766,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>470</v>
       </c>
@@ -10724,7 +10777,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>585</v>
       </c>
@@ -10740,19 +10793,7 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B125:E125"/>
-    <mergeCell ref="B133:E133"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B115:E115"/>
-    <mergeCell ref="B116:E116"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B89:E89"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B24:E24"/>
@@ -10761,6 +10802,11 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B98:E98"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="B78:E78"/>
@@ -10772,7 +10818,14 @@
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B64:E64"/>
     <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B133:E133"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B115:E115"/>
+    <mergeCell ref="B116:E116"/>
+    <mergeCell ref="B124:E124"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10782,14 +10835,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F8DE2A-76E6-452A-AE90-13C80C3D40F2}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.26953125" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.7265625" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
@@ -10800,7 +10853,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -10811,7 +10864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -10819,7 +10872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>25</v>
       </c>
@@ -10830,7 +10883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -10841,57 +10894,57 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="101.5">
+    <row r="17" spans="1:1" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>94</v>
       </c>
